--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
   <si>
     <t>#</t>
   </si>
@@ -90,6 +90,15 @@
   </si>
   <si>
     <t>属性倍率</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>血量倍率</t>
   </si>
   <si>
     <t>Strong</t>
@@ -1190,7 +1199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:AB46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1200,8 +1209,8 @@
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.58333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5833333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="22" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.0833333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.0833333333333" style="2" customWidth="1"/>
     <col min="10" max="10" width="18.5" style="2" customWidth="1"/>
     <col min="11" max="11" width="13.4166666666667" style="2" customWidth="1"/>
     <col min="12" max="12" width="10.3333333333333" style="2" customWidth="1"/>
@@ -1211,16 +1220,17 @@
     <col min="17" max="17" width="7.50833333333333" style="2" customWidth="1"/>
     <col min="18" max="18" width="11.8333333333333" style="2" customWidth="1"/>
     <col min="19" max="19" width="10.3333333333333" style="2" customWidth="1"/>
-    <col min="20" max="20" width="11.125" style="1"/>
-    <col min="21" max="21" width="9" style="1"/>
-    <col min="22" max="22" width="13.625" style="2" customWidth="1"/>
-    <col min="23" max="23" width="4.33333333333333" style="2" customWidth="1"/>
-    <col min="24" max="24" width="3.75" style="2" customWidth="1"/>
-    <col min="25" max="25" width="3" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="2"/>
+    <col min="20" max="20" width="8.33333333333333" style="1" customWidth="1"/>
+    <col min="21" max="21" width="7.25" style="1" customWidth="1"/>
+    <col min="22" max="24" width="7.16666666666667" style="2" customWidth="1"/>
+    <col min="25" max="25" width="8.41666666666667" style="2" customWidth="1"/>
+    <col min="26" max="26" width="4.33333333333333" style="2" customWidth="1"/>
+    <col min="27" max="27" width="3.75" style="2" customWidth="1"/>
+    <col min="28" max="28" width="3" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="2"/>
@@ -1253,8 +1263,17 @@
       <c r="Y1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="Z1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="2"/>
@@ -1287,8 +1306,17 @@
       <c r="Y2" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="Z2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1351,21 +1379,30 @@
       <c r="V3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="Z3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1416,82 +1453,88 @@
         <v>17</v>
       </c>
       <c r="V4" s="2"/>
-      <c r="W4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>23</v>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="V5" s="2"/>
-      <c r="W5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>26</v>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" ht="14" spans="1:25">
+    <row r="6" ht="14" spans="1:28">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1502,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1536,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1">
         <f t="shared" ref="R6:R46" si="4">T6*10</f>
@@ -1558,15 +1601,24 @@
       <c r="V6" s="2">
         <v>100</v>
       </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1">
+      <c r="W6" s="2">
+        <v>1</v>
+      </c>
+      <c r="X6" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:25">
+    <row r="7" customHeight="1" spans="1:28">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1577,22 +1629,22 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:H45" si="6">U7*V7/2</f>
-        <v>110</v>
+        <f t="shared" ref="H7:H45" si="6">U7*V7*W7</f>
+        <v>220</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" ref="I7:I45" si="7">U7*V7/5</f>
-        <v>44</v>
+        <f t="shared" ref="I7:I45" si="7">U7*V7*X7/100</f>
+        <v>11</v>
       </c>
       <c r="J7" s="1">
-        <f t="shared" ref="J7:J45" si="8">U7*V7*10</f>
-        <v>2200</v>
+        <f>U7*V7*Y7</f>
+        <v>3300</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="0"/>
@@ -1614,10 +1666,10 @@
         <v>0</v>
       </c>
       <c r="P7" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" si="4"/>
@@ -1634,18 +1686,28 @@
         <v>2</v>
       </c>
       <c r="V7" s="2">
-        <f t="shared" ref="V7:V17" si="9">V6+10</f>
+        <f t="shared" ref="V7:V17" si="8">V6+10</f>
         <v>110</v>
       </c>
-      <c r="W7" s="1">
-        <v>0</v>
-      </c>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1">
+      <c r="W7" s="2">
+        <v>1</v>
+      </c>
+      <c r="X7" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>Y6+5</f>
+        <v>15</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:25">
+    <row r="8" customHeight="1" spans="1:28">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1656,22 +1718,22 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
       <c r="H8" s="1">
         <f t="shared" si="6"/>
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="7"/>
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="J8" s="1">
-        <f t="shared" si="8"/>
-        <v>3600</v>
+        <f>U8*V8*Y8</f>
+        <v>7200</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="0"/>
@@ -1692,11 +1754,12 @@
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="4">
-        <v>0</v>
+      <c r="P8" s="2">
+        <f t="shared" ref="P8:P45" si="9">P7+2</f>
+        <v>12</v>
       </c>
       <c r="Q8" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="4"/>
@@ -1713,18 +1776,28 @@
         <v>3</v>
       </c>
       <c r="V8" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="W8" s="1">
-        <v>0</v>
-      </c>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1">
+      <c r="W8" s="2">
+        <v>1</v>
+      </c>
+      <c r="X8" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="2">
+        <f>Y7+5</f>
+        <v>20</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:25">
+    <row r="9" customHeight="1" spans="1:28">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1735,22 +1808,22 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G9" s="1">
         <v>4</v>
       </c>
       <c r="H9" s="1">
         <f t="shared" si="6"/>
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="7"/>
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" si="8"/>
-        <v>5200</v>
+        <f t="shared" ref="J7:J45" si="10">U9*V9*Y9</f>
+        <v>13000</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="0"/>
@@ -1771,11 +1844,12 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
-      <c r="P9" s="4">
-        <v>0</v>
+      <c r="P9" s="2">
+        <f t="shared" si="9"/>
+        <v>14</v>
       </c>
       <c r="Q9" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R9" s="1">
         <f t="shared" si="4"/>
@@ -1792,18 +1866,28 @@
         <v>4</v>
       </c>
       <c r="V9" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>130</v>
       </c>
-      <c r="W9" s="1">
-        <v>0</v>
-      </c>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1">
+      <c r="W9" s="2">
+        <v>1</v>
+      </c>
+      <c r="X9" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="2">
+        <f>Y8+5</f>
+        <v>25</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:25">
+    <row r="10" customHeight="1" spans="1:28">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1814,22 +1898,22 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
       </c>
       <c r="H10" s="1">
         <f t="shared" si="6"/>
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="7"/>
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="8"/>
-        <v>7000</v>
+        <f t="shared" si="10"/>
+        <v>21000</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="0"/>
@@ -1850,11 +1934,12 @@
       <c r="O10" s="1">
         <v>0</v>
       </c>
-      <c r="P10" s="4">
-        <v>0</v>
+      <c r="P10" s="2">
+        <f t="shared" si="9"/>
+        <v>16</v>
       </c>
       <c r="Q10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R10" s="1">
         <f t="shared" si="4"/>
@@ -1871,18 +1956,28 @@
         <v>5</v>
       </c>
       <c r="V10" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
-      <c r="W10" s="1">
-        <v>0</v>
-      </c>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1">
+      <c r="W10" s="2">
+        <v>1</v>
+      </c>
+      <c r="X10" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="2">
+        <f>Y9+5</f>
+        <v>30</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:25">
+    <row r="11" customHeight="1" spans="1:28">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1893,22 +1988,22 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="6"/>
-        <v>450</v>
+        <v>1800</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" si="7"/>
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="8"/>
-        <v>9000</v>
+        <f t="shared" si="10"/>
+        <v>36000</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" si="0"/>
@@ -1929,11 +2024,12 @@
       <c r="O11" s="1">
         <v>0</v>
       </c>
-      <c r="P11" s="4">
-        <v>0</v>
+      <c r="P11" s="2">
+        <f t="shared" si="9"/>
+        <v>18</v>
       </c>
       <c r="Q11" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" si="4"/>
@@ -1950,18 +2046,28 @@
         <v>6</v>
       </c>
       <c r="V11" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="W11" s="1">
-        <v>0</v>
-      </c>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1">
+      <c r="W11" s="2">
+        <v>2</v>
+      </c>
+      <c r="X11" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="2">
+        <f t="shared" ref="Y11:Y20" si="11">Y10+10</f>
+        <v>40</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:25">
+    <row r="12" customHeight="1" spans="1:28">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1972,22 +2078,22 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="6"/>
-        <v>560</v>
+        <v>2240</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="7"/>
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="8"/>
-        <v>11200</v>
+        <f t="shared" si="10"/>
+        <v>56000</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="0"/>
@@ -2008,11 +2114,12 @@
       <c r="O12" s="1">
         <v>0</v>
       </c>
-      <c r="P12" s="4">
-        <v>0</v>
+      <c r="P12" s="2">
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="Q12" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" si="4"/>
@@ -2029,18 +2136,28 @@
         <v>7</v>
       </c>
       <c r="V12" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>160</v>
       </c>
-      <c r="W12" s="1">
-        <v>0</v>
-      </c>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1">
+      <c r="W12" s="2">
+        <v>2</v>
+      </c>
+      <c r="X12" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="2">
+        <f t="shared" si="11"/>
+        <v>50</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:25">
+    <row r="13" customHeight="1" spans="1:28">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2051,22 +2168,22 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="6"/>
-        <v>680</v>
+        <v>2720</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="7"/>
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="8"/>
-        <v>13600</v>
+        <f t="shared" si="10"/>
+        <v>81600</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="0"/>
@@ -2087,11 +2204,12 @@
       <c r="O13" s="1">
         <v>0</v>
       </c>
-      <c r="P13" s="4">
-        <v>0</v>
+      <c r="P13" s="2">
+        <f t="shared" si="9"/>
+        <v>22</v>
       </c>
       <c r="Q13" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="4"/>
@@ -2108,18 +2226,28 @@
         <v>8</v>
       </c>
       <c r="V13" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>170</v>
       </c>
-      <c r="W13" s="1">
-        <v>0</v>
-      </c>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1">
+      <c r="W13" s="2">
+        <v>2</v>
+      </c>
+      <c r="X13" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y13" s="2">
+        <f t="shared" si="11"/>
+        <v>60</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:25">
+    <row r="14" customHeight="1" spans="1:28">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2130,22 +2258,22 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" si="6"/>
-        <v>810</v>
+        <v>3240</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="7"/>
-        <v>324</v>
+        <v>162</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" si="8"/>
-        <v>16200</v>
+        <f t="shared" si="10"/>
+        <v>113400</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="0"/>
@@ -2166,11 +2294,12 @@
       <c r="O14" s="1">
         <v>0</v>
       </c>
-      <c r="P14" s="4">
-        <v>0</v>
+      <c r="P14" s="2">
+        <f t="shared" si="9"/>
+        <v>24</v>
       </c>
       <c r="Q14" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="4"/>
@@ -2187,18 +2316,28 @@
         <v>9</v>
       </c>
       <c r="V14" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>180</v>
       </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1">
+      <c r="W14" s="2">
+        <v>2</v>
+      </c>
+      <c r="X14" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="2">
+        <f t="shared" si="11"/>
+        <v>70</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:25">
+    <row r="15" customHeight="1" spans="1:28">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2209,22 +2348,22 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" si="6"/>
-        <v>950</v>
+        <v>3800</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="7"/>
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="8"/>
-        <v>19000</v>
+        <f t="shared" si="10"/>
+        <v>152000</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="0"/>
@@ -2245,11 +2384,12 @@
       <c r="O15" s="1">
         <v>0</v>
       </c>
-      <c r="P15" s="4">
-        <v>0</v>
+      <c r="P15" s="2">
+        <f t="shared" si="9"/>
+        <v>26</v>
       </c>
       <c r="Q15" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R15" s="1">
         <f t="shared" si="4"/>
@@ -2266,18 +2406,28 @@
         <v>10</v>
       </c>
       <c r="V15" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>190</v>
       </c>
-      <c r="W15" s="1">
-        <v>0</v>
-      </c>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1">
+      <c r="W15" s="2">
+        <v>2</v>
+      </c>
+      <c r="X15" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y15" s="2">
+        <f t="shared" si="11"/>
+        <v>80</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:25">
+    <row r="16" customHeight="1" spans="1:28">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2288,22 +2438,22 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="1">
         <f t="shared" si="6"/>
-        <v>1100</v>
+        <v>6600</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="7"/>
-        <v>440</v>
+        <v>330</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="8"/>
-        <v>22000</v>
+        <f t="shared" si="10"/>
+        <v>198000</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="0"/>
@@ -2324,11 +2474,12 @@
       <c r="O16" s="1">
         <v>0</v>
       </c>
-      <c r="P16" s="4">
-        <v>0</v>
+      <c r="P16" s="2">
+        <f t="shared" si="9"/>
+        <v>28</v>
       </c>
       <c r="Q16" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R16" s="1">
         <f t="shared" si="4"/>
@@ -2345,18 +2496,28 @@
         <v>11</v>
       </c>
       <c r="V16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>200</v>
       </c>
-      <c r="W16" s="1">
-        <v>0</v>
-      </c>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1">
+      <c r="W16" s="2">
+        <v>3</v>
+      </c>
+      <c r="X16" s="2">
+        <v>15</v>
+      </c>
+      <c r="Y16" s="2">
+        <f t="shared" si="11"/>
+        <v>90</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:25">
+    <row r="17" customHeight="1" spans="3:28">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2367,22 +2528,22 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="1">
         <f t="shared" si="6"/>
-        <v>1320</v>
+        <v>7920</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="7"/>
-        <v>528</v>
+        <v>396</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="8"/>
-        <v>26400</v>
+        <f t="shared" si="10"/>
+        <v>264000</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="0"/>
@@ -2403,11 +2564,12 @@
       <c r="O17" s="1">
         <v>0</v>
       </c>
-      <c r="P17" s="4">
-        <v>0</v>
+      <c r="P17" s="2">
+        <f t="shared" si="9"/>
+        <v>30</v>
       </c>
       <c r="Q17" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R17" s="1">
         <f t="shared" si="4"/>
@@ -2424,18 +2586,28 @@
         <v>12</v>
       </c>
       <c r="V17" s="2">
-        <f t="shared" ref="V17:V30" si="10">V16+20</f>
+        <f t="shared" ref="V17:V30" si="12">V16+20</f>
         <v>220</v>
       </c>
-      <c r="W17" s="1">
-        <v>0</v>
-      </c>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1">
+      <c r="W17" s="2">
+        <v>3</v>
+      </c>
+      <c r="X17" s="2">
+        <v>15</v>
+      </c>
+      <c r="Y17" s="2">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:25">
+    <row r="18" customHeight="1" spans="3:28">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -2446,22 +2618,22 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G18" s="1">
         <v>13</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="6"/>
-        <v>1560</v>
+        <v>9360</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="7"/>
-        <v>624</v>
+        <v>468</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="8"/>
-        <v>31200</v>
+        <f t="shared" si="10"/>
+        <v>374400</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" si="0"/>
@@ -2482,11 +2654,12 @@
       <c r="O18" s="1">
         <v>0</v>
       </c>
-      <c r="P18" s="4">
-        <v>0</v>
+      <c r="P18" s="2">
+        <f t="shared" si="9"/>
+        <v>32</v>
       </c>
       <c r="Q18" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R18" s="1">
         <f t="shared" si="4"/>
@@ -2503,18 +2676,28 @@
         <v>13</v>
       </c>
       <c r="V18" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>240</v>
       </c>
-      <c r="W18" s="1">
-        <v>0</v>
-      </c>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1">
+      <c r="W18" s="2">
+        <v>3</v>
+      </c>
+      <c r="X18" s="2">
+        <v>15</v>
+      </c>
+      <c r="Y18" s="2">
+        <f t="shared" ref="Y18:Y30" si="13">Y17+20</f>
+        <v>120</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:25">
+    <row r="19" customHeight="1" spans="3:28">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -2525,22 +2708,22 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19" s="1">
         <v>14</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="6"/>
-        <v>1820</v>
+        <v>10920</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="7"/>
-        <v>728</v>
+        <v>546</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="8"/>
-        <v>36400</v>
+        <f t="shared" si="10"/>
+        <v>509600</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" si="0"/>
@@ -2561,11 +2744,12 @@
       <c r="O19" s="1">
         <v>0</v>
       </c>
-      <c r="P19" s="4">
-        <v>0</v>
+      <c r="P19" s="2">
+        <f t="shared" si="9"/>
+        <v>34</v>
       </c>
       <c r="Q19" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R19" s="1">
         <f t="shared" si="4"/>
@@ -2582,18 +2766,28 @@
         <v>14</v>
       </c>
       <c r="V19" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>260</v>
       </c>
-      <c r="W19" s="1">
-        <v>0</v>
-      </c>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1">
+      <c r="W19" s="2">
+        <v>3</v>
+      </c>
+      <c r="X19" s="2">
+        <v>15</v>
+      </c>
+      <c r="Y19" s="2">
+        <f t="shared" si="13"/>
+        <v>140</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:25">
+    <row r="20" customHeight="1" spans="3:28">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -2604,22 +2798,22 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G20" s="1">
         <v>15</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="6"/>
-        <v>2100</v>
+        <v>12600</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="7"/>
-        <v>840</v>
+        <v>630</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="8"/>
-        <v>42000</v>
+        <f t="shared" si="10"/>
+        <v>672000</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" si="0"/>
@@ -2640,11 +2834,12 @@
       <c r="O20" s="1">
         <v>0</v>
       </c>
-      <c r="P20" s="4">
-        <v>0</v>
+      <c r="P20" s="2">
+        <f t="shared" si="9"/>
+        <v>36</v>
       </c>
       <c r="Q20" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R20" s="1">
         <f t="shared" si="4"/>
@@ -2661,18 +2856,28 @@
         <v>15</v>
       </c>
       <c r="V20" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>280</v>
       </c>
-      <c r="W20" s="1">
-        <v>0</v>
-      </c>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1">
+      <c r="W20" s="2">
+        <v>3</v>
+      </c>
+      <c r="X20" s="2">
+        <v>15</v>
+      </c>
+      <c r="Y20" s="2">
+        <f t="shared" si="13"/>
+        <v>160</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:25">
+    <row r="21" customHeight="1" spans="3:28">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -2683,22 +2888,22 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G21" s="1">
         <v>16</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="6"/>
-        <v>2400</v>
+        <v>19200</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="7"/>
         <v>960</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="8"/>
-        <v>48000</v>
+        <f t="shared" si="10"/>
+        <v>864000</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" si="0"/>
@@ -2719,11 +2924,12 @@
       <c r="O21" s="1">
         <v>0</v>
       </c>
-      <c r="P21" s="4">
-        <v>0</v>
+      <c r="P21" s="2">
+        <f t="shared" si="9"/>
+        <v>38</v>
       </c>
       <c r="Q21" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R21" s="1">
         <f t="shared" si="4"/>
@@ -2740,18 +2946,28 @@
         <v>16</v>
       </c>
       <c r="V21" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>300</v>
       </c>
-      <c r="W21" s="1">
-        <v>0</v>
-      </c>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1">
+      <c r="W21" s="2">
+        <v>4</v>
+      </c>
+      <c r="X21" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y21" s="2">
+        <f t="shared" si="13"/>
+        <v>180</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:25">
+    <row r="22" customHeight="1" spans="3:28">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2762,22 +2978,22 @@
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G22" s="1">
         <v>17</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="6"/>
-        <v>2720</v>
+        <v>21760</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="7"/>
         <v>1088</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="8"/>
-        <v>54400</v>
+        <f t="shared" si="10"/>
+        <v>1088000</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" si="0"/>
@@ -2798,11 +3014,12 @@
       <c r="O22" s="1">
         <v>0</v>
       </c>
-      <c r="P22" s="4">
-        <v>0</v>
+      <c r="P22" s="2">
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
       <c r="Q22" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="R22" s="1">
         <f t="shared" si="4"/>
@@ -2819,18 +3036,28 @@
         <v>17</v>
       </c>
       <c r="V22" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>320</v>
       </c>
-      <c r="W22" s="1">
-        <v>0</v>
-      </c>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1">
+      <c r="W22" s="2">
+        <v>4</v>
+      </c>
+      <c r="X22" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y22" s="2">
+        <f t="shared" si="13"/>
+        <v>200</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:25">
+    <row r="23" customHeight="1" spans="3:28">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -2841,22 +3068,22 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G23" s="1">
         <v>18</v>
       </c>
       <c r="H23" s="1">
         <f t="shared" si="6"/>
-        <v>3060</v>
+        <v>24480</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="7"/>
         <v>1224</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="8"/>
-        <v>61200</v>
+        <f t="shared" si="10"/>
+        <v>1346400</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" si="0"/>
@@ -2877,11 +3104,12 @@
       <c r="O23" s="1">
         <v>0</v>
       </c>
-      <c r="P23" s="4">
-        <v>0</v>
+      <c r="P23" s="2">
+        <f t="shared" si="9"/>
+        <v>42</v>
       </c>
       <c r="Q23" s="4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R23" s="1">
         <f t="shared" si="4"/>
@@ -2898,18 +3126,28 @@
         <v>18</v>
       </c>
       <c r="V23" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>340</v>
       </c>
-      <c r="W23" s="1">
-        <v>0</v>
-      </c>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1">
+      <c r="W23" s="2">
+        <v>4</v>
+      </c>
+      <c r="X23" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y23" s="2">
+        <f t="shared" si="13"/>
+        <v>220</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:25">
+    <row r="24" customHeight="1" spans="3:28">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -2920,22 +3158,22 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G24" s="1">
         <v>19</v>
       </c>
       <c r="H24" s="1">
         <f t="shared" si="6"/>
-        <v>3420</v>
+        <v>27360</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" si="7"/>
         <v>1368</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="8"/>
-        <v>68400</v>
+        <f t="shared" si="10"/>
+        <v>1641600</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" si="0"/>
@@ -2956,11 +3194,12 @@
       <c r="O24" s="1">
         <v>0</v>
       </c>
-      <c r="P24" s="4">
-        <v>0</v>
+      <c r="P24" s="2">
+        <f t="shared" si="9"/>
+        <v>44</v>
       </c>
       <c r="Q24" s="4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R24" s="1">
         <f t="shared" si="4"/>
@@ -2977,18 +3216,28 @@
         <v>19</v>
       </c>
       <c r="V24" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>360</v>
       </c>
-      <c r="W24" s="1">
-        <v>0</v>
-      </c>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1">
+      <c r="W24" s="2">
+        <v>4</v>
+      </c>
+      <c r="X24" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y24" s="2">
+        <f t="shared" si="13"/>
+        <v>240</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="3:25">
+    <row r="25" customHeight="1" spans="3:28">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -2999,22 +3248,22 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G25" s="1">
         <v>20</v>
       </c>
       <c r="H25" s="1">
         <f t="shared" si="6"/>
-        <v>3800</v>
+        <v>30400</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="7"/>
         <v>1520</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="8"/>
-        <v>76000</v>
+        <f t="shared" si="10"/>
+        <v>1976000</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" si="0"/>
@@ -3035,11 +3284,12 @@
       <c r="O25" s="1">
         <v>0</v>
       </c>
-      <c r="P25" s="4">
-        <v>0</v>
+      <c r="P25" s="2">
+        <f t="shared" si="9"/>
+        <v>46</v>
       </c>
       <c r="Q25" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R25" s="1">
         <f t="shared" si="4"/>
@@ -3056,18 +3306,28 @@
         <v>20</v>
       </c>
       <c r="V25" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>380</v>
       </c>
-      <c r="W25" s="1">
-        <v>0</v>
-      </c>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1">
+      <c r="W25" s="2">
+        <v>4</v>
+      </c>
+      <c r="X25" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y25" s="2">
+        <f t="shared" si="13"/>
+        <v>260</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="3:25">
+    <row r="26" customHeight="1" spans="3:28">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -3078,22 +3338,22 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G26" s="1">
         <v>21</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="6"/>
-        <v>4200</v>
+        <v>42000</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="7"/>
-        <v>1680</v>
+        <v>2100</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="8"/>
-        <v>84000</v>
+        <f t="shared" si="10"/>
+        <v>2352000</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" si="0"/>
@@ -3114,11 +3374,12 @@
       <c r="O26" s="1">
         <v>0</v>
       </c>
-      <c r="P26" s="4">
-        <v>0</v>
+      <c r="P26" s="2">
+        <f t="shared" si="9"/>
+        <v>48</v>
       </c>
       <c r="Q26" s="4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R26" s="1">
         <f t="shared" si="4"/>
@@ -3135,18 +3396,28 @@
         <v>21</v>
       </c>
       <c r="V26" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>400</v>
       </c>
-      <c r="W26" s="1">
-        <v>0</v>
-      </c>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1">
+      <c r="W26" s="2">
+        <v>5</v>
+      </c>
+      <c r="X26" s="2">
+        <v>25</v>
+      </c>
+      <c r="Y26" s="2">
+        <f t="shared" si="13"/>
+        <v>280</v>
+      </c>
+      <c r="Z26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="3:25">
+    <row r="27" customHeight="1" spans="3:28">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -3157,22 +3428,22 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G27" s="1">
         <v>22</v>
       </c>
       <c r="H27" s="1">
         <f t="shared" si="6"/>
-        <v>4840</v>
+        <v>48400</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="7"/>
-        <v>1936</v>
+        <v>2420</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="8"/>
-        <v>96800</v>
+        <f t="shared" si="10"/>
+        <v>2904000</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" si="0"/>
@@ -3193,11 +3464,12 @@
       <c r="O27" s="1">
         <v>0</v>
       </c>
-      <c r="P27" s="4">
-        <v>0</v>
+      <c r="P27" s="2">
+        <f t="shared" si="9"/>
+        <v>50</v>
       </c>
       <c r="Q27" s="4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R27" s="1">
         <f t="shared" si="4"/>
@@ -3214,18 +3486,28 @@
         <v>22</v>
       </c>
       <c r="V27" s="2">
-        <f t="shared" ref="V27:V38" si="11">V26+40</f>
+        <f t="shared" ref="V27:V38" si="14">V26+40</f>
         <v>440</v>
       </c>
-      <c r="W27" s="1">
-        <v>0</v>
-      </c>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1">
+      <c r="W27" s="2">
+        <v>5</v>
+      </c>
+      <c r="X27" s="2">
+        <v>25</v>
+      </c>
+      <c r="Y27" s="2">
+        <f t="shared" si="13"/>
+        <v>300</v>
+      </c>
+      <c r="Z27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:25">
+    <row r="28" customHeight="1" spans="3:28">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -3236,22 +3518,22 @@
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G28" s="1">
         <v>23</v>
       </c>
       <c r="H28" s="1">
         <f t="shared" si="6"/>
-        <v>5520</v>
+        <v>55200</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="7"/>
-        <v>2208</v>
+        <v>2760</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="8"/>
-        <v>110400</v>
+        <f t="shared" si="10"/>
+        <v>3643200</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="0"/>
@@ -3272,11 +3554,12 @@
       <c r="O28" s="1">
         <v>0</v>
       </c>
-      <c r="P28" s="4">
-        <v>0</v>
+      <c r="P28" s="2">
+        <f>P27+5</f>
+        <v>55</v>
       </c>
       <c r="Q28" s="4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R28" s="1">
         <f t="shared" si="4"/>
@@ -3293,18 +3576,28 @@
         <v>23</v>
       </c>
       <c r="V28" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>480</v>
       </c>
-      <c r="W28" s="1">
-        <v>0</v>
-      </c>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1">
+      <c r="W28" s="2">
+        <v>5</v>
+      </c>
+      <c r="X28" s="2">
+        <v>25</v>
+      </c>
+      <c r="Y28" s="2">
+        <f t="shared" ref="Y28:Y45" si="15">Y27+30</f>
+        <v>330</v>
+      </c>
+      <c r="Z28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:25">
+    <row r="29" customHeight="1" spans="3:28">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -3315,22 +3608,22 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G29" s="1">
         <v>24</v>
       </c>
       <c r="H29" s="1">
         <f t="shared" si="6"/>
-        <v>6240</v>
+        <v>62400</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="7"/>
-        <v>2496</v>
+        <v>3120</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="8"/>
-        <v>124800</v>
+        <f t="shared" si="10"/>
+        <v>4492800</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" si="0"/>
@@ -3351,11 +3644,12 @@
       <c r="O29" s="1">
         <v>0</v>
       </c>
-      <c r="P29" s="4">
-        <v>0</v>
+      <c r="P29" s="2">
+        <f t="shared" ref="P29:P45" si="16">P28+5</f>
+        <v>60</v>
       </c>
       <c r="Q29" s="4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R29" s="1">
         <f t="shared" si="4"/>
@@ -3372,18 +3666,28 @@
         <v>24</v>
       </c>
       <c r="V29" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>520</v>
       </c>
-      <c r="W29" s="1">
-        <v>0</v>
-      </c>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1">
+      <c r="W29" s="2">
+        <v>5</v>
+      </c>
+      <c r="X29" s="2">
+        <v>25</v>
+      </c>
+      <c r="Y29" s="2">
+        <f t="shared" si="15"/>
+        <v>360</v>
+      </c>
+      <c r="Z29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:25">
+    <row r="30" customHeight="1" spans="3:28">
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -3394,22 +3698,22 @@
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G30" s="1">
         <v>25</v>
       </c>
       <c r="H30" s="1">
         <f t="shared" si="6"/>
-        <v>7000</v>
+        <v>70000</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="7"/>
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="8"/>
-        <v>140000</v>
+        <f t="shared" si="10"/>
+        <v>5460000</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="0"/>
@@ -3430,11 +3734,12 @@
       <c r="O30" s="1">
         <v>0</v>
       </c>
-      <c r="P30" s="4">
-        <v>0</v>
+      <c r="P30" s="2">
+        <f t="shared" si="16"/>
+        <v>65</v>
       </c>
       <c r="Q30" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R30" s="1">
         <f t="shared" si="4"/>
@@ -3451,18 +3756,28 @@
         <v>25</v>
       </c>
       <c r="V30" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>560</v>
       </c>
-      <c r="W30" s="1">
-        <v>0</v>
-      </c>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1">
+      <c r="W30" s="2">
+        <v>5</v>
+      </c>
+      <c r="X30" s="2">
+        <v>25</v>
+      </c>
+      <c r="Y30" s="2">
+        <f t="shared" si="15"/>
+        <v>390</v>
+      </c>
+      <c r="Z30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:25">
+    <row r="31" customHeight="1" spans="3:28">
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -3473,22 +3788,22 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G31" s="1">
         <v>26</v>
       </c>
       <c r="H31" s="1">
         <f t="shared" si="6"/>
-        <v>7800</v>
+        <v>93600</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" si="7"/>
-        <v>3120</v>
+        <v>4680</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="8"/>
-        <v>156000</v>
+        <f t="shared" si="10"/>
+        <v>6552000</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" si="0"/>
@@ -3509,11 +3824,12 @@
       <c r="O31" s="1">
         <v>0</v>
       </c>
-      <c r="P31" s="4">
-        <v>0</v>
+      <c r="P31" s="2">
+        <f t="shared" si="16"/>
+        <v>70</v>
       </c>
       <c r="Q31" s="4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R31" s="1">
         <f t="shared" si="4"/>
@@ -3530,18 +3846,28 @@
         <v>26</v>
       </c>
       <c r="V31" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>600</v>
       </c>
-      <c r="W31" s="1">
-        <v>0</v>
-      </c>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1">
+      <c r="W31" s="2">
+        <v>6</v>
+      </c>
+      <c r="X31" s="2">
+        <v>30</v>
+      </c>
+      <c r="Y31" s="2">
+        <f t="shared" si="15"/>
+        <v>420</v>
+      </c>
+      <c r="Z31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:25">
+    <row r="32" customHeight="1" spans="3:28">
       <c r="C32" s="1">
         <v>27</v>
       </c>
@@ -3552,22 +3878,22 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G32" s="1">
         <v>27</v>
       </c>
       <c r="H32" s="1">
         <f t="shared" si="6"/>
-        <v>8640</v>
+        <v>103680</v>
       </c>
       <c r="I32" s="1">
         <f t="shared" si="7"/>
-        <v>3456</v>
+        <v>5184</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="8"/>
-        <v>172800</v>
+        <f t="shared" si="10"/>
+        <v>7776000</v>
       </c>
       <c r="K32" s="1">
         <f t="shared" si="0"/>
@@ -3588,11 +3914,12 @@
       <c r="O32" s="1">
         <v>0</v>
       </c>
-      <c r="P32" s="4">
-        <v>0</v>
+      <c r="P32" s="2">
+        <f t="shared" si="16"/>
+        <v>75</v>
       </c>
       <c r="Q32" s="4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R32" s="1">
         <f t="shared" si="4"/>
@@ -3609,18 +3936,28 @@
         <v>27</v>
       </c>
       <c r="V32" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>640</v>
       </c>
-      <c r="W32" s="1">
-        <v>0</v>
-      </c>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1">
+      <c r="W32" s="2">
+        <v>6</v>
+      </c>
+      <c r="X32" s="2">
+        <v>30</v>
+      </c>
+      <c r="Y32" s="2">
+        <f t="shared" si="15"/>
+        <v>450</v>
+      </c>
+      <c r="Z32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:25">
+    <row r="33" customHeight="1" spans="1:28">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -3631,22 +3968,22 @@
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G33" s="1">
         <v>28</v>
       </c>
       <c r="H33" s="1">
         <f t="shared" si="6"/>
-        <v>9520</v>
+        <v>114240</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="7"/>
-        <v>3808</v>
+        <v>5712</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" si="8"/>
-        <v>190400</v>
+        <f t="shared" si="10"/>
+        <v>9139200</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" si="0"/>
@@ -3667,11 +4004,12 @@
       <c r="O33" s="1">
         <v>0</v>
       </c>
-      <c r="P33" s="4">
-        <v>0</v>
+      <c r="P33" s="2">
+        <f t="shared" si="16"/>
+        <v>80</v>
       </c>
       <c r="Q33" s="4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R33" s="1">
         <f t="shared" si="4"/>
@@ -3688,18 +4026,28 @@
         <v>28</v>
       </c>
       <c r="V33" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>680</v>
       </c>
-      <c r="W33" s="1">
-        <v>0</v>
-      </c>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1">
+      <c r="W33" s="2">
+        <v>6</v>
+      </c>
+      <c r="X33" s="2">
+        <v>30</v>
+      </c>
+      <c r="Y33" s="2">
+        <f t="shared" si="15"/>
+        <v>480</v>
+      </c>
+      <c r="Z33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:25">
+    <row r="34" customHeight="1" spans="1:28">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -3710,22 +4058,22 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G34" s="1">
         <v>29</v>
       </c>
       <c r="H34" s="1">
         <f t="shared" si="6"/>
-        <v>10440</v>
+        <v>125280</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="7"/>
-        <v>4176</v>
+        <v>6264</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="8"/>
-        <v>208800</v>
+        <f t="shared" si="10"/>
+        <v>10648800</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" si="0"/>
@@ -3746,11 +4094,12 @@
       <c r="O34" s="1">
         <v>0</v>
       </c>
-      <c r="P34" s="4">
-        <v>0</v>
+      <c r="P34" s="2">
+        <f t="shared" si="16"/>
+        <v>85</v>
       </c>
       <c r="Q34" s="4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R34" s="1">
         <f t="shared" si="4"/>
@@ -3767,18 +4116,28 @@
         <v>29</v>
       </c>
       <c r="V34" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>720</v>
       </c>
-      <c r="W34" s="1">
-        <v>0</v>
-      </c>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1">
+      <c r="W34" s="2">
+        <v>6</v>
+      </c>
+      <c r="X34" s="2">
+        <v>30</v>
+      </c>
+      <c r="Y34" s="2">
+        <f t="shared" si="15"/>
+        <v>510</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:25">
+    <row r="35" customHeight="1" spans="1:28">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -3789,22 +4148,22 @@
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G35" s="1">
         <v>30</v>
       </c>
       <c r="H35" s="1">
         <f t="shared" si="6"/>
-        <v>11400</v>
+        <v>136800</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" si="7"/>
-        <v>4560</v>
+        <v>6840</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="8"/>
-        <v>228000</v>
+        <f t="shared" si="10"/>
+        <v>12312000</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" si="0"/>
@@ -3825,11 +4184,12 @@
       <c r="O35" s="1">
         <v>0</v>
       </c>
-      <c r="P35" s="4">
-        <v>0</v>
+      <c r="P35" s="2">
+        <f t="shared" si="16"/>
+        <v>90</v>
       </c>
       <c r="Q35" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R35" s="1">
         <f t="shared" si="4"/>
@@ -3846,18 +4206,28 @@
         <v>30</v>
       </c>
       <c r="V35" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>760</v>
       </c>
-      <c r="W35" s="1">
-        <v>0</v>
-      </c>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1">
+      <c r="W35" s="2">
+        <v>6</v>
+      </c>
+      <c r="X35" s="2">
+        <v>30</v>
+      </c>
+      <c r="Y35" s="2">
+        <f t="shared" si="15"/>
+        <v>540</v>
+      </c>
+      <c r="Z35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:25">
+    <row r="36" customHeight="1" spans="1:28">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -3868,22 +4238,22 @@
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G36" s="1">
         <v>31</v>
       </c>
       <c r="H36" s="1">
         <f t="shared" si="6"/>
-        <v>12400</v>
+        <v>173600</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="7"/>
-        <v>4960</v>
+        <v>8680</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="8"/>
-        <v>248000</v>
+        <f t="shared" si="10"/>
+        <v>14136000</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" si="0"/>
@@ -3904,11 +4274,12 @@
       <c r="O36" s="1">
         <v>0</v>
       </c>
-      <c r="P36" s="4">
-        <v>0</v>
+      <c r="P36" s="2">
+        <f t="shared" si="16"/>
+        <v>95</v>
       </c>
       <c r="Q36" s="4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R36" s="1">
         <f t="shared" si="4"/>
@@ -3925,18 +4296,28 @@
         <v>31</v>
       </c>
       <c r="V36" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>800</v>
       </c>
-      <c r="W36" s="1">
-        <v>0</v>
-      </c>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1">
+      <c r="W36" s="2">
+        <v>7</v>
+      </c>
+      <c r="X36" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y36" s="2">
+        <f t="shared" si="15"/>
+        <v>570</v>
+      </c>
+      <c r="Z36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:25">
+    <row r="37" customHeight="1" spans="1:28">
       <c r="C37" s="1">
         <v>32</v>
       </c>
@@ -3947,22 +4328,22 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G37" s="1">
         <v>32</v>
       </c>
       <c r="H37" s="1">
         <f t="shared" si="6"/>
-        <v>14080</v>
+        <v>197120</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="7"/>
-        <v>5632</v>
+        <v>9856</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="8"/>
-        <v>281600</v>
+        <f t="shared" si="10"/>
+        <v>16896000</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" si="0"/>
@@ -3983,11 +4364,12 @@
       <c r="O37" s="1">
         <v>0</v>
       </c>
-      <c r="P37" s="4">
-        <v>0</v>
+      <c r="P37" s="2">
+        <f t="shared" si="16"/>
+        <v>100</v>
       </c>
       <c r="Q37" s="4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R37" s="1">
         <f t="shared" si="4"/>
@@ -4004,18 +4386,28 @@
         <v>32</v>
       </c>
       <c r="V37" s="2">
-        <f t="shared" ref="V37:V45" si="12">V36+80</f>
+        <f t="shared" ref="V37:V45" si="17">V36+80</f>
         <v>880</v>
       </c>
-      <c r="W37" s="1">
-        <v>0</v>
-      </c>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1">
+      <c r="W37" s="2">
+        <v>7</v>
+      </c>
+      <c r="X37" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y37" s="2">
+        <f t="shared" si="15"/>
+        <v>600</v>
+      </c>
+      <c r="Z37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:25">
+    <row r="38" customHeight="1" spans="1:28">
       <c r="C38" s="1">
         <v>33</v>
       </c>
@@ -4026,22 +4418,22 @@
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G38" s="1">
         <v>33</v>
       </c>
       <c r="H38" s="1">
         <f t="shared" si="6"/>
-        <v>15840</v>
+        <v>221760</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="7"/>
-        <v>6336</v>
+        <v>11088</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="8"/>
-        <v>316800</v>
+        <f t="shared" si="10"/>
+        <v>20908800</v>
       </c>
       <c r="K38" s="1">
         <f t="shared" si="0"/>
@@ -4062,11 +4454,12 @@
       <c r="O38" s="1">
         <v>0</v>
       </c>
-      <c r="P38" s="4">
-        <v>0</v>
+      <c r="P38" s="2">
+        <f t="shared" si="16"/>
+        <v>105</v>
       </c>
       <c r="Q38" s="4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R38" s="1">
         <f t="shared" si="4"/>
@@ -4083,18 +4476,28 @@
         <v>33</v>
       </c>
       <c r="V38" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>960</v>
       </c>
-      <c r="W38" s="1">
-        <v>0</v>
-      </c>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1">
+      <c r="W38" s="2">
+        <v>7</v>
+      </c>
+      <c r="X38" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y38" s="2">
+        <f t="shared" ref="Y38:Y45" si="18">Y37+60</f>
+        <v>660</v>
+      </c>
+      <c r="Z38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:25">
+    <row r="39" customHeight="1" spans="1:28">
       <c r="C39" s="1">
         <v>34</v>
       </c>
@@ -4105,22 +4508,22 @@
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G39" s="1">
         <v>34</v>
       </c>
       <c r="H39" s="1">
         <f t="shared" si="6"/>
-        <v>17680</v>
+        <v>247520</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="7"/>
-        <v>7072</v>
+        <v>12376</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="8"/>
-        <v>353600</v>
+        <f t="shared" si="10"/>
+        <v>25459200</v>
       </c>
       <c r="K39" s="1">
         <f t="shared" si="0"/>
@@ -4141,11 +4544,12 @@
       <c r="O39" s="1">
         <v>0</v>
       </c>
-      <c r="P39" s="4">
-        <v>0</v>
+      <c r="P39" s="2">
+        <f t="shared" si="16"/>
+        <v>110</v>
       </c>
       <c r="Q39" s="4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R39" s="1">
         <f t="shared" si="4"/>
@@ -4162,18 +4566,28 @@
         <v>34</v>
       </c>
       <c r="V39" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>1040</v>
       </c>
-      <c r="W39" s="1">
-        <v>0</v>
-      </c>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1">
+      <c r="W39" s="2">
+        <v>7</v>
+      </c>
+      <c r="X39" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y39" s="2">
+        <f t="shared" si="18"/>
+        <v>720</v>
+      </c>
+      <c r="Z39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:25">
+    <row r="40" customHeight="1" spans="1:28">
       <c r="C40" s="1">
         <v>35</v>
       </c>
@@ -4184,22 +4598,22 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G40" s="1">
         <v>35</v>
       </c>
       <c r="H40" s="1">
         <f t="shared" si="6"/>
-        <v>19600</v>
+        <v>274400</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="7"/>
-        <v>7840</v>
+        <v>13720</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="8"/>
-        <v>392000</v>
+        <f t="shared" si="10"/>
+        <v>30576000</v>
       </c>
       <c r="K40" s="1">
         <f t="shared" si="0"/>
@@ -4220,11 +4634,12 @@
       <c r="O40" s="1">
         <v>0</v>
       </c>
-      <c r="P40" s="4">
-        <v>0</v>
+      <c r="P40" s="2">
+        <f t="shared" si="16"/>
+        <v>115</v>
       </c>
       <c r="Q40" s="4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R40" s="1">
         <f t="shared" si="4"/>
@@ -4241,18 +4656,28 @@
         <v>35</v>
       </c>
       <c r="V40" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>1120</v>
       </c>
-      <c r="W40" s="1">
-        <v>0</v>
-      </c>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1">
+      <c r="W40" s="2">
+        <v>7</v>
+      </c>
+      <c r="X40" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y40" s="2">
+        <f t="shared" si="18"/>
+        <v>780</v>
+      </c>
+      <c r="Z40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A41" s="2"/>
       <c r="C41" s="1">
         <v>36</v>
@@ -4264,22 +4689,22 @@
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="6"/>
-        <v>21600</v>
+        <v>345600</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="7"/>
-        <v>8640</v>
+        <v>17280</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="8"/>
-        <v>432000</v>
+        <f t="shared" si="10"/>
+        <v>36288000</v>
       </c>
       <c r="K41" s="1">
         <f t="shared" si="0"/>
@@ -4300,11 +4725,12 @@
       <c r="O41" s="1">
         <v>0</v>
       </c>
-      <c r="P41" s="4">
-        <v>0</v>
+      <c r="P41" s="2">
+        <f t="shared" si="16"/>
+        <v>120</v>
       </c>
       <c r="Q41" s="4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R41" s="1">
         <f t="shared" si="4"/>
@@ -4321,17 +4747,27 @@
         <v>36</v>
       </c>
       <c r="V41" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>1200</v>
       </c>
-      <c r="W41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="1">
+      <c r="W41" s="2">
+        <v>8</v>
+      </c>
+      <c r="X41" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y41" s="2">
+        <f t="shared" si="18"/>
+        <v>840</v>
+      </c>
+      <c r="Z41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A42" s="2"/>
       <c r="C42" s="1">
         <v>37</v>
@@ -4343,22 +4779,22 @@
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G42" s="1">
         <v>2</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="6"/>
-        <v>23680</v>
+        <v>378880</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="7"/>
-        <v>9472</v>
+        <v>18944</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="8"/>
-        <v>473600</v>
+        <f t="shared" si="10"/>
+        <v>42624000</v>
       </c>
       <c r="K42" s="1">
         <f t="shared" si="0"/>
@@ -4379,11 +4815,12 @@
       <c r="O42" s="1">
         <v>0</v>
       </c>
-      <c r="P42" s="4">
-        <v>0</v>
+      <c r="P42" s="2">
+        <f t="shared" si="16"/>
+        <v>125</v>
       </c>
       <c r="Q42" s="4">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="R42" s="1">
         <f t="shared" si="4"/>
@@ -4400,17 +4837,27 @@
         <v>37</v>
       </c>
       <c r="V42" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>1280</v>
       </c>
-      <c r="W42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="1">
+      <c r="W42" s="2">
+        <v>8</v>
+      </c>
+      <c r="X42" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y42" s="2">
+        <f t="shared" si="18"/>
+        <v>900</v>
+      </c>
+      <c r="Z42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A43" s="2"/>
       <c r="C43" s="1">
         <v>38</v>
@@ -4422,22 +4869,22 @@
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G43" s="1">
         <v>3</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="6"/>
-        <v>25840</v>
+        <v>413440</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="7"/>
-        <v>10336</v>
+        <v>20672</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="8"/>
-        <v>516800</v>
+        <f t="shared" si="10"/>
+        <v>49612800</v>
       </c>
       <c r="K43" s="1">
         <f t="shared" si="0"/>
@@ -4458,11 +4905,12 @@
       <c r="O43" s="1">
         <v>0</v>
       </c>
-      <c r="P43" s="4">
-        <v>0</v>
+      <c r="P43" s="2">
+        <f t="shared" si="16"/>
+        <v>130</v>
       </c>
       <c r="Q43" s="4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R43" s="1">
         <f t="shared" si="4"/>
@@ -4479,17 +4927,27 @@
         <v>38</v>
       </c>
       <c r="V43" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>1360</v>
       </c>
-      <c r="W43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="1">
+      <c r="W43" s="2">
+        <v>8</v>
+      </c>
+      <c r="X43" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y43" s="2">
+        <f t="shared" si="18"/>
+        <v>960</v>
+      </c>
+      <c r="Z43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A44" s="2"/>
       <c r="C44" s="1">
         <v>39</v>
@@ -4501,22 +4959,22 @@
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G44" s="1">
         <v>4</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="6"/>
-        <v>28080</v>
+        <v>449280</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="7"/>
-        <v>11232</v>
+        <v>22464</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="8"/>
-        <v>561600</v>
+        <f t="shared" si="10"/>
+        <v>57283200</v>
       </c>
       <c r="K44" s="1">
         <f t="shared" si="0"/>
@@ -4537,11 +4995,12 @@
       <c r="O44" s="1">
         <v>0</v>
       </c>
-      <c r="P44" s="4">
-        <v>0</v>
+      <c r="P44" s="2">
+        <f t="shared" si="16"/>
+        <v>135</v>
       </c>
       <c r="Q44" s="4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1">
         <f t="shared" si="4"/>
@@ -4558,17 +5017,27 @@
         <v>39</v>
       </c>
       <c r="V44" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>1440</v>
       </c>
-      <c r="W44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="1">
+      <c r="W44" s="2">
+        <v>8</v>
+      </c>
+      <c r="X44" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y44" s="2">
+        <f t="shared" si="18"/>
+        <v>1020</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A45" s="2"/>
       <c r="C45" s="1">
         <v>40</v>
@@ -4580,22 +5049,22 @@
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G45" s="1">
         <v>5</v>
       </c>
       <c r="H45" s="1">
         <f t="shared" si="6"/>
-        <v>30400</v>
+        <v>486400</v>
       </c>
       <c r="I45" s="1">
         <f t="shared" si="7"/>
-        <v>12160</v>
+        <v>24320</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="8"/>
-        <v>608000</v>
+        <f t="shared" si="10"/>
+        <v>65664000</v>
       </c>
       <c r="K45" s="1">
         <f t="shared" si="0"/>
@@ -4616,11 +5085,12 @@
       <c r="O45" s="1">
         <v>0</v>
       </c>
-      <c r="P45" s="4">
-        <v>0</v>
+      <c r="P45" s="2">
+        <f t="shared" si="16"/>
+        <v>140</v>
       </c>
       <c r="Q45" s="4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R45" s="1">
         <f t="shared" si="4"/>
@@ -4637,17 +5107,27 @@
         <v>40</v>
       </c>
       <c r="V45" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="17"/>
         <v>1520</v>
       </c>
-      <c r="W45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="1">
+      <c r="W45" s="2">
+        <v>8</v>
+      </c>
+      <c r="X45" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y45" s="2">
+        <f t="shared" si="18"/>
+        <v>1080</v>
+      </c>
+      <c r="Z45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:25">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A46" s="2"/>
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
@@ -4656,10 +5136,13 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="2"/>
+      <c r="W46" s="2"/>
+      <c r="X46" s="2"/>
+      <c r="Y46" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3 E3 F3 G3 H3:J3 G4 G5 C4:F5 K3:Q5 W3:Y5 H4:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:Q5 Z3:AB5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -47,7 +47,7 @@
     <t>ModelId</t>
   </si>
   <si>
-    <t>Attr</t>
+    <t>Atk</t>
   </si>
   <si>
     <t>Def</t>
@@ -68,13 +68,25 @@
     <t>CritDamage</t>
   </si>
   <si>
+    <t>CritRateResist</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Miss</t>
+  </si>
+  <si>
     <t>Speed</t>
   </si>
   <si>
-    <t>Miss</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>Lucky</t>
+  </si>
+  <si>
+    <t>Curse</t>
   </si>
   <si>
     <t>Exp</t>
@@ -1199,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB46"/>
+  <dimension ref="A1:AF46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1216,21 +1228,24 @@
     <col min="12" max="12" width="10.3333333333333" style="2" customWidth="1"/>
     <col min="13" max="13" width="9.91666666666667" style="2" customWidth="1"/>
     <col min="14" max="15" width="8.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="9.16666666666667" style="2" customWidth="1"/>
-    <col min="17" max="17" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="18" max="18" width="11.8333333333333" style="2" customWidth="1"/>
-    <col min="19" max="19" width="10.3333333333333" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.33333333333333" style="1" customWidth="1"/>
-    <col min="21" max="21" width="7.25" style="1" customWidth="1"/>
-    <col min="22" max="24" width="7.16666666666667" style="2" customWidth="1"/>
-    <col min="25" max="25" width="8.41666666666667" style="2" customWidth="1"/>
-    <col min="26" max="26" width="4.33333333333333" style="2" customWidth="1"/>
-    <col min="27" max="27" width="3.75" style="2" customWidth="1"/>
-    <col min="28" max="28" width="3" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="9" style="2"/>
+    <col min="16" max="16" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.16666666666667" style="2" customWidth="1"/>
+    <col min="18" max="19" width="8.75" style="2" customWidth="1"/>
+    <col min="20" max="20" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="21" max="21" width="8.33333333333333" style="2" customWidth="1"/>
+    <col min="22" max="22" width="9.91666666666667" style="2" customWidth="1"/>
+    <col min="23" max="23" width="10.3333333333333" style="2" customWidth="1"/>
+    <col min="24" max="24" width="8.33333333333333" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.25" style="1" customWidth="1"/>
+    <col min="26" max="28" width="7.16666666666667" style="2" customWidth="1"/>
+    <col min="29" max="29" width="8.41666666666667" style="2" customWidth="1"/>
+    <col min="30" max="30" width="4.33333333333333" style="2" customWidth="1"/>
+    <col min="31" max="31" width="3.75" style="2" customWidth="1"/>
+    <col min="32" max="32" width="3" style="2" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="2"/>
@@ -1245,22 +1260,14 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
-      <c r="T1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y1" s="2" t="s">
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Z1" s="2" t="s">
@@ -1272,8 +1279,20 @@
       <c r="AB1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="AC1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="2"/>
@@ -1288,22 +1307,14 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
-      <c r="T2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="2" t="s">
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Z2" s="2" t="s">
@@ -1315,8 +1326,20 @@
       <c r="AB2" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="AC2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1370,39 +1393,51 @@
       <c r="S3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="T3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AA3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AB3" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="AC3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1452,89 +1487,113 @@
       <c r="S4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>26</v>
+      <c r="T4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB5" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="6" ht="14" spans="1:28">
+    <row r="6" ht="14" spans="1:32">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1545,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1554,25 +1613,26 @@
         <v>5</v>
       </c>
       <c r="I6" s="1">
+        <f t="shared" ref="I6:I45" si="0">AB6*2</f>
         <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>100</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" ref="K6:K45" si="0">U6*5</f>
+        <f t="shared" ref="K6:K45" si="1">Y6*5</f>
         <v>5</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L45" si="1">U6*3</f>
+        <f t="shared" ref="L6:L45" si="2">Y6*3</f>
         <v>3</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M45" si="2">U6*2</f>
+        <f t="shared" ref="M6:M45" si="3">Y6*2</f>
         <v>2</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" ref="N6:N45" si="3">U6*4</f>
+        <f t="shared" ref="N6:N45" si="4">Y6*4</f>
         <v>4</v>
       </c>
       <c r="O6" s="1">
@@ -1585,40 +1645,52 @@
         <v>1</v>
       </c>
       <c r="R6" s="1">
-        <f t="shared" ref="R6:R46" si="4">T6*10</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" ref="V6:V46" si="5">X6*10</f>
         <v>100</v>
       </c>
-      <c r="S6" s="1">
-        <f t="shared" ref="S6:S46" si="5">T6*10</f>
+      <c r="W6" s="1">
+        <f t="shared" ref="W6:W46" si="6">X6*10</f>
         <v>100</v>
       </c>
-      <c r="T6" s="1">
+      <c r="X6" s="1">
         <v>10</v>
       </c>
-      <c r="U6" s="1">
+      <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="V6" s="2">
+      <c r="Z6" s="2">
         <v>100</v>
       </c>
-      <c r="W6" s="2">
+      <c r="AA6" s="2">
         <v>1</v>
       </c>
-      <c r="X6" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="2">
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2">
         <v>10</v>
       </c>
-      <c r="Z6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1">
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:28">
+    <row r="7" customHeight="1" spans="1:32">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1629,265 +1701,301 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:H45" si="6">U7*V7*W7</f>
-        <v>220</v>
+        <f t="shared" ref="H7:H45" si="7">Y7*Z7*AA7/10</f>
+        <v>22</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" ref="I7:I45" si="7">U7*V7*X7/100</f>
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
+        <f>Y7*Z7*AC7</f>
+        <v>3300</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="M7" s="1">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="N7" s="1">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>10</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" si="6"/>
+        <v>110</v>
+      </c>
+      <c r="X7" s="1">
         <v>11</v>
       </c>
-      <c r="J7" s="1">
-        <f>U7*V7*Y7</f>
-        <v>3300</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="Y7" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="2">
+        <f t="shared" ref="Z7:Z17" si="8">Z6+10</f>
+        <v>110</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="2">
+        <f>AC6+5</f>
+        <v>15</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:32">
+      <c r="C8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="I8" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="L7" s="1">
+        <v>4</v>
+      </c>
+      <c r="J8" s="1">
+        <f>Y8*Z8*AC8</f>
+        <v>7200</v>
+      </c>
+      <c r="K8" s="1">
         <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="M8" s="1">
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N8" s="1">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="O8" s="1">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="2">
+        <f t="shared" ref="Q8:Q45" si="9">Q7+2</f>
+        <v>12</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0</v>
+      </c>
+      <c r="V8" s="1">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" si="6"/>
+        <v>120</v>
+      </c>
+      <c r="X8" s="1">
+        <v>12</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="2">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="2">
+        <f>AC7+5</f>
+        <v>20</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:32">
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="7"/>
+        <v>52</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" ref="J7:J45" si="10">Y9*Z9*AC9</f>
+        <v>13000</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L9" s="1">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N7" s="1">
+        <v>12</v>
+      </c>
+      <c r="M9" s="1">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>2</v>
-      </c>
-      <c r="R7" s="1">
+      <c r="N9" s="1">
         <f t="shared" si="4"/>
-        <v>110</v>
-      </c>
-      <c r="S7" s="1">
-        <f t="shared" si="5"/>
-        <v>110</v>
-      </c>
-      <c r="T7" s="1">
-        <v>11</v>
-      </c>
-      <c r="U7" s="1">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2">
-        <f t="shared" ref="V7:V17" si="8">V6+10</f>
-        <v>110</v>
-      </c>
-      <c r="W7" s="2">
-        <v>1</v>
-      </c>
-      <c r="X7" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y7" s="2">
-        <f>Y6+5</f>
-        <v>15</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:28">
-      <c r="C8" s="1">
+        <v>16</v>
+      </c>
+      <c r="O9" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="1">
-        <v>3</v>
-      </c>
-      <c r="H8" s="1">
-        <f t="shared" si="6"/>
-        <v>360</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="7"/>
-        <v>18</v>
-      </c>
-      <c r="J8" s="1">
-        <f>U8*V8*Y8</f>
-        <v>7200</v>
-      </c>
-      <c r="K8" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="M8" s="1">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="N8" s="1">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2">
-        <f t="shared" ref="P8:P45" si="9">P7+2</f>
-        <v>12</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>3</v>
-      </c>
-      <c r="R8" s="1">
-        <f t="shared" si="4"/>
-        <v>120</v>
-      </c>
-      <c r="S8" s="1">
-        <f t="shared" si="5"/>
-        <v>120</v>
-      </c>
-      <c r="T8" s="1">
-        <v>12</v>
-      </c>
-      <c r="U8" s="1">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2">
-        <f t="shared" si="8"/>
-        <v>120</v>
-      </c>
-      <c r="W8" s="2">
-        <v>1</v>
-      </c>
-      <c r="X8" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y8" s="2">
-        <f>Y7+5</f>
-        <v>20</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:28">
-      <c r="C9" s="1">
+      <c r="P9" s="4">
         <v>4</v>
       </c>
-      <c r="D9" s="1">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="1">
-        <v>4</v>
-      </c>
-      <c r="H9" s="1">
-        <f t="shared" si="6"/>
-        <v>520</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="7"/>
-        <v>26</v>
-      </c>
-      <c r="J9" s="1">
-        <f t="shared" ref="J7:J45" si="10">U9*V9*Y9</f>
-        <v>13000</v>
-      </c>
-      <c r="K9" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="M9" s="1">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="N9" s="1">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2">
+      <c r="Q9" s="2">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="Q9" s="4">
-        <v>4</v>
-      </c>
       <c r="R9" s="1">
-        <f t="shared" si="4"/>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
         <f t="shared" si="5"/>
         <v>130</v>
       </c>
-      <c r="T9" s="1">
+      <c r="W9" s="1">
+        <f t="shared" si="6"/>
+        <v>130</v>
+      </c>
+      <c r="X9" s="1">
         <v>13</v>
       </c>
-      <c r="U9" s="1">
+      <c r="Y9" s="1">
         <v>4</v>
       </c>
-      <c r="V9" s="2">
+      <c r="Z9" s="2">
         <f t="shared" si="8"/>
         <v>130</v>
       </c>
-      <c r="W9" s="2">
+      <c r="AA9" s="2">
         <v>1</v>
       </c>
-      <c r="X9" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="2">
-        <f>Y8+5</f>
+      <c r="AB9" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="2">
+        <f>AC8+5</f>
         <v>25</v>
       </c>
-      <c r="Z9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1">
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:28">
+    <row r="10" customHeight="1" spans="1:32">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1898,86 +2006,98 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
       </c>
       <c r="H10" s="1">
-        <f t="shared" si="6"/>
-        <v>700</v>
+        <f t="shared" si="7"/>
+        <v>70</v>
       </c>
       <c r="I10" s="1">
-        <f t="shared" si="7"/>
-        <v>35</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" si="10"/>
         <v>21000</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="N10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2">
+        <v>4</v>
+      </c>
+      <c r="P10" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="2">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="Q10" s="4">
-        <v>5</v>
-      </c>
       <c r="R10" s="1">
-        <f t="shared" si="4"/>
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
         <f t="shared" si="5"/>
         <v>140</v>
       </c>
-      <c r="T10" s="1">
+      <c r="W10" s="1">
+        <f t="shared" si="6"/>
+        <v>140</v>
+      </c>
+      <c r="X10" s="1">
         <v>14</v>
       </c>
-      <c r="U10" s="1">
+      <c r="Y10" s="1">
         <v>5</v>
       </c>
-      <c r="V10" s="2">
+      <c r="Z10" s="2">
         <f t="shared" si="8"/>
         <v>140</v>
       </c>
-      <c r="W10" s="2">
+      <c r="AA10" s="2">
         <v>1</v>
       </c>
-      <c r="X10" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="2">
-        <f>Y9+5</f>
+      <c r="AB10" s="2">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="2">
+        <f>AC9+5</f>
         <v>30</v>
       </c>
-      <c r="Z10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1">
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:28">
+    <row r="11" customHeight="1" spans="1:32">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1988,86 +2108,98 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <v>6</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" si="6"/>
-        <v>1800</v>
+        <f t="shared" si="7"/>
+        <v>180</v>
       </c>
       <c r="I11" s="1">
-        <f t="shared" si="7"/>
-        <v>90</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" si="10"/>
         <v>36000</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="N11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="O11" s="1">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2">
+        <v>5</v>
+      </c>
+      <c r="P11" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="2">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="Q11" s="4">
-        <v>6</v>
-      </c>
       <c r="R11" s="1">
-        <f t="shared" si="4"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="4">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1">
         <f t="shared" si="5"/>
         <v>150</v>
       </c>
-      <c r="T11" s="1">
+      <c r="W11" s="1">
+        <f t="shared" si="6"/>
+        <v>150</v>
+      </c>
+      <c r="X11" s="1">
         <v>15</v>
       </c>
-      <c r="U11" s="1">
+      <c r="Y11" s="1">
         <v>6</v>
       </c>
-      <c r="V11" s="2">
+      <c r="Z11" s="2">
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="W11" s="2">
+      <c r="AA11" s="2">
         <v>2</v>
       </c>
-      <c r="X11" s="2">
-        <v>10</v>
-      </c>
-      <c r="Y11" s="2">
-        <f t="shared" ref="Y11:Y20" si="11">Y10+10</f>
+      <c r="AB11" s="2">
+        <v>5</v>
+      </c>
+      <c r="AC11" s="2">
+        <f t="shared" ref="AC11:AC20" si="11">AC10+10</f>
         <v>40</v>
       </c>
-      <c r="Z11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1">
+      <c r="AD11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:28">
+    <row r="12" customHeight="1" spans="1:32">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2078,86 +2210,98 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G12" s="1">
         <v>7</v>
       </c>
       <c r="H12" s="1">
-        <f t="shared" si="6"/>
-        <v>2240</v>
+        <f t="shared" si="7"/>
+        <v>224</v>
       </c>
       <c r="I12" s="1">
-        <f t="shared" si="7"/>
-        <v>112</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="10"/>
         <v>56000</v>
       </c>
       <c r="K12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="N12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2">
+        <v>6</v>
+      </c>
+      <c r="P12" s="4">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="2">
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="Q12" s="4">
-        <v>7</v>
-      </c>
       <c r="R12" s="1">
-        <f t="shared" si="4"/>
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="4">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
         <f t="shared" si="5"/>
         <v>160</v>
       </c>
-      <c r="T12" s="1">
+      <c r="W12" s="1">
+        <f t="shared" si="6"/>
+        <v>160</v>
+      </c>
+      <c r="X12" s="1">
         <v>16</v>
       </c>
-      <c r="U12" s="1">
+      <c r="Y12" s="1">
         <v>7</v>
       </c>
-      <c r="V12" s="2">
+      <c r="Z12" s="2">
         <f t="shared" si="8"/>
         <v>160</v>
       </c>
-      <c r="W12" s="2">
+      <c r="AA12" s="2">
         <v>2</v>
       </c>
-      <c r="X12" s="2">
-        <v>10</v>
-      </c>
-      <c r="Y12" s="2">
+      <c r="AB12" s="2">
+        <v>6</v>
+      </c>
+      <c r="AC12" s="2">
         <f t="shared" si="11"/>
         <v>50</v>
       </c>
-      <c r="Z12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1">
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:28">
+    <row r="13" customHeight="1" spans="1:32">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2168,86 +2312,98 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G13" s="1">
         <v>8</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" si="6"/>
-        <v>2720</v>
+        <f t="shared" si="7"/>
+        <v>272</v>
       </c>
       <c r="I13" s="1">
-        <f t="shared" si="7"/>
-        <v>136</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" si="10"/>
         <v>81600</v>
       </c>
       <c r="K13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="N13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2">
+        <v>7</v>
+      </c>
+      <c r="P13" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2">
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="Q13" s="4">
-        <v>8</v>
-      </c>
       <c r="R13" s="1">
-        <f t="shared" si="4"/>
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1">
         <f t="shared" si="5"/>
         <v>170</v>
       </c>
-      <c r="T13" s="1">
+      <c r="W13" s="1">
+        <f t="shared" si="6"/>
+        <v>170</v>
+      </c>
+      <c r="X13" s="1">
         <v>17</v>
       </c>
-      <c r="U13" s="1">
+      <c r="Y13" s="1">
         <v>8</v>
       </c>
-      <c r="V13" s="2">
+      <c r="Z13" s="2">
         <f t="shared" si="8"/>
         <v>170</v>
       </c>
-      <c r="W13" s="2">
+      <c r="AA13" s="2">
         <v>2</v>
       </c>
-      <c r="X13" s="2">
-        <v>10</v>
-      </c>
-      <c r="Y13" s="2">
+      <c r="AB13" s="2">
+        <v>7</v>
+      </c>
+      <c r="AC13" s="2">
         <f t="shared" si="11"/>
         <v>60</v>
       </c>
-      <c r="Z13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="1">
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" customHeight="1" spans="1:32">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2258,86 +2414,98 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G14" s="1">
         <v>9</v>
       </c>
       <c r="H14" s="1">
-        <f t="shared" si="6"/>
-        <v>3240</v>
+        <f t="shared" si="7"/>
+        <v>324</v>
       </c>
       <c r="I14" s="1">
-        <f t="shared" si="7"/>
-        <v>162</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" si="10"/>
         <v>113400</v>
       </c>
       <c r="K14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="N14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2">
+        <v>8</v>
+      </c>
+      <c r="P14" s="4">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="2">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="Q14" s="4">
-        <v>9</v>
-      </c>
       <c r="R14" s="1">
-        <f t="shared" si="4"/>
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="4">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1">
         <f t="shared" si="5"/>
         <v>180</v>
       </c>
-      <c r="T14" s="1">
+      <c r="W14" s="1">
+        <f t="shared" si="6"/>
+        <v>180</v>
+      </c>
+      <c r="X14" s="1">
         <v>18</v>
       </c>
-      <c r="U14" s="1">
+      <c r="Y14" s="1">
         <v>9</v>
       </c>
-      <c r="V14" s="2">
+      <c r="Z14" s="2">
         <f t="shared" si="8"/>
         <v>180</v>
       </c>
-      <c r="W14" s="2">
+      <c r="AA14" s="2">
         <v>2</v>
       </c>
-      <c r="X14" s="2">
-        <v>10</v>
-      </c>
-      <c r="Y14" s="2">
+      <c r="AB14" s="2">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="2">
         <f t="shared" si="11"/>
         <v>70</v>
       </c>
-      <c r="Z14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1">
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:28">
+    <row r="15" customHeight="1" spans="1:32">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2348,86 +2516,98 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G15" s="1">
         <v>10</v>
       </c>
       <c r="H15" s="1">
-        <f t="shared" si="6"/>
-        <v>3800</v>
+        <f t="shared" si="7"/>
+        <v>380</v>
       </c>
       <c r="I15" s="1">
-        <f t="shared" si="7"/>
-        <v>190</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" si="10"/>
         <v>152000</v>
       </c>
       <c r="K15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="N15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="O15" s="1">
-        <v>0</v>
-      </c>
-      <c r="P15" s="2">
+        <v>9</v>
+      </c>
+      <c r="P15" s="4">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="2">
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="Q15" s="4">
-        <v>10</v>
-      </c>
       <c r="R15" s="1">
-        <f t="shared" si="4"/>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
         <f t="shared" si="5"/>
         <v>190</v>
       </c>
-      <c r="T15" s="1">
+      <c r="W15" s="1">
+        <f t="shared" si="6"/>
+        <v>190</v>
+      </c>
+      <c r="X15" s="1">
         <v>19</v>
       </c>
-      <c r="U15" s="1">
+      <c r="Y15" s="1">
         <v>10</v>
       </c>
-      <c r="V15" s="2">
+      <c r="Z15" s="2">
         <f t="shared" si="8"/>
         <v>190</v>
       </c>
-      <c r="W15" s="2">
+      <c r="AA15" s="2">
         <v>2</v>
       </c>
-      <c r="X15" s="2">
-        <v>10</v>
-      </c>
-      <c r="Y15" s="2">
+      <c r="AB15" s="2">
+        <v>9</v>
+      </c>
+      <c r="AC15" s="2">
         <f t="shared" si="11"/>
         <v>80</v>
       </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="1">
+      <c r="AD15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:28">
+    <row r="16" customHeight="1" spans="1:32">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2438,86 +2618,98 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G16" s="1">
         <v>11</v>
       </c>
       <c r="H16" s="1">
-        <f t="shared" si="6"/>
-        <v>6600</v>
+        <f t="shared" si="7"/>
+        <v>660</v>
       </c>
       <c r="I16" s="1">
-        <f t="shared" si="7"/>
-        <v>330</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="J16" s="1">
         <f t="shared" si="10"/>
         <v>198000</v>
       </c>
       <c r="K16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>44</v>
       </c>
       <c r="O16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="2">
+        <v>10</v>
+      </c>
+      <c r="P16" s="4">
+        <v>11</v>
+      </c>
+      <c r="Q16" s="2">
         <f t="shared" si="9"/>
         <v>28</v>
       </c>
-      <c r="Q16" s="4">
-        <v>11</v>
-      </c>
       <c r="R16" s="1">
-        <f t="shared" si="4"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="4">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
         <f t="shared" si="5"/>
         <v>200</v>
       </c>
-      <c r="T16" s="1">
+      <c r="W16" s="1">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
+      <c r="X16" s="1">
         <v>20</v>
       </c>
-      <c r="U16" s="1">
+      <c r="Y16" s="1">
         <v>11</v>
       </c>
-      <c r="V16" s="2">
+      <c r="Z16" s="2">
         <f t="shared" si="8"/>
         <v>200</v>
       </c>
-      <c r="W16" s="2">
+      <c r="AA16" s="2">
         <v>3</v>
       </c>
-      <c r="X16" s="2">
-        <v>15</v>
-      </c>
-      <c r="Y16" s="2">
+      <c r="AB16" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC16" s="2">
         <f t="shared" si="11"/>
         <v>90</v>
       </c>
-      <c r="Z16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1">
+      <c r="AD16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:28">
+    <row r="17" customHeight="1" spans="3:32">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2528,86 +2720,98 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G17" s="1">
         <v>12</v>
       </c>
       <c r="H17" s="1">
-        <f t="shared" si="6"/>
-        <v>7920</v>
+        <f t="shared" si="7"/>
+        <v>792</v>
       </c>
       <c r="I17" s="1">
-        <f t="shared" si="7"/>
-        <v>396</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" si="10"/>
         <v>264000</v>
       </c>
       <c r="K17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="N17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>48</v>
       </c>
       <c r="O17" s="1">
-        <v>0</v>
-      </c>
-      <c r="P17" s="2">
+        <v>11</v>
+      </c>
+      <c r="P17" s="4">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="2">
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="Q17" s="4">
-        <v>12</v>
-      </c>
       <c r="R17" s="1">
-        <f t="shared" si="4"/>
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="4">
+        <v>0</v>
+      </c>
+      <c r="U17" s="4">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1">
         <f t="shared" si="5"/>
         <v>210</v>
       </c>
-      <c r="T17" s="1">
+      <c r="W17" s="1">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="X17" s="1">
         <v>21</v>
       </c>
-      <c r="U17" s="1">
+      <c r="Y17" s="1">
         <v>12</v>
       </c>
-      <c r="V17" s="2">
-        <f t="shared" ref="V17:V30" si="12">V16+20</f>
+      <c r="Z17" s="2">
+        <f t="shared" ref="Z17:Z30" si="12">Z16+20</f>
         <v>220</v>
       </c>
-      <c r="W17" s="2">
+      <c r="AA17" s="2">
         <v>3</v>
       </c>
-      <c r="X17" s="2">
-        <v>15</v>
-      </c>
-      <c r="Y17" s="2">
+      <c r="AB17" s="2">
+        <v>11</v>
+      </c>
+      <c r="AC17" s="2">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="Z17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1">
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:28">
+    <row r="18" customHeight="1" spans="3:32">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -2618,86 +2822,98 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G18" s="1">
         <v>13</v>
       </c>
       <c r="H18" s="1">
-        <f t="shared" si="6"/>
-        <v>9360</v>
+        <f t="shared" si="7"/>
+        <v>936</v>
       </c>
       <c r="I18" s="1">
-        <f t="shared" si="7"/>
-        <v>468</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="J18" s="1">
         <f t="shared" si="10"/>
         <v>374400</v>
       </c>
       <c r="K18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="M18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="N18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>52</v>
       </c>
       <c r="O18" s="1">
-        <v>0</v>
-      </c>
-      <c r="P18" s="2">
+        <v>12</v>
+      </c>
+      <c r="P18" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="2">
         <f t="shared" si="9"/>
         <v>32</v>
       </c>
-      <c r="Q18" s="4">
-        <v>13</v>
-      </c>
       <c r="R18" s="1">
-        <f t="shared" si="4"/>
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="T18" s="4">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1">
         <f t="shared" si="5"/>
         <v>220</v>
       </c>
-      <c r="T18" s="1">
+      <c r="W18" s="1">
+        <f t="shared" si="6"/>
+        <v>220</v>
+      </c>
+      <c r="X18" s="1">
         <v>22</v>
       </c>
-      <c r="U18" s="1">
+      <c r="Y18" s="1">
         <v>13</v>
       </c>
-      <c r="V18" s="2">
+      <c r="Z18" s="2">
         <f t="shared" si="12"/>
         <v>240</v>
       </c>
-      <c r="W18" s="2">
+      <c r="AA18" s="2">
         <v>3</v>
       </c>
-      <c r="X18" s="2">
-        <v>15</v>
-      </c>
-      <c r="Y18" s="2">
-        <f t="shared" ref="Y18:Y30" si="13">Y17+20</f>
+      <c r="AB18" s="2">
+        <v>12</v>
+      </c>
+      <c r="AC18" s="2">
+        <f t="shared" ref="AC18:AC30" si="13">AC17+20</f>
         <v>120</v>
       </c>
-      <c r="Z18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1">
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:28">
+    <row r="19" customHeight="1" spans="3:32">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -2708,86 +2924,98 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G19" s="1">
         <v>14</v>
       </c>
       <c r="H19" s="1">
-        <f t="shared" si="6"/>
-        <v>10920</v>
+        <f t="shared" si="7"/>
+        <v>1092</v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" si="7"/>
-        <v>546</v>
+        <f t="shared" si="0"/>
+        <v>26</v>
       </c>
       <c r="J19" s="1">
         <f t="shared" si="10"/>
         <v>509600</v>
       </c>
       <c r="K19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="M19" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="N19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="O19" s="1">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2">
+        <v>13</v>
+      </c>
+      <c r="P19" s="4">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="2">
         <f t="shared" si="9"/>
         <v>34</v>
       </c>
-      <c r="Q19" s="4">
-        <v>14</v>
-      </c>
       <c r="R19" s="1">
-        <f t="shared" si="4"/>
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="S19" s="1">
+        <v>0</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
+        <v>0</v>
+      </c>
+      <c r="V19" s="1">
         <f t="shared" si="5"/>
         <v>230</v>
       </c>
-      <c r="T19" s="1">
+      <c r="W19" s="1">
+        <f t="shared" si="6"/>
+        <v>230</v>
+      </c>
+      <c r="X19" s="1">
         <v>23</v>
       </c>
-      <c r="U19" s="1">
+      <c r="Y19" s="1">
         <v>14</v>
       </c>
-      <c r="V19" s="2">
+      <c r="Z19" s="2">
         <f t="shared" si="12"/>
         <v>260</v>
       </c>
-      <c r="W19" s="2">
+      <c r="AA19" s="2">
         <v>3</v>
       </c>
-      <c r="X19" s="2">
-        <v>15</v>
-      </c>
-      <c r="Y19" s="2">
+      <c r="AB19" s="2">
+        <v>13</v>
+      </c>
+      <c r="AC19" s="2">
         <f t="shared" si="13"/>
         <v>140</v>
       </c>
-      <c r="Z19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1">
+      <c r="AD19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:28">
+    <row r="20" customHeight="1" spans="3:32">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -2798,86 +3026,98 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G20" s="1">
         <v>15</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" si="6"/>
-        <v>12600</v>
+        <f t="shared" si="7"/>
+        <v>1260</v>
       </c>
       <c r="I20" s="1">
-        <f t="shared" si="7"/>
-        <v>630</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" si="10"/>
         <v>672000</v>
       </c>
       <c r="K20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="M20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="N20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="2">
+        <v>14</v>
+      </c>
+      <c r="P20" s="4">
+        <v>15</v>
+      </c>
+      <c r="Q20" s="2">
         <f t="shared" si="9"/>
         <v>36</v>
       </c>
-      <c r="Q20" s="4">
-        <v>15</v>
-      </c>
       <c r="R20" s="1">
-        <f t="shared" si="4"/>
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="S20" s="1">
+        <v>0</v>
+      </c>
+      <c r="T20" s="4">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4">
+        <v>0</v>
+      </c>
+      <c r="V20" s="1">
         <f t="shared" si="5"/>
         <v>240</v>
       </c>
-      <c r="T20" s="1">
+      <c r="W20" s="1">
+        <f t="shared" si="6"/>
+        <v>240</v>
+      </c>
+      <c r="X20" s="1">
         <v>24</v>
       </c>
-      <c r="U20" s="1">
+      <c r="Y20" s="1">
         <v>15</v>
       </c>
-      <c r="V20" s="2">
+      <c r="Z20" s="2">
         <f t="shared" si="12"/>
         <v>280</v>
       </c>
-      <c r="W20" s="2">
+      <c r="AA20" s="2">
         <v>3</v>
       </c>
-      <c r="X20" s="2">
-        <v>15</v>
-      </c>
-      <c r="Y20" s="2">
+      <c r="AB20" s="2">
+        <v>14</v>
+      </c>
+      <c r="AC20" s="2">
         <f t="shared" si="13"/>
         <v>160</v>
       </c>
-      <c r="Z20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1">
+      <c r="AD20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:28">
+    <row r="21" customHeight="1" spans="3:32">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -2888,86 +3128,98 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G21" s="1">
         <v>16</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" si="6"/>
-        <v>19200</v>
+        <f t="shared" si="7"/>
+        <v>1920</v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" si="7"/>
-        <v>960</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" si="10"/>
         <v>864000</v>
       </c>
       <c r="K21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="N21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="2">
+        <v>15</v>
+      </c>
+      <c r="P21" s="4">
+        <v>16</v>
+      </c>
+      <c r="Q21" s="2">
         <f t="shared" si="9"/>
         <v>38</v>
       </c>
-      <c r="Q21" s="4">
-        <v>16</v>
-      </c>
       <c r="R21" s="1">
-        <f t="shared" si="4"/>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="4">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
         <f t="shared" si="5"/>
         <v>250</v>
       </c>
-      <c r="T21" s="1">
+      <c r="W21" s="1">
+        <f t="shared" si="6"/>
+        <v>250</v>
+      </c>
+      <c r="X21" s="1">
         <v>25</v>
       </c>
-      <c r="U21" s="1">
+      <c r="Y21" s="1">
         <v>16</v>
       </c>
-      <c r="V21" s="2">
+      <c r="Z21" s="2">
         <f t="shared" si="12"/>
         <v>300</v>
       </c>
-      <c r="W21" s="2">
+      <c r="AA21" s="2">
         <v>4</v>
       </c>
-      <c r="X21" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y21" s="2">
+      <c r="AB21" s="2">
+        <v>15</v>
+      </c>
+      <c r="AC21" s="2">
         <f t="shared" si="13"/>
         <v>180</v>
       </c>
-      <c r="Z21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1">
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:28">
+    <row r="22" customHeight="1" spans="3:32">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2978,86 +3230,98 @@
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G22" s="1">
         <v>17</v>
       </c>
       <c r="H22" s="1">
-        <f t="shared" si="6"/>
-        <v>21760</v>
+        <f t="shared" si="7"/>
+        <v>2176</v>
       </c>
       <c r="I22" s="1">
-        <f t="shared" si="7"/>
-        <v>1088</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" si="10"/>
         <v>1088000</v>
       </c>
       <c r="K22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="L22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>51</v>
       </c>
       <c r="M22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="N22" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>68</v>
       </c>
       <c r="O22" s="1">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2">
+        <v>16</v>
+      </c>
+      <c r="P22" s="4">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="2">
         <f t="shared" si="9"/>
         <v>40</v>
       </c>
-      <c r="Q22" s="4">
-        <v>17</v>
-      </c>
       <c r="R22" s="1">
-        <f t="shared" si="4"/>
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="4">
+        <v>0</v>
+      </c>
+      <c r="U22" s="4">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
         <f t="shared" si="5"/>
         <v>260</v>
       </c>
-      <c r="T22" s="1">
+      <c r="W22" s="1">
+        <f t="shared" si="6"/>
+        <v>260</v>
+      </c>
+      <c r="X22" s="1">
         <v>26</v>
       </c>
-      <c r="U22" s="1">
+      <c r="Y22" s="1">
         <v>17</v>
       </c>
-      <c r="V22" s="2">
+      <c r="Z22" s="2">
         <f t="shared" si="12"/>
         <v>320</v>
       </c>
-      <c r="W22" s="2">
+      <c r="AA22" s="2">
         <v>4</v>
       </c>
-      <c r="X22" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y22" s="2">
+      <c r="AB22" s="2">
+        <v>16</v>
+      </c>
+      <c r="AC22" s="2">
         <f t="shared" si="13"/>
         <v>200</v>
       </c>
-      <c r="Z22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1">
+      <c r="AD22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:28">
+    <row r="23" customHeight="1" spans="3:32">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -3068,86 +3332,98 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G23" s="1">
         <v>18</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" si="6"/>
-        <v>24480</v>
+        <f t="shared" si="7"/>
+        <v>2448</v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" si="7"/>
-        <v>1224</v>
+        <f t="shared" si="0"/>
+        <v>34</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" si="10"/>
         <v>1346400</v>
       </c>
       <c r="K23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="L23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
       <c r="M23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="N23" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="2">
+        <v>17</v>
+      </c>
+      <c r="P23" s="4">
+        <v>18</v>
+      </c>
+      <c r="Q23" s="2">
         <f t="shared" si="9"/>
         <v>42</v>
       </c>
-      <c r="Q23" s="4">
-        <v>18</v>
-      </c>
       <c r="R23" s="1">
-        <f t="shared" si="4"/>
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="4">
+        <v>0</v>
+      </c>
+      <c r="U23" s="4">
+        <v>0</v>
+      </c>
+      <c r="V23" s="1">
         <f t="shared" si="5"/>
         <v>270</v>
       </c>
-      <c r="T23" s="1">
+      <c r="W23" s="1">
+        <f t="shared" si="6"/>
+        <v>270</v>
+      </c>
+      <c r="X23" s="1">
         <v>27</v>
       </c>
-      <c r="U23" s="1">
+      <c r="Y23" s="1">
         <v>18</v>
       </c>
-      <c r="V23" s="2">
+      <c r="Z23" s="2">
         <f t="shared" si="12"/>
         <v>340</v>
       </c>
-      <c r="W23" s="2">
+      <c r="AA23" s="2">
         <v>4</v>
       </c>
-      <c r="X23" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y23" s="2">
+      <c r="AB23" s="2">
+        <v>17</v>
+      </c>
+      <c r="AC23" s="2">
         <f t="shared" si="13"/>
         <v>220</v>
       </c>
-      <c r="Z23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="1">
+      <c r="AD23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="1"/>
+      <c r="AF23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:28">
+    <row r="24" customHeight="1" spans="3:32">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -3158,86 +3434,98 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G24" s="1">
         <v>19</v>
       </c>
       <c r="H24" s="1">
-        <f t="shared" si="6"/>
-        <v>27360</v>
+        <f t="shared" si="7"/>
+        <v>2736</v>
       </c>
       <c r="I24" s="1">
-        <f t="shared" si="7"/>
-        <v>1368</v>
+        <f t="shared" si="0"/>
+        <v>36</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" si="10"/>
         <v>1641600</v>
       </c>
       <c r="K24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="L24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>57</v>
       </c>
       <c r="M24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="N24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>76</v>
       </c>
       <c r="O24" s="1">
-        <v>0</v>
-      </c>
-      <c r="P24" s="2">
+        <v>18</v>
+      </c>
+      <c r="P24" s="4">
+        <v>19</v>
+      </c>
+      <c r="Q24" s="2">
         <f t="shared" si="9"/>
         <v>44</v>
       </c>
-      <c r="Q24" s="4">
-        <v>19</v>
-      </c>
       <c r="R24" s="1">
-        <f t="shared" si="4"/>
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="S24" s="1">
+        <v>0</v>
+      </c>
+      <c r="T24" s="4">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4">
+        <v>0</v>
+      </c>
+      <c r="V24" s="1">
         <f t="shared" si="5"/>
         <v>280</v>
       </c>
-      <c r="T24" s="1">
+      <c r="W24" s="1">
+        <f t="shared" si="6"/>
+        <v>280</v>
+      </c>
+      <c r="X24" s="1">
         <v>28</v>
       </c>
-      <c r="U24" s="1">
+      <c r="Y24" s="1">
         <v>19</v>
       </c>
-      <c r="V24" s="2">
+      <c r="Z24" s="2">
         <f t="shared" si="12"/>
         <v>360</v>
       </c>
-      <c r="W24" s="2">
+      <c r="AA24" s="2">
         <v>4</v>
       </c>
-      <c r="X24" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y24" s="2">
+      <c r="AB24" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC24" s="2">
         <f t="shared" si="13"/>
         <v>240</v>
       </c>
-      <c r="Z24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1">
+      <c r="AD24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="3:28">
+    <row r="25" customHeight="1" spans="3:32">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -3248,86 +3536,98 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G25" s="1">
         <v>20</v>
       </c>
       <c r="H25" s="1">
-        <f t="shared" si="6"/>
-        <v>30400</v>
+        <f t="shared" si="7"/>
+        <v>3040</v>
       </c>
       <c r="I25" s="1">
-        <f t="shared" si="7"/>
-        <v>1520</v>
+        <f t="shared" si="0"/>
+        <v>38</v>
       </c>
       <c r="J25" s="1">
         <f t="shared" si="10"/>
         <v>1976000</v>
       </c>
       <c r="K25" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="M25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="N25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="O25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="2">
+        <v>19</v>
+      </c>
+      <c r="P25" s="4">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="2">
         <f t="shared" si="9"/>
         <v>46</v>
       </c>
-      <c r="Q25" s="4">
-        <v>20</v>
-      </c>
       <c r="R25" s="1">
-        <f t="shared" si="4"/>
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="S25" s="1">
+        <v>0</v>
+      </c>
+      <c r="T25" s="4">
+        <v>0</v>
+      </c>
+      <c r="U25" s="4">
+        <v>0</v>
+      </c>
+      <c r="V25" s="1">
         <f t="shared" si="5"/>
         <v>290</v>
       </c>
-      <c r="T25" s="1">
+      <c r="W25" s="1">
+        <f t="shared" si="6"/>
+        <v>290</v>
+      </c>
+      <c r="X25" s="1">
         <v>29</v>
       </c>
-      <c r="U25" s="1">
+      <c r="Y25" s="1">
         <v>20</v>
       </c>
-      <c r="V25" s="2">
+      <c r="Z25" s="2">
         <f t="shared" si="12"/>
         <v>380</v>
       </c>
-      <c r="W25" s="2">
+      <c r="AA25" s="2">
         <v>4</v>
       </c>
-      <c r="X25" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y25" s="2">
+      <c r="AB25" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC25" s="2">
         <f t="shared" si="13"/>
         <v>260</v>
       </c>
-      <c r="Z25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1">
+      <c r="AD25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="3:28">
+    <row r="26" customHeight="1" spans="3:32">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -3338,86 +3638,98 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G26" s="1">
         <v>21</v>
       </c>
       <c r="H26" s="1">
-        <f t="shared" si="6"/>
-        <v>42000</v>
+        <f t="shared" si="7"/>
+        <v>4200</v>
       </c>
       <c r="I26" s="1">
-        <f t="shared" si="7"/>
-        <v>2100</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" si="10"/>
         <v>2352000</v>
       </c>
       <c r="K26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="L26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="M26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="N26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="O26" s="1">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2">
+        <v>20</v>
+      </c>
+      <c r="P26" s="4">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="2">
         <f t="shared" si="9"/>
         <v>48</v>
       </c>
-      <c r="Q26" s="4">
-        <v>21</v>
-      </c>
       <c r="R26" s="1">
-        <f t="shared" si="4"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="S26" s="1">
+        <v>0</v>
+      </c>
+      <c r="T26" s="4">
+        <v>0</v>
+      </c>
+      <c r="U26" s="4">
+        <v>0</v>
+      </c>
+      <c r="V26" s="1">
         <f t="shared" si="5"/>
         <v>300</v>
       </c>
-      <c r="T26" s="1">
+      <c r="W26" s="1">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
+      <c r="X26" s="1">
         <v>30</v>
       </c>
-      <c r="U26" s="1">
+      <c r="Y26" s="1">
         <v>21</v>
       </c>
-      <c r="V26" s="2">
+      <c r="Z26" s="2">
         <f t="shared" si="12"/>
         <v>400</v>
       </c>
-      <c r="W26" s="2">
+      <c r="AA26" s="2">
         <v>5</v>
       </c>
-      <c r="X26" s="2">
-        <v>25</v>
-      </c>
-      <c r="Y26" s="2">
+      <c r="AB26" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC26" s="2">
         <f t="shared" si="13"/>
         <v>280</v>
       </c>
-      <c r="Z26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1">
+      <c r="AD26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="3:28">
+    <row r="27" customHeight="1" spans="3:32">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -3428,86 +3740,98 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G27" s="1">
         <v>22</v>
       </c>
       <c r="H27" s="1">
-        <f t="shared" si="6"/>
-        <v>48400</v>
+        <f t="shared" si="7"/>
+        <v>4840</v>
       </c>
       <c r="I27" s="1">
-        <f t="shared" si="7"/>
-        <v>2420</v>
+        <f t="shared" si="0"/>
+        <v>42</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" si="10"/>
         <v>2904000</v>
       </c>
       <c r="K27" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="L27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>66</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="N27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>88</v>
       </c>
       <c r="O27" s="1">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2">
+        <v>21</v>
+      </c>
+      <c r="P27" s="4">
+        <v>22</v>
+      </c>
+      <c r="Q27" s="2">
         <f t="shared" si="9"/>
         <v>50</v>
       </c>
-      <c r="Q27" s="4">
-        <v>22</v>
-      </c>
       <c r="R27" s="1">
-        <f t="shared" si="4"/>
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="S27" s="1">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4">
+        <v>0</v>
+      </c>
+      <c r="V27" s="1">
         <f t="shared" si="5"/>
         <v>310</v>
       </c>
-      <c r="T27" s="1">
+      <c r="W27" s="1">
+        <f t="shared" si="6"/>
+        <v>310</v>
+      </c>
+      <c r="X27" s="1">
         <v>31</v>
       </c>
-      <c r="U27" s="1">
+      <c r="Y27" s="1">
         <v>22</v>
       </c>
-      <c r="V27" s="2">
-        <f t="shared" ref="V27:V38" si="14">V26+40</f>
+      <c r="Z27" s="2">
+        <f t="shared" ref="Z27:Z38" si="14">Z26+40</f>
         <v>440</v>
       </c>
-      <c r="W27" s="2">
+      <c r="AA27" s="2">
         <v>5</v>
       </c>
-      <c r="X27" s="2">
-        <v>25</v>
-      </c>
-      <c r="Y27" s="2">
+      <c r="AB27" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" s="2">
         <f t="shared" si="13"/>
         <v>300</v>
       </c>
-      <c r="Z27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1">
+      <c r="AD27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:28">
+    <row r="28" customHeight="1" spans="3:32">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -3518,86 +3842,98 @@
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G28" s="1">
         <v>23</v>
       </c>
       <c r="H28" s="1">
-        <f t="shared" si="6"/>
-        <v>55200</v>
+        <f t="shared" si="7"/>
+        <v>5520</v>
       </c>
       <c r="I28" s="1">
-        <f t="shared" si="7"/>
-        <v>2760</v>
+        <f t="shared" si="0"/>
+        <v>44</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" si="10"/>
         <v>3643200</v>
       </c>
       <c r="K28" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="L28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="N28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="O28" s="1">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2">
-        <f>P27+5</f>
+        <v>22</v>
+      </c>
+      <c r="P28" s="4">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="2">
+        <f>Q27+5</f>
         <v>55</v>
       </c>
-      <c r="Q28" s="4">
-        <v>23</v>
-      </c>
       <c r="R28" s="1">
-        <f t="shared" si="4"/>
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="S28" s="1">
+        <v>0</v>
+      </c>
+      <c r="T28" s="4">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4">
+        <v>0</v>
+      </c>
+      <c r="V28" s="1">
         <f t="shared" si="5"/>
         <v>320</v>
       </c>
-      <c r="T28" s="1">
+      <c r="W28" s="1">
+        <f t="shared" si="6"/>
+        <v>320</v>
+      </c>
+      <c r="X28" s="1">
         <v>32</v>
       </c>
-      <c r="U28" s="1">
+      <c r="Y28" s="1">
         <v>23</v>
       </c>
-      <c r="V28" s="2">
+      <c r="Z28" s="2">
         <f t="shared" si="14"/>
         <v>480</v>
       </c>
-      <c r="W28" s="2">
+      <c r="AA28" s="2">
         <v>5</v>
       </c>
-      <c r="X28" s="2">
-        <v>25</v>
-      </c>
-      <c r="Y28" s="2">
-        <f t="shared" ref="Y28:Y45" si="15">Y27+30</f>
+      <c r="AB28" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC28" s="2">
+        <f t="shared" ref="AC28:AC45" si="15">AC27+30</f>
         <v>330</v>
       </c>
-      <c r="Z28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1">
+      <c r="AD28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:28">
+    <row r="29" customHeight="1" spans="3:32">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -3608,86 +3944,98 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G29" s="1">
         <v>24</v>
       </c>
       <c r="H29" s="1">
-        <f t="shared" si="6"/>
-        <v>62400</v>
+        <f t="shared" si="7"/>
+        <v>6240</v>
       </c>
       <c r="I29" s="1">
-        <f t="shared" si="7"/>
-        <v>3120</v>
+        <f t="shared" si="0"/>
+        <v>46</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" si="10"/>
         <v>4492800</v>
       </c>
       <c r="K29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="L29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="N29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>96</v>
       </c>
       <c r="O29" s="1">
-        <v>0</v>
-      </c>
-      <c r="P29" s="2">
-        <f t="shared" ref="P29:P45" si="16">P28+5</f>
+        <v>23</v>
+      </c>
+      <c r="P29" s="4">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="2">
+        <f t="shared" ref="Q29:Q45" si="16">Q28+5</f>
         <v>60</v>
       </c>
-      <c r="Q29" s="4">
-        <v>24</v>
-      </c>
       <c r="R29" s="1">
-        <f t="shared" si="4"/>
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="S29" s="1">
+        <v>0</v>
+      </c>
+      <c r="T29" s="4">
+        <v>0</v>
+      </c>
+      <c r="U29" s="4">
+        <v>0</v>
+      </c>
+      <c r="V29" s="1">
         <f t="shared" si="5"/>
         <v>330</v>
       </c>
-      <c r="T29" s="1">
+      <c r="W29" s="1">
+        <f t="shared" si="6"/>
+        <v>330</v>
+      </c>
+      <c r="X29" s="1">
         <v>33</v>
       </c>
-      <c r="U29" s="1">
+      <c r="Y29" s="1">
         <v>24</v>
       </c>
-      <c r="V29" s="2">
+      <c r="Z29" s="2">
         <f t="shared" si="14"/>
         <v>520</v>
       </c>
-      <c r="W29" s="2">
+      <c r="AA29" s="2">
         <v>5</v>
       </c>
-      <c r="X29" s="2">
-        <v>25</v>
-      </c>
-      <c r="Y29" s="2">
+      <c r="AB29" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC29" s="2">
         <f t="shared" si="15"/>
         <v>360</v>
       </c>
-      <c r="Z29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="1">
+      <c r="AD29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:28">
+    <row r="30" customHeight="1" spans="3:32">
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -3698,86 +4046,98 @@
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G30" s="1">
         <v>25</v>
       </c>
       <c r="H30" s="1">
-        <f t="shared" si="6"/>
-        <v>70000</v>
+        <f t="shared" si="7"/>
+        <v>7000</v>
       </c>
       <c r="I30" s="1">
-        <f t="shared" si="7"/>
-        <v>3500</v>
+        <f t="shared" si="0"/>
+        <v>48</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" si="10"/>
         <v>5460000</v>
       </c>
       <c r="K30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="L30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="M30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="N30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="O30" s="1">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2">
+        <v>24</v>
+      </c>
+      <c r="P30" s="4">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="2">
         <f t="shared" si="16"/>
         <v>65</v>
       </c>
-      <c r="Q30" s="4">
-        <v>25</v>
-      </c>
       <c r="R30" s="1">
-        <f t="shared" si="4"/>
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="S30" s="1">
+        <v>0</v>
+      </c>
+      <c r="T30" s="4">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4">
+        <v>0</v>
+      </c>
+      <c r="V30" s="1">
         <f t="shared" si="5"/>
         <v>340</v>
       </c>
-      <c r="T30" s="1">
+      <c r="W30" s="1">
+        <f t="shared" si="6"/>
+        <v>340</v>
+      </c>
+      <c r="X30" s="1">
         <v>34</v>
       </c>
-      <c r="U30" s="1">
+      <c r="Y30" s="1">
         <v>25</v>
       </c>
-      <c r="V30" s="2">
+      <c r="Z30" s="2">
         <f t="shared" si="14"/>
         <v>560</v>
       </c>
-      <c r="W30" s="2">
+      <c r="AA30" s="2">
         <v>5</v>
       </c>
-      <c r="X30" s="2">
-        <v>25</v>
-      </c>
-      <c r="Y30" s="2">
+      <c r="AB30" s="2">
+        <v>24</v>
+      </c>
+      <c r="AC30" s="2">
         <f t="shared" si="15"/>
         <v>390</v>
       </c>
-      <c r="Z30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1">
+      <c r="AD30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:28">
+    <row r="31" customHeight="1" spans="3:32">
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -3788,86 +4148,98 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G31" s="1">
         <v>26</v>
       </c>
       <c r="H31" s="1">
-        <f t="shared" si="6"/>
-        <v>93600</v>
+        <f t="shared" si="7"/>
+        <v>9360</v>
       </c>
       <c r="I31" s="1">
-        <f t="shared" si="7"/>
-        <v>4680</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" si="10"/>
         <v>6552000</v>
       </c>
       <c r="K31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>130</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>78</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="N31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>104</v>
       </c>
       <c r="O31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2">
+        <v>25</v>
+      </c>
+      <c r="P31" s="4">
+        <v>26</v>
+      </c>
+      <c r="Q31" s="2">
         <f t="shared" si="16"/>
         <v>70</v>
       </c>
-      <c r="Q31" s="4">
-        <v>26</v>
-      </c>
       <c r="R31" s="1">
-        <f t="shared" si="4"/>
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S31" s="1">
+        <v>0</v>
+      </c>
+      <c r="T31" s="4">
+        <v>0</v>
+      </c>
+      <c r="U31" s="4">
+        <v>0</v>
+      </c>
+      <c r="V31" s="1">
         <f t="shared" si="5"/>
         <v>350</v>
       </c>
-      <c r="T31" s="1">
+      <c r="W31" s="1">
+        <f t="shared" si="6"/>
+        <v>350</v>
+      </c>
+      <c r="X31" s="1">
         <v>35</v>
       </c>
-      <c r="U31" s="1">
+      <c r="Y31" s="1">
         <v>26</v>
       </c>
-      <c r="V31" s="2">
+      <c r="Z31" s="2">
         <f t="shared" si="14"/>
         <v>600</v>
       </c>
-      <c r="W31" s="2">
+      <c r="AA31" s="2">
         <v>6</v>
       </c>
-      <c r="X31" s="2">
-        <v>30</v>
-      </c>
-      <c r="Y31" s="2">
+      <c r="AB31" s="2">
+        <v>25</v>
+      </c>
+      <c r="AC31" s="2">
         <f t="shared" si="15"/>
         <v>420</v>
       </c>
-      <c r="Z31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1">
+      <c r="AD31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:28">
+    <row r="32" customHeight="1" spans="3:32">
       <c r="C32" s="1">
         <v>27</v>
       </c>
@@ -3878,86 +4250,98 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G32" s="1">
         <v>27</v>
       </c>
       <c r="H32" s="1">
-        <f t="shared" si="6"/>
-        <v>103680</v>
+        <f t="shared" si="7"/>
+        <v>10368</v>
       </c>
       <c r="I32" s="1">
-        <f t="shared" si="7"/>
-        <v>5184</v>
+        <f t="shared" si="0"/>
+        <v>52</v>
       </c>
       <c r="J32" s="1">
         <f t="shared" si="10"/>
         <v>7776000</v>
       </c>
       <c r="K32" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>135</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
       <c r="N32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>108</v>
       </c>
       <c r="O32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2">
+        <v>26</v>
+      </c>
+      <c r="P32" s="4">
+        <v>27</v>
+      </c>
+      <c r="Q32" s="2">
         <f t="shared" si="16"/>
         <v>75</v>
       </c>
-      <c r="Q32" s="4">
-        <v>27</v>
-      </c>
       <c r="R32" s="1">
-        <f t="shared" si="4"/>
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="S32" s="1">
+        <v>0</v>
+      </c>
+      <c r="T32" s="4">
+        <v>0</v>
+      </c>
+      <c r="U32" s="4">
+        <v>0</v>
+      </c>
+      <c r="V32" s="1">
         <f t="shared" si="5"/>
         <v>360</v>
       </c>
-      <c r="T32" s="1">
+      <c r="W32" s="1">
+        <f t="shared" si="6"/>
+        <v>360</v>
+      </c>
+      <c r="X32" s="1">
         <v>36</v>
       </c>
-      <c r="U32" s="1">
+      <c r="Y32" s="1">
         <v>27</v>
       </c>
-      <c r="V32" s="2">
+      <c r="Z32" s="2">
         <f t="shared" si="14"/>
         <v>640</v>
       </c>
-      <c r="W32" s="2">
+      <c r="AA32" s="2">
         <v>6</v>
       </c>
-      <c r="X32" s="2">
-        <v>30</v>
-      </c>
-      <c r="Y32" s="2">
+      <c r="AB32" s="2">
+        <v>26</v>
+      </c>
+      <c r="AC32" s="2">
         <f t="shared" si="15"/>
         <v>450</v>
       </c>
-      <c r="Z32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="1"/>
-      <c r="AB32" s="1">
+      <c r="AD32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:28">
+    <row r="33" customHeight="1" spans="1:32">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -3968,86 +4352,98 @@
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G33" s="1">
         <v>28</v>
       </c>
       <c r="H33" s="1">
-        <f t="shared" si="6"/>
-        <v>114240</v>
+        <f t="shared" si="7"/>
+        <v>11424</v>
       </c>
       <c r="I33" s="1">
-        <f t="shared" si="7"/>
-        <v>5712</v>
+        <f t="shared" si="0"/>
+        <v>54</v>
       </c>
       <c r="J33" s="1">
         <f t="shared" si="10"/>
         <v>9139200</v>
       </c>
       <c r="K33" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>140</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>56</v>
       </c>
       <c r="N33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="O33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="2">
+        <v>27</v>
+      </c>
+      <c r="P33" s="4">
+        <v>28</v>
+      </c>
+      <c r="Q33" s="2">
         <f t="shared" si="16"/>
         <v>80</v>
       </c>
-      <c r="Q33" s="4">
-        <v>28</v>
-      </c>
       <c r="R33" s="1">
-        <f t="shared" si="4"/>
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="S33" s="1">
+        <v>0</v>
+      </c>
+      <c r="T33" s="4">
+        <v>0</v>
+      </c>
+      <c r="U33" s="4">
+        <v>0</v>
+      </c>
+      <c r="V33" s="1">
         <f t="shared" si="5"/>
         <v>370</v>
       </c>
-      <c r="T33" s="1">
+      <c r="W33" s="1">
+        <f t="shared" si="6"/>
+        <v>370</v>
+      </c>
+      <c r="X33" s="1">
         <v>37</v>
       </c>
-      <c r="U33" s="1">
+      <c r="Y33" s="1">
         <v>28</v>
       </c>
-      <c r="V33" s="2">
+      <c r="Z33" s="2">
         <f t="shared" si="14"/>
         <v>680</v>
       </c>
-      <c r="W33" s="2">
+      <c r="AA33" s="2">
         <v>6</v>
       </c>
-      <c r="X33" s="2">
-        <v>30</v>
-      </c>
-      <c r="Y33" s="2">
+      <c r="AB33" s="2">
+        <v>27</v>
+      </c>
+      <c r="AC33" s="2">
         <f t="shared" si="15"/>
         <v>480</v>
       </c>
-      <c r="Z33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="1"/>
-      <c r="AB33" s="1">
+      <c r="AD33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:28">
+    <row r="34" customHeight="1" spans="1:32">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -4058,86 +4454,98 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G34" s="1">
         <v>29</v>
       </c>
       <c r="H34" s="1">
-        <f t="shared" si="6"/>
-        <v>125280</v>
+        <f t="shared" si="7"/>
+        <v>12528</v>
       </c>
       <c r="I34" s="1">
-        <f t="shared" si="7"/>
-        <v>6264</v>
+        <f t="shared" si="0"/>
+        <v>56</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" si="10"/>
         <v>10648800</v>
       </c>
       <c r="K34" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>145</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="M34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="N34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>116</v>
       </c>
       <c r="O34" s="1">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2">
+        <v>28</v>
+      </c>
+      <c r="P34" s="4">
+        <v>29</v>
+      </c>
+      <c r="Q34" s="2">
         <f t="shared" si="16"/>
         <v>85</v>
       </c>
-      <c r="Q34" s="4">
-        <v>29</v>
-      </c>
       <c r="R34" s="1">
-        <f t="shared" si="4"/>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="S34" s="1">
+        <v>0</v>
+      </c>
+      <c r="T34" s="4">
+        <v>0</v>
+      </c>
+      <c r="U34" s="4">
+        <v>0</v>
+      </c>
+      <c r="V34" s="1">
         <f t="shared" si="5"/>
         <v>380</v>
       </c>
-      <c r="T34" s="1">
+      <c r="W34" s="1">
+        <f t="shared" si="6"/>
+        <v>380</v>
+      </c>
+      <c r="X34" s="1">
         <v>38</v>
       </c>
-      <c r="U34" s="1">
+      <c r="Y34" s="1">
         <v>29</v>
       </c>
-      <c r="V34" s="2">
+      <c r="Z34" s="2">
         <f t="shared" si="14"/>
         <v>720</v>
       </c>
-      <c r="W34" s="2">
+      <c r="AA34" s="2">
         <v>6</v>
       </c>
-      <c r="X34" s="2">
-        <v>30</v>
-      </c>
-      <c r="Y34" s="2">
+      <c r="AB34" s="2">
+        <v>28</v>
+      </c>
+      <c r="AC34" s="2">
         <f t="shared" si="15"/>
         <v>510</v>
       </c>
-      <c r="Z34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="1"/>
-      <c r="AB34" s="1">
+      <c r="AD34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:28">
+    <row r="35" customHeight="1" spans="1:32">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -4148,86 +4556,98 @@
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G35" s="1">
         <v>30</v>
       </c>
       <c r="H35" s="1">
-        <f t="shared" si="6"/>
-        <v>136800</v>
+        <f t="shared" si="7"/>
+        <v>13680</v>
       </c>
       <c r="I35" s="1">
-        <f t="shared" si="7"/>
-        <v>6840</v>
+        <f t="shared" si="0"/>
+        <v>58</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" si="10"/>
         <v>12312000</v>
       </c>
       <c r="K35" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="M35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="N35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>120</v>
       </c>
       <c r="O35" s="1">
-        <v>0</v>
-      </c>
-      <c r="P35" s="2">
+        <v>29</v>
+      </c>
+      <c r="P35" s="4">
+        <v>30</v>
+      </c>
+      <c r="Q35" s="2">
         <f t="shared" si="16"/>
         <v>90</v>
       </c>
-      <c r="Q35" s="4">
-        <v>30</v>
-      </c>
       <c r="R35" s="1">
-        <f t="shared" si="4"/>
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="S35" s="1">
+        <v>0</v>
+      </c>
+      <c r="T35" s="4">
+        <v>0</v>
+      </c>
+      <c r="U35" s="4">
+        <v>0</v>
+      </c>
+      <c r="V35" s="1">
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
-      <c r="T35" s="1">
+      <c r="W35" s="1">
+        <f t="shared" si="6"/>
+        <v>390</v>
+      </c>
+      <c r="X35" s="1">
         <v>39</v>
       </c>
-      <c r="U35" s="1">
+      <c r="Y35" s="1">
         <v>30</v>
       </c>
-      <c r="V35" s="2">
+      <c r="Z35" s="2">
         <f t="shared" si="14"/>
         <v>760</v>
       </c>
-      <c r="W35" s="2">
+      <c r="AA35" s="2">
         <v>6</v>
       </c>
-      <c r="X35" s="2">
-        <v>30</v>
-      </c>
-      <c r="Y35" s="2">
+      <c r="AB35" s="2">
+        <v>29</v>
+      </c>
+      <c r="AC35" s="2">
         <f t="shared" si="15"/>
         <v>540</v>
       </c>
-      <c r="Z35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="1"/>
-      <c r="AB35" s="1">
+      <c r="AD35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:28">
+    <row r="36" customHeight="1" spans="1:32">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -4238,86 +4658,98 @@
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G36" s="1">
         <v>31</v>
       </c>
       <c r="H36" s="1">
-        <f t="shared" si="6"/>
-        <v>173600</v>
+        <f t="shared" si="7"/>
+        <v>17360</v>
       </c>
       <c r="I36" s="1">
-        <f t="shared" si="7"/>
-        <v>8680</v>
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" si="10"/>
         <v>14136000</v>
       </c>
       <c r="K36" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>155</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
       <c r="M36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>62</v>
       </c>
       <c r="N36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>124</v>
       </c>
       <c r="O36" s="1">
-        <v>0</v>
-      </c>
-      <c r="P36" s="2">
+        <v>30</v>
+      </c>
+      <c r="P36" s="4">
+        <v>31</v>
+      </c>
+      <c r="Q36" s="2">
         <f t="shared" si="16"/>
         <v>95</v>
       </c>
-      <c r="Q36" s="4">
-        <v>31</v>
-      </c>
       <c r="R36" s="1">
-        <f t="shared" si="4"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S36" s="1">
+        <v>0</v>
+      </c>
+      <c r="T36" s="4">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4">
+        <v>0</v>
+      </c>
+      <c r="V36" s="1">
         <f t="shared" si="5"/>
         <v>400</v>
       </c>
-      <c r="T36" s="1">
+      <c r="W36" s="1">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="X36" s="1">
         <v>40</v>
       </c>
-      <c r="U36" s="1">
+      <c r="Y36" s="1">
         <v>31</v>
       </c>
-      <c r="V36" s="2">
+      <c r="Z36" s="2">
         <f t="shared" si="14"/>
         <v>800</v>
       </c>
-      <c r="W36" s="2">
+      <c r="AA36" s="2">
         <v>7</v>
       </c>
-      <c r="X36" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y36" s="2">
+      <c r="AB36" s="2">
+        <v>30</v>
+      </c>
+      <c r="AC36" s="2">
         <f t="shared" si="15"/>
         <v>570</v>
       </c>
-      <c r="Z36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="1"/>
-      <c r="AB36" s="1">
+      <c r="AD36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:28">
+    <row r="37" customHeight="1" spans="1:32">
       <c r="C37" s="1">
         <v>32</v>
       </c>
@@ -4328,86 +4760,98 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G37" s="1">
         <v>32</v>
       </c>
       <c r="H37" s="1">
-        <f t="shared" si="6"/>
-        <v>197120</v>
+        <f t="shared" si="7"/>
+        <v>19712</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="7"/>
-        <v>9856</v>
+        <f t="shared" si="0"/>
+        <v>62</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" si="10"/>
         <v>16896000</v>
       </c>
       <c r="K37" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>160</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="M37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>64</v>
       </c>
       <c r="N37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>128</v>
       </c>
       <c r="O37" s="1">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2">
+        <v>31</v>
+      </c>
+      <c r="P37" s="4">
+        <v>32</v>
+      </c>
+      <c r="Q37" s="2">
         <f t="shared" si="16"/>
         <v>100</v>
       </c>
-      <c r="Q37" s="4">
-        <v>32</v>
-      </c>
       <c r="R37" s="1">
-        <f t="shared" si="4"/>
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="S37" s="1">
+        <v>0</v>
+      </c>
+      <c r="T37" s="4">
+        <v>0</v>
+      </c>
+      <c r="U37" s="4">
+        <v>0</v>
+      </c>
+      <c r="V37" s="1">
         <f t="shared" si="5"/>
         <v>410</v>
       </c>
-      <c r="T37" s="1">
+      <c r="W37" s="1">
+        <f t="shared" si="6"/>
+        <v>410</v>
+      </c>
+      <c r="X37" s="1">
         <v>41</v>
       </c>
-      <c r="U37" s="1">
+      <c r="Y37" s="1">
         <v>32</v>
       </c>
-      <c r="V37" s="2">
-        <f t="shared" ref="V37:V45" si="17">V36+80</f>
+      <c r="Z37" s="2">
+        <f t="shared" ref="Z37:Z45" si="17">Z36+80</f>
         <v>880</v>
       </c>
-      <c r="W37" s="2">
+      <c r="AA37" s="2">
         <v>7</v>
       </c>
-      <c r="X37" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y37" s="2">
+      <c r="AB37" s="2">
+        <v>31</v>
+      </c>
+      <c r="AC37" s="2">
         <f t="shared" si="15"/>
         <v>600</v>
       </c>
-      <c r="Z37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="1"/>
-      <c r="AB37" s="1">
+      <c r="AD37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:28">
+    <row r="38" customHeight="1" spans="1:32">
       <c r="C38" s="1">
         <v>33</v>
       </c>
@@ -4418,86 +4862,98 @@
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G38" s="1">
         <v>33</v>
       </c>
       <c r="H38" s="1">
-        <f t="shared" si="6"/>
-        <v>221760</v>
+        <f t="shared" si="7"/>
+        <v>22176</v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="7"/>
-        <v>11088</v>
+        <f t="shared" si="0"/>
+        <v>64</v>
       </c>
       <c r="J38" s="1">
         <f t="shared" si="10"/>
         <v>20908800</v>
       </c>
       <c r="K38" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>165</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>99</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>66</v>
       </c>
       <c r="N38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>132</v>
       </c>
       <c r="O38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="2">
+        <v>32</v>
+      </c>
+      <c r="P38" s="4">
+        <v>33</v>
+      </c>
+      <c r="Q38" s="2">
         <f t="shared" si="16"/>
         <v>105</v>
       </c>
-      <c r="Q38" s="4">
-        <v>33</v>
-      </c>
       <c r="R38" s="1">
-        <f t="shared" si="4"/>
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="4">
+        <v>0</v>
+      </c>
+      <c r="U38" s="4">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1">
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
-      <c r="T38" s="1">
+      <c r="W38" s="1">
+        <f t="shared" si="6"/>
+        <v>420</v>
+      </c>
+      <c r="X38" s="1">
         <v>42</v>
       </c>
-      <c r="U38" s="1">
+      <c r="Y38" s="1">
         <v>33</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <f t="shared" si="17"/>
         <v>960</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>7</v>
       </c>
-      <c r="X38" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y38" s="2">
-        <f t="shared" ref="Y38:Y45" si="18">Y37+60</f>
+      <c r="AB38" s="2">
+        <v>32</v>
+      </c>
+      <c r="AC38" s="2">
+        <f t="shared" ref="AC38:AC45" si="18">AC37+60</f>
         <v>660</v>
       </c>
-      <c r="Z38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="1"/>
-      <c r="AB38" s="1">
+      <c r="AD38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="1"/>
+      <c r="AF38" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:28">
+    <row r="39" customHeight="1" spans="1:32">
       <c r="C39" s="1">
         <v>34</v>
       </c>
@@ -4508,86 +4964,98 @@
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G39" s="1">
         <v>34</v>
       </c>
       <c r="H39" s="1">
-        <f t="shared" si="6"/>
-        <v>247520</v>
+        <f t="shared" si="7"/>
+        <v>24752</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="7"/>
-        <v>12376</v>
+        <f t="shared" si="0"/>
+        <v>66</v>
       </c>
       <c r="J39" s="1">
         <f t="shared" si="10"/>
         <v>25459200</v>
       </c>
       <c r="K39" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>170</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>102</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>68</v>
       </c>
       <c r="N39" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>136</v>
       </c>
       <c r="O39" s="1">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2">
+        <v>33</v>
+      </c>
+      <c r="P39" s="4">
+        <v>34</v>
+      </c>
+      <c r="Q39" s="2">
         <f t="shared" si="16"/>
         <v>110</v>
       </c>
-      <c r="Q39" s="4">
-        <v>34</v>
-      </c>
       <c r="R39" s="1">
-        <f t="shared" si="4"/>
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="S39" s="1">
+        <v>0</v>
+      </c>
+      <c r="T39" s="4">
+        <v>0</v>
+      </c>
+      <c r="U39" s="4">
+        <v>0</v>
+      </c>
+      <c r="V39" s="1">
         <f t="shared" si="5"/>
         <v>430</v>
       </c>
-      <c r="T39" s="1">
+      <c r="W39" s="1">
+        <f t="shared" si="6"/>
+        <v>430</v>
+      </c>
+      <c r="X39" s="1">
         <v>43</v>
       </c>
-      <c r="U39" s="1">
+      <c r="Y39" s="1">
         <v>34</v>
       </c>
-      <c r="V39" s="2">
+      <c r="Z39" s="2">
         <f t="shared" si="17"/>
         <v>1040</v>
       </c>
-      <c r="W39" s="2">
+      <c r="AA39" s="2">
         <v>7</v>
       </c>
-      <c r="X39" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y39" s="2">
+      <c r="AB39" s="2">
+        <v>33</v>
+      </c>
+      <c r="AC39" s="2">
         <f t="shared" si="18"/>
         <v>720</v>
       </c>
-      <c r="Z39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1">
+      <c r="AD39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="1"/>
+      <c r="AF39" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:28">
+    <row r="40" customHeight="1" spans="1:32">
       <c r="C40" s="1">
         <v>35</v>
       </c>
@@ -4598,86 +5066,98 @@
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G40" s="1">
         <v>35</v>
       </c>
       <c r="H40" s="1">
-        <f t="shared" si="6"/>
-        <v>274400</v>
+        <f t="shared" si="7"/>
+        <v>27440</v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="7"/>
-        <v>13720</v>
+        <f t="shared" si="0"/>
+        <v>68</v>
       </c>
       <c r="J40" s="1">
         <f t="shared" si="10"/>
         <v>30576000</v>
       </c>
       <c r="K40" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>175</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>105</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="N40" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="O40" s="1">
-        <v>0</v>
-      </c>
-      <c r="P40" s="2">
+        <v>34</v>
+      </c>
+      <c r="P40" s="4">
+        <v>35</v>
+      </c>
+      <c r="Q40" s="2">
         <f t="shared" si="16"/>
         <v>115</v>
       </c>
-      <c r="Q40" s="4">
-        <v>35</v>
-      </c>
       <c r="R40" s="1">
-        <f t="shared" si="4"/>
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="S40" s="1">
+        <v>0</v>
+      </c>
+      <c r="T40" s="4">
+        <v>0</v>
+      </c>
+      <c r="U40" s="4">
+        <v>0</v>
+      </c>
+      <c r="V40" s="1">
         <f t="shared" si="5"/>
         <v>440</v>
       </c>
-      <c r="T40" s="1">
+      <c r="W40" s="1">
+        <f t="shared" si="6"/>
+        <v>440</v>
+      </c>
+      <c r="X40" s="1">
         <v>44</v>
       </c>
-      <c r="U40" s="1">
+      <c r="Y40" s="1">
         <v>35</v>
       </c>
-      <c r="V40" s="2">
+      <c r="Z40" s="2">
         <f t="shared" si="17"/>
         <v>1120</v>
       </c>
-      <c r="W40" s="2">
+      <c r="AA40" s="2">
         <v>7</v>
       </c>
-      <c r="X40" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y40" s="2">
+      <c r="AB40" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC40" s="2">
         <f t="shared" si="18"/>
         <v>780</v>
       </c>
-      <c r="Z40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="1"/>
-      <c r="AB40" s="1">
+      <c r="AD40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A41" s="2"/>
       <c r="C41" s="1">
         <v>36</v>
@@ -4689,85 +5169,97 @@
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
       </c>
       <c r="H41" s="1">
-        <f t="shared" si="6"/>
-        <v>345600</v>
+        <f t="shared" si="7"/>
+        <v>34560</v>
       </c>
       <c r="I41" s="1">
-        <f t="shared" si="7"/>
-        <v>17280</v>
+        <f t="shared" si="0"/>
+        <v>70</v>
       </c>
       <c r="J41" s="1">
         <f t="shared" si="10"/>
         <v>36288000</v>
       </c>
       <c r="K41" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>180</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>108</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="N41" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="O41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2">
+        <v>35</v>
+      </c>
+      <c r="P41" s="4">
+        <v>36</v>
+      </c>
+      <c r="Q41" s="2">
         <f t="shared" si="16"/>
         <v>120</v>
       </c>
-      <c r="Q41" s="4">
-        <v>36</v>
-      </c>
       <c r="R41" s="1">
-        <f t="shared" si="4"/>
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="S41" s="1">
+        <v>0</v>
+      </c>
+      <c r="T41" s="4">
+        <v>0</v>
+      </c>
+      <c r="U41" s="4">
+        <v>0</v>
+      </c>
+      <c r="V41" s="1">
         <f t="shared" si="5"/>
         <v>450</v>
       </c>
-      <c r="T41" s="1">
+      <c r="W41" s="1">
+        <f t="shared" si="6"/>
+        <v>450</v>
+      </c>
+      <c r="X41" s="1">
         <v>45</v>
       </c>
-      <c r="U41" s="1">
+      <c r="Y41" s="1">
         <v>36</v>
       </c>
-      <c r="V41" s="2">
+      <c r="Z41" s="2">
         <f t="shared" si="17"/>
         <v>1200</v>
       </c>
-      <c r="W41" s="2">
+      <c r="AA41" s="2">
         <v>8</v>
       </c>
-      <c r="X41" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y41" s="2">
+      <c r="AB41" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC41" s="2">
         <f t="shared" si="18"/>
         <v>840</v>
       </c>
-      <c r="Z41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="1">
+      <c r="AD41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A42" s="2"/>
       <c r="C42" s="1">
         <v>37</v>
@@ -4779,85 +5271,97 @@
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G42" s="1">
         <v>2</v>
       </c>
       <c r="H42" s="1">
-        <f t="shared" si="6"/>
-        <v>378880</v>
+        <f t="shared" si="7"/>
+        <v>37888</v>
       </c>
       <c r="I42" s="1">
-        <f t="shared" si="7"/>
-        <v>18944</v>
+        <f t="shared" si="0"/>
+        <v>72</v>
       </c>
       <c r="J42" s="1">
         <f t="shared" si="10"/>
         <v>42624000</v>
       </c>
       <c r="K42" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>185</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>111</v>
       </c>
       <c r="M42" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74</v>
       </c>
       <c r="N42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>148</v>
       </c>
       <c r="O42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" s="2">
+        <v>36</v>
+      </c>
+      <c r="P42" s="4">
+        <v>37</v>
+      </c>
+      <c r="Q42" s="2">
         <f t="shared" si="16"/>
         <v>125</v>
       </c>
-      <c r="Q42" s="4">
-        <v>37</v>
-      </c>
       <c r="R42" s="1">
-        <f t="shared" si="4"/>
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="S42" s="1">
+        <v>0</v>
+      </c>
+      <c r="T42" s="4">
+        <v>0</v>
+      </c>
+      <c r="U42" s="4">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1">
         <f t="shared" si="5"/>
         <v>460</v>
       </c>
-      <c r="T42" s="1">
+      <c r="W42" s="1">
+        <f t="shared" si="6"/>
+        <v>460</v>
+      </c>
+      <c r="X42" s="1">
         <v>46</v>
       </c>
-      <c r="U42" s="1">
+      <c r="Y42" s="1">
         <v>37</v>
       </c>
-      <c r="V42" s="2">
+      <c r="Z42" s="2">
         <f t="shared" si="17"/>
         <v>1280</v>
       </c>
-      <c r="W42" s="2">
+      <c r="AA42" s="2">
         <v>8</v>
       </c>
-      <c r="X42" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y42" s="2">
+      <c r="AB42" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC42" s="2">
         <f t="shared" si="18"/>
         <v>900</v>
       </c>
-      <c r="Z42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="1">
+      <c r="AD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A43" s="2"/>
       <c r="C43" s="1">
         <v>38</v>
@@ -4869,85 +5373,97 @@
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G43" s="1">
         <v>3</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" si="6"/>
-        <v>413440</v>
+        <f t="shared" si="7"/>
+        <v>41344</v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="7"/>
-        <v>20672</v>
+        <f t="shared" si="0"/>
+        <v>74</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" si="10"/>
         <v>49612800</v>
       </c>
       <c r="K43" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>190</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>114</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>76</v>
       </c>
       <c r="N43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>152</v>
       </c>
       <c r="O43" s="1">
-        <v>0</v>
-      </c>
-      <c r="P43" s="2">
+        <v>37</v>
+      </c>
+      <c r="P43" s="4">
+        <v>38</v>
+      </c>
+      <c r="Q43" s="2">
         <f t="shared" si="16"/>
         <v>130</v>
       </c>
-      <c r="Q43" s="4">
-        <v>38</v>
-      </c>
       <c r="R43" s="1">
-        <f t="shared" si="4"/>
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="S43" s="1">
+        <v>0</v>
+      </c>
+      <c r="T43" s="4">
+        <v>0</v>
+      </c>
+      <c r="U43" s="4">
+        <v>0</v>
+      </c>
+      <c r="V43" s="1">
         <f t="shared" si="5"/>
         <v>470</v>
       </c>
-      <c r="T43" s="1">
+      <c r="W43" s="1">
+        <f t="shared" si="6"/>
+        <v>470</v>
+      </c>
+      <c r="X43" s="1">
         <v>47</v>
       </c>
-      <c r="U43" s="1">
+      <c r="Y43" s="1">
         <v>38</v>
       </c>
-      <c r="V43" s="2">
+      <c r="Z43" s="2">
         <f t="shared" si="17"/>
         <v>1360</v>
       </c>
-      <c r="W43" s="2">
+      <c r="AA43" s="2">
         <v>8</v>
       </c>
-      <c r="X43" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y43" s="2">
+      <c r="AB43" s="2">
+        <v>37</v>
+      </c>
+      <c r="AC43" s="2">
         <f t="shared" si="18"/>
         <v>960</v>
       </c>
-      <c r="Z43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="1">
+      <c r="AD43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A44" s="2"/>
       <c r="C44" s="1">
         <v>39</v>
@@ -4959,85 +5475,97 @@
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G44" s="1">
         <v>4</v>
       </c>
       <c r="H44" s="1">
-        <f t="shared" si="6"/>
-        <v>449280</v>
+        <f t="shared" si="7"/>
+        <v>44928</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="7"/>
-        <v>22464</v>
+        <f t="shared" si="0"/>
+        <v>76</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" si="10"/>
         <v>57283200</v>
       </c>
       <c r="K44" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>195</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>117</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>78</v>
       </c>
       <c r="N44" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>156</v>
       </c>
       <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="2">
+        <v>38</v>
+      </c>
+      <c r="P44" s="4">
+        <v>39</v>
+      </c>
+      <c r="Q44" s="2">
         <f t="shared" si="16"/>
         <v>135</v>
       </c>
-      <c r="Q44" s="4">
-        <v>39</v>
-      </c>
       <c r="R44" s="1">
-        <f t="shared" si="4"/>
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="4">
+        <v>0</v>
+      </c>
+      <c r="U44" s="4">
+        <v>0</v>
+      </c>
+      <c r="V44" s="1">
         <f t="shared" si="5"/>
         <v>480</v>
       </c>
-      <c r="T44" s="1">
+      <c r="W44" s="1">
+        <f t="shared" si="6"/>
+        <v>480</v>
+      </c>
+      <c r="X44" s="1">
         <v>48</v>
       </c>
-      <c r="U44" s="1">
+      <c r="Y44" s="1">
         <v>39</v>
       </c>
-      <c r="V44" s="2">
+      <c r="Z44" s="2">
         <f t="shared" si="17"/>
         <v>1440</v>
       </c>
-      <c r="W44" s="2">
+      <c r="AA44" s="2">
         <v>8</v>
       </c>
-      <c r="X44" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y44" s="2">
+      <c r="AB44" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC44" s="2">
         <f t="shared" si="18"/>
         <v>1020</v>
       </c>
-      <c r="Z44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="1">
+      <c r="AD44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A45" s="2"/>
       <c r="C45" s="1">
         <v>40</v>
@@ -5049,100 +5577,114 @@
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G45" s="1">
         <v>5</v>
       </c>
       <c r="H45" s="1">
-        <f t="shared" si="6"/>
-        <v>486400</v>
+        <f t="shared" si="7"/>
+        <v>48640</v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="7"/>
-        <v>24320</v>
+        <f t="shared" si="0"/>
+        <v>78</v>
       </c>
       <c r="J45" s="1">
         <f t="shared" si="10"/>
         <v>65664000</v>
       </c>
       <c r="K45" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="N45" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>160</v>
       </c>
       <c r="O45" s="1">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2">
+        <v>39</v>
+      </c>
+      <c r="P45" s="4">
+        <v>40</v>
+      </c>
+      <c r="Q45" s="2">
         <f t="shared" si="16"/>
         <v>140</v>
       </c>
-      <c r="Q45" s="4">
-        <v>40</v>
-      </c>
       <c r="R45" s="1">
-        <f t="shared" si="4"/>
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="S45" s="1">
+        <v>0</v>
+      </c>
+      <c r="T45" s="4">
+        <v>0</v>
+      </c>
+      <c r="U45" s="4">
+        <v>0</v>
+      </c>
+      <c r="V45" s="1">
         <f t="shared" si="5"/>
         <v>490</v>
       </c>
-      <c r="T45" s="1">
+      <c r="W45" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X45" s="1">
         <v>49</v>
       </c>
-      <c r="U45" s="1">
+      <c r="Y45" s="1">
         <v>40</v>
       </c>
-      <c r="V45" s="2">
+      <c r="Z45" s="2">
         <f t="shared" si="17"/>
         <v>1520</v>
       </c>
-      <c r="W45" s="2">
+      <c r="AA45" s="2">
         <v>8</v>
       </c>
-      <c r="X45" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y45" s="2">
+      <c r="AB45" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC45" s="2">
         <f t="shared" si="18"/>
         <v>1080</v>
       </c>
-      <c r="Z45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="1">
+      <c r="AD45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:32">
       <c r="A46" s="2"/>
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="2"/>
-      <c r="X46" s="2"/>
-      <c r="Y46" s="2"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="1"/>
+      <c r="W46" s="1"/>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="2"/>
+      <c r="AA46" s="2"/>
+      <c r="AB46" s="2"/>
+      <c r="AC46" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:Q5 Z3:AB5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N3 O3 P3 Q3 R3 S3 T3 U3 C4:G4 H4 I4:N4 O4 P4 Q4 R4 S4 T4 U4 C5:N5 O5 P5 Q5 R5 S5 T5 U5 AD3:AF5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -1211,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF46"/>
+  <dimension ref="A1:AG103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1245,7 +1245,7 @@
     <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="2"/>
@@ -1291,8 +1291,11 @@
       <c r="AF1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:32">
+      <c r="AG1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="2"/>
@@ -1338,8 +1341,11 @@
       <c r="AF2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:32">
+      <c r="AG2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1433,7 +1439,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1512,8 +1518,11 @@
       <c r="AF4" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:32">
+      <c r="AG4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -1592,8 +1601,11 @@
       <c r="AF5" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" ht="14" spans="1:32">
+      <c r="AG5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="14" spans="1:33">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1610,10 +1622,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" ref="I6:I45" si="0">AB6*2</f>
+        <f t="shared" ref="I6:I45" si="0">AB6*AG4*Z6/10</f>
         <v>0</v>
       </c>
       <c r="J6" s="1">
@@ -1674,7 +1686,7 @@
         <v>100</v>
       </c>
       <c r="AA6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB6" s="2">
         <v>0</v>
@@ -1689,8 +1701,11 @@
       <c r="AF6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:32">
+      <c r="AG6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:33">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1707,16 +1722,16 @@
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:H45" si="7">Y7*Z7*AA7/10</f>
-        <v>22</v>
+        <f t="shared" ref="H7:H45" si="7">AG9*Z7*AA7/10</f>
+        <v>252</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J7" s="1">
         <f>Y7*Z7*AC7</f>
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="1"/>
@@ -1770,17 +1785,16 @@
         <v>2</v>
       </c>
       <c r="Z7" s="2">
-        <f t="shared" ref="Z7:Z17" si="8">Z6+10</f>
-        <v>110</v>
+        <f>Z6+20</f>
+        <v>120</v>
       </c>
       <c r="AA7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB7" s="2">
         <v>1</v>
       </c>
       <c r="AC7" s="2">
-        <f>AC6+5</f>
         <v>15</v>
       </c>
       <c r="AD7" s="1">
@@ -1790,8 +1804,11 @@
       <c r="AF7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:32">
+      <c r="AG7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:33">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1809,15 +1826,15 @@
       </c>
       <c r="H8" s="1">
         <f t="shared" si="7"/>
-        <v>36</v>
+        <v>770</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="J8" s="1">
         <f>Y8*Z8*AC8</f>
-        <v>7200</v>
+        <v>7560</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="1"/>
@@ -1842,7 +1859,7 @@
         <v>3</v>
       </c>
       <c r="Q8" s="2">
-        <f t="shared" ref="Q8:Q45" si="9">Q7+2</f>
+        <f t="shared" ref="Q8:Q45" si="8">Q7+2</f>
         <v>12</v>
       </c>
       <c r="R8" s="1">
@@ -1872,18 +1889,18 @@
         <v>3</v>
       </c>
       <c r="Z8" s="2">
-        <f t="shared" si="8"/>
-        <v>120</v>
+        <f>Z7+20</f>
+        <v>140</v>
       </c>
       <c r="AA8" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB8" s="2">
         <v>2</v>
       </c>
       <c r="AC8" s="2">
-        <f>AC7+5</f>
-        <v>20</v>
+        <f t="shared" ref="AC8:AC45" si="9">AC7+AG7</f>
+        <v>18</v>
       </c>
       <c r="AD8" s="1">
         <v>0</v>
@@ -1892,8 +1909,11 @@
       <c r="AF8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:32">
+      <c r="AG8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:33">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1911,15 +1931,15 @@
       </c>
       <c r="H9" s="1">
         <f t="shared" si="7"/>
-        <v>52</v>
+        <v>1456</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>144</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" ref="J7:J45" si="10">Y9*Z9*AC9</f>
-        <v>13000</v>
+        <v>14720</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="1"/>
@@ -1944,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="Q9" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="R9" s="1">
@@ -1974,18 +1994,18 @@
         <v>4</v>
       </c>
       <c r="Z9" s="2">
-        <f t="shared" si="8"/>
-        <v>130</v>
+        <f>Z8+20</f>
+        <v>160</v>
       </c>
       <c r="AA9" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB9" s="2">
         <v>3</v>
       </c>
       <c r="AC9" s="2">
-        <f>AC8+5</f>
-        <v>25</v>
+        <f t="shared" si="9"/>
+        <v>23</v>
       </c>
       <c r="AD9" s="1">
         <v>0</v>
@@ -1994,8 +2014,11 @@
       <c r="AF9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:32">
+      <c r="AG9" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:33">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -2013,15 +2036,15 @@
       </c>
       <c r="H10" s="1">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>3366</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>360</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" si="10"/>
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="1"/>
@@ -2046,7 +2069,7 @@
         <v>5</v>
       </c>
       <c r="Q10" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="R10" s="1">
@@ -2076,17 +2099,17 @@
         <v>5</v>
       </c>
       <c r="Z10" s="2">
-        <f t="shared" si="8"/>
-        <v>140</v>
+        <f>Z9+20</f>
+        <v>180</v>
       </c>
       <c r="AA10" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AB10" s="2">
         <v>4</v>
       </c>
       <c r="AC10" s="2">
-        <f>AC9+5</f>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="AD10" s="1">
@@ -2096,8 +2119,11 @@
       <c r="AF10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:32">
+      <c r="AG10" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:33">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -2115,15 +2141,15 @@
       </c>
       <c r="H11" s="1">
         <f t="shared" si="7"/>
-        <v>180</v>
+        <v>4940</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>700</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" si="10"/>
-        <v>36000</v>
+        <v>49200</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" si="1"/>
@@ -2148,7 +2174,7 @@
         <v>6</v>
       </c>
       <c r="Q11" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="R11" s="1">
@@ -2178,18 +2204,18 @@
         <v>6</v>
       </c>
       <c r="Z11" s="2">
-        <f t="shared" si="8"/>
-        <v>150</v>
+        <f>Z10+20</f>
+        <v>200</v>
       </c>
       <c r="AA11" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AB11" s="2">
         <v>5</v>
       </c>
       <c r="AC11" s="2">
-        <f t="shared" ref="AC11:AC20" si="11">AC10+10</f>
-        <v>40</v>
+        <f t="shared" si="9"/>
+        <v>41</v>
       </c>
       <c r="AD11" s="1">
         <v>0</v>
@@ -2198,8 +2224,11 @@
       <c r="AF11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:32">
+      <c r="AG11" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:33">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -2217,15 +2246,15 @@
       </c>
       <c r="H12" s="1">
         <f t="shared" si="7"/>
-        <v>224</v>
+        <v>9384</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>1584</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="10"/>
-        <v>56000</v>
+        <v>90720</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="1"/>
@@ -2250,7 +2279,7 @@
         <v>7</v>
       </c>
       <c r="Q12" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="R12" s="1">
@@ -2280,18 +2309,18 @@
         <v>7</v>
       </c>
       <c r="Z12" s="2">
-        <f t="shared" si="8"/>
-        <v>160</v>
+        <f>Z11+40</f>
+        <v>240</v>
       </c>
       <c r="AA12" s="2">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AB12" s="2">
         <v>6</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" si="11"/>
-        <v>50</v>
+        <f t="shared" si="9"/>
+        <v>54</v>
       </c>
       <c r="AD12" s="1">
         <v>0</v>
@@ -2300,8 +2329,11 @@
       <c r="AF12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:32">
+      <c r="AG12" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:33">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -2319,15 +2351,15 @@
       </c>
       <c r="H13" s="1">
         <f t="shared" si="7"/>
-        <v>272</v>
+        <v>15428</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>2548</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" si="10"/>
-        <v>81600</v>
+        <v>159040</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="1"/>
@@ -2352,7 +2384,7 @@
         <v>8</v>
       </c>
       <c r="Q13" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="R13" s="1">
@@ -2382,18 +2414,18 @@
         <v>8</v>
       </c>
       <c r="Z13" s="2">
-        <f t="shared" si="8"/>
-        <v>170</v>
+        <f>Z12+40</f>
+        <v>280</v>
       </c>
       <c r="AA13" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="AB13" s="2">
         <v>7</v>
       </c>
       <c r="AC13" s="2">
-        <f t="shared" si="11"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>71</v>
       </c>
       <c r="AD13" s="1">
         <v>0</v>
@@ -2402,8 +2434,11 @@
       <c r="AF13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:32">
+      <c r="AG13" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:33">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -2421,15 +2456,15 @@
       </c>
       <c r="H14" s="1">
         <f t="shared" si="7"/>
-        <v>324</v>
+        <v>22816</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>4352</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" si="10"/>
-        <v>113400</v>
+        <v>259200</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="1"/>
@@ -2454,7 +2489,7 @@
         <v>9</v>
       </c>
       <c r="Q14" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="R14" s="1">
@@ -2484,18 +2519,18 @@
         <v>9</v>
       </c>
       <c r="Z14" s="2">
-        <f t="shared" si="8"/>
-        <v>180</v>
+        <f>Z13+40</f>
+        <v>320</v>
       </c>
       <c r="AA14" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="AB14" s="2">
         <v>8</v>
       </c>
       <c r="AC14" s="2">
-        <f t="shared" si="11"/>
-        <v>70</v>
+        <f t="shared" si="9"/>
+        <v>90</v>
       </c>
       <c r="AD14" s="1">
         <v>0</v>
@@ -2504,8 +2539,11 @@
       <c r="AF14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:32">
+      <c r="AG14" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:33">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -2523,15 +2561,15 @@
       </c>
       <c r="H15" s="1">
         <f t="shared" si="7"/>
-        <v>380</v>
+        <v>38628</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>6156</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" si="10"/>
-        <v>152000</v>
+        <v>406800</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="1"/>
@@ -2556,7 +2594,7 @@
         <v>10</v>
       </c>
       <c r="Q15" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>26</v>
       </c>
       <c r="R15" s="1">
@@ -2586,18 +2624,18 @@
         <v>10</v>
       </c>
       <c r="Z15" s="2">
-        <f t="shared" si="8"/>
-        <v>190</v>
+        <f>Z14+40</f>
+        <v>360</v>
       </c>
       <c r="AA15" s="2">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="AB15" s="2">
         <v>9</v>
       </c>
       <c r="AC15" s="2">
-        <f t="shared" si="11"/>
-        <v>80</v>
+        <f t="shared" si="9"/>
+        <v>113</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
@@ -2606,8 +2644,11 @@
       <c r="AF15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:32">
+      <c r="AG15" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:33">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2625,15 +2666,15 @@
       </c>
       <c r="H16" s="1">
         <f t="shared" si="7"/>
-        <v>660</v>
+        <v>50840</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>9200</v>
       </c>
       <c r="J16" s="1">
         <f t="shared" si="10"/>
-        <v>198000</v>
+        <v>624800</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="1"/>
@@ -2658,7 +2699,7 @@
         <v>11</v>
       </c>
       <c r="Q16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="R16" s="1">
@@ -2688,18 +2729,18 @@
         <v>11</v>
       </c>
       <c r="Z16" s="2">
-        <f t="shared" si="8"/>
-        <v>200</v>
+        <f>Z15+40</f>
+        <v>400</v>
       </c>
       <c r="AA16" s="2">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="AB16" s="2">
         <v>10</v>
       </c>
       <c r="AC16" s="2">
-        <f t="shared" si="11"/>
-        <v>90</v>
+        <f t="shared" si="9"/>
+        <v>142</v>
       </c>
       <c r="AD16" s="1">
         <v>0</v>
@@ -2708,8 +2749,11 @@
       <c r="AF16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:32">
+      <c r="AG16" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:33">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2727,15 +2771,15 @@
       </c>
       <c r="H17" s="1">
         <f t="shared" si="7"/>
-        <v>792</v>
+        <v>79550</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>15950</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" si="10"/>
-        <v>264000</v>
+        <v>1038000</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="1"/>
@@ -2760,7 +2804,7 @@
         <v>12</v>
       </c>
       <c r="Q17" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="R17" s="1">
@@ -2790,18 +2834,18 @@
         <v>12</v>
       </c>
       <c r="Z17" s="2">
-        <f t="shared" ref="Z17:Z30" si="12">Z16+20</f>
-        <v>220</v>
+        <f>Z16+100</f>
+        <v>500</v>
       </c>
       <c r="AA17" s="2">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="AB17" s="2">
         <v>11</v>
       </c>
       <c r="AC17" s="2">
-        <f t="shared" si="11"/>
-        <v>100</v>
+        <f t="shared" si="9"/>
+        <v>173</v>
       </c>
       <c r="AD17" s="1">
         <v>0</v>
@@ -2810,8 +2854,11 @@
       <c r="AF17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:32">
+      <c r="AG17" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:33">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -2829,15 +2876,15 @@
       </c>
       <c r="H18" s="1">
         <f t="shared" si="7"/>
-        <v>936</v>
+        <v>115620</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22320</v>
       </c>
       <c r="J18" s="1">
         <f t="shared" si="10"/>
-        <v>374400</v>
+        <v>1638000</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" si="1"/>
@@ -2862,7 +2909,7 @@
         <v>13</v>
       </c>
       <c r="Q18" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="R18" s="1">
@@ -2892,18 +2939,18 @@
         <v>13</v>
       </c>
       <c r="Z18" s="2">
-        <f t="shared" si="12"/>
-        <v>240</v>
+        <f>Z17+100</f>
+        <v>600</v>
       </c>
       <c r="AA18" s="2">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="AB18" s="2">
         <v>12</v>
       </c>
       <c r="AC18" s="2">
-        <f t="shared" ref="AC18:AC30" si="13">AC17+20</f>
-        <v>120</v>
+        <f t="shared" si="9"/>
+        <v>210</v>
       </c>
       <c r="AD18" s="1">
         <v>0</v>
@@ -2912,8 +2959,11 @@
       <c r="AF18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:32">
+      <c r="AG18" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:33">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -2931,15 +2981,15 @@
       </c>
       <c r="H19" s="1">
         <f t="shared" si="7"/>
-        <v>1092</v>
+        <v>159530</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>33670</v>
       </c>
       <c r="J19" s="1">
         <f t="shared" si="10"/>
-        <v>509600</v>
+        <v>2459800</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" si="1"/>
@@ -2964,7 +3014,7 @@
         <v>14</v>
       </c>
       <c r="Q19" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="R19" s="1">
@@ -2994,18 +3044,18 @@
         <v>14</v>
       </c>
       <c r="Z19" s="2">
-        <f t="shared" si="12"/>
-        <v>260</v>
+        <f>Z18+100</f>
+        <v>700</v>
       </c>
       <c r="AA19" s="2">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="AB19" s="2">
         <v>13</v>
       </c>
       <c r="AC19" s="2">
-        <f t="shared" si="13"/>
-        <v>140</v>
+        <f t="shared" si="9"/>
+        <v>251</v>
       </c>
       <c r="AD19" s="1">
         <v>0</v>
@@ -3014,8 +3064,11 @@
       <c r="AF19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:32">
+      <c r="AG19" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:33">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -3033,15 +3086,15 @@
       </c>
       <c r="H20" s="1">
         <f t="shared" si="7"/>
-        <v>1260</v>
+        <v>221840</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>45920</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" si="10"/>
-        <v>672000</v>
+        <v>3528000</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" si="1"/>
@@ -3066,7 +3119,7 @@
         <v>15</v>
       </c>
       <c r="Q20" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>36</v>
       </c>
       <c r="R20" s="1">
@@ -3096,18 +3149,18 @@
         <v>15</v>
       </c>
       <c r="Z20" s="2">
-        <f t="shared" si="12"/>
-        <v>280</v>
+        <f>Z19+100</f>
+        <v>800</v>
       </c>
       <c r="AA20" s="2">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="AB20" s="2">
         <v>14</v>
       </c>
       <c r="AC20" s="2">
-        <f t="shared" si="13"/>
-        <v>160</v>
+        <f t="shared" si="9"/>
+        <v>294</v>
       </c>
       <c r="AD20" s="1">
         <v>0</v>
@@ -3116,8 +3169,11 @@
       <c r="AF20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:32">
+      <c r="AG20" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:33">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -3135,15 +3191,15 @@
       </c>
       <c r="H21" s="1">
         <f t="shared" si="7"/>
-        <v>1920</v>
+        <v>290970</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>58050</v>
       </c>
       <c r="J21" s="1">
         <f t="shared" si="10"/>
-        <v>864000</v>
+        <v>4910400</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" si="1"/>
@@ -3168,7 +3224,7 @@
         <v>16</v>
       </c>
       <c r="Q21" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="R21" s="1">
@@ -3198,18 +3254,18 @@
         <v>16</v>
       </c>
       <c r="Z21" s="2">
-        <f t="shared" si="12"/>
-        <v>300</v>
+        <f>Z20+100</f>
+        <v>900</v>
       </c>
       <c r="AA21" s="2">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="AB21" s="2">
         <v>15</v>
       </c>
       <c r="AC21" s="2">
-        <f t="shared" si="13"/>
-        <v>180</v>
+        <f t="shared" si="9"/>
+        <v>341</v>
       </c>
       <c r="AD21" s="1">
         <v>0</v>
@@ -3218,8 +3274,11 @@
       <c r="AF21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:32">
+      <c r="AG21" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:33">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -3237,15 +3296,15 @@
       </c>
       <c r="H22" s="1">
         <f t="shared" si="7"/>
-        <v>2176</v>
+        <v>395300</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>75200</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" si="10"/>
-        <v>1088000</v>
+        <v>6698000</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" si="1"/>
@@ -3270,7 +3329,7 @@
         <v>17</v>
       </c>
       <c r="Q22" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="R22" s="1">
@@ -3300,18 +3359,18 @@
         <v>17</v>
       </c>
       <c r="Z22" s="2">
-        <f t="shared" si="12"/>
-        <v>320</v>
+        <f>Z21+100</f>
+        <v>1000</v>
       </c>
       <c r="AA22" s="2">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="AB22" s="2">
         <v>16</v>
       </c>
       <c r="AC22" s="2">
-        <f t="shared" si="13"/>
-        <v>200</v>
+        <f t="shared" si="9"/>
+        <v>394</v>
       </c>
       <c r="AD22" s="1">
         <v>0</v>
@@ -3320,8 +3379,11 @@
       <c r="AF22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:32">
+      <c r="AG22" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:33">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -3339,15 +3401,15 @@
       </c>
       <c r="H23" s="1">
         <f t="shared" si="7"/>
-        <v>2448</v>
+        <v>519720</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>108120</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" si="10"/>
-        <v>1346400</v>
+        <v>9784800</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" si="1"/>
@@ -3372,7 +3434,7 @@
         <v>18</v>
       </c>
       <c r="Q23" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>42</v>
       </c>
       <c r="R23" s="1">
@@ -3402,18 +3464,18 @@
         <v>18</v>
       </c>
       <c r="Z23" s="2">
-        <f t="shared" si="12"/>
-        <v>340</v>
+        <f>Z22+200</f>
+        <v>1200</v>
       </c>
       <c r="AA23" s="2">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="AB23" s="2">
         <v>17</v>
       </c>
       <c r="AC23" s="2">
-        <f t="shared" si="13"/>
-        <v>220</v>
+        <f t="shared" si="9"/>
+        <v>453</v>
       </c>
       <c r="AD23" s="1">
         <v>0</v>
@@ -3422,8 +3484,11 @@
       <c r="AF23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:32">
+      <c r="AG23" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:33">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -3441,15 +3506,15 @@
       </c>
       <c r="H24" s="1">
         <f t="shared" si="7"/>
-        <v>2736</v>
+        <v>684740</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>148680</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" si="10"/>
-        <v>1641600</v>
+        <v>13672400</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" si="1"/>
@@ -3474,7 +3539,7 @@
         <v>19</v>
       </c>
       <c r="Q24" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>44</v>
       </c>
       <c r="R24" s="1">
@@ -3504,18 +3569,18 @@
         <v>19</v>
       </c>
       <c r="Z24" s="2">
-        <f t="shared" si="12"/>
-        <v>360</v>
+        <f>Z23+200</f>
+        <v>1400</v>
       </c>
       <c r="AA24" s="2">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="AB24" s="2">
         <v>18</v>
       </c>
       <c r="AC24" s="2">
-        <f t="shared" si="13"/>
-        <v>240</v>
+        <f t="shared" si="9"/>
+        <v>514</v>
       </c>
       <c r="AD24" s="1">
         <v>0</v>
@@ -3524,8 +3589,11 @@
       <c r="AF24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:32">
+      <c r="AG24" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:33">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -3543,15 +3611,15 @@
       </c>
       <c r="H25" s="1">
         <f t="shared" si="7"/>
-        <v>3040</v>
+        <v>897440</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>185440</v>
       </c>
       <c r="J25" s="1">
         <f t="shared" si="10"/>
-        <v>1976000</v>
+        <v>18592000</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" si="1"/>
@@ -3576,7 +3644,7 @@
         <v>20</v>
       </c>
       <c r="Q25" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>46</v>
       </c>
       <c r="R25" s="1">
@@ -3606,18 +3674,18 @@
         <v>20</v>
       </c>
       <c r="Z25" s="2">
-        <f t="shared" si="12"/>
-        <v>380</v>
+        <f>Z24+200</f>
+        <v>1600</v>
       </c>
       <c r="AA25" s="2">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="AB25" s="2">
         <v>19</v>
       </c>
       <c r="AC25" s="2">
-        <f t="shared" si="13"/>
-        <v>260</v>
+        <f t="shared" si="9"/>
+        <v>581</v>
       </c>
       <c r="AD25" s="1">
         <v>0</v>
@@ -3626,8 +3694,11 @@
       <c r="AF25" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:32">
+      <c r="AG25" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:33">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -3645,15 +3716,15 @@
       </c>
       <c r="H26" s="1">
         <f t="shared" si="7"/>
-        <v>4200</v>
+        <v>1090620</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>241200</v>
       </c>
       <c r="J26" s="1">
         <f t="shared" si="10"/>
-        <v>2352000</v>
+        <v>24645600</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" si="1"/>
@@ -3678,7 +3749,7 @@
         <v>21</v>
       </c>
       <c r="Q26" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>48</v>
       </c>
       <c r="R26" s="1">
@@ -3708,18 +3779,18 @@
         <v>21</v>
       </c>
       <c r="Z26" s="2">
-        <f t="shared" si="12"/>
-        <v>400</v>
+        <f>Z25+200</f>
+        <v>1800</v>
       </c>
       <c r="AA26" s="2">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="AB26" s="2">
         <v>20</v>
       </c>
       <c r="AC26" s="2">
-        <f t="shared" si="13"/>
-        <v>280</v>
+        <f t="shared" si="9"/>
+        <v>652</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
@@ -3728,8 +3799,11 @@
       <c r="AF26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:32">
+      <c r="AG26" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:33">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -3747,15 +3821,15 @@
       </c>
       <c r="H27" s="1">
         <f t="shared" si="7"/>
-        <v>4840</v>
+        <v>1406200</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>298200</v>
       </c>
       <c r="J27" s="1">
         <f t="shared" si="10"/>
-        <v>2904000</v>
+        <v>31900000</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" si="1"/>
@@ -3780,7 +3854,7 @@
         <v>22</v>
       </c>
       <c r="Q27" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="R27" s="1">
@@ -3810,18 +3884,18 @@
         <v>22</v>
       </c>
       <c r="Z27" s="2">
-        <f t="shared" ref="Z27:Z38" si="14">Z26+40</f>
-        <v>440</v>
+        <f>Z26+200</f>
+        <v>2000</v>
       </c>
       <c r="AA27" s="2">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="AB27" s="2">
         <v>21</v>
       </c>
       <c r="AC27" s="2">
-        <f t="shared" si="13"/>
-        <v>300</v>
+        <f t="shared" si="9"/>
+        <v>725</v>
       </c>
       <c r="AD27" s="1">
         <v>0</v>
@@ -3830,8 +3904,11 @@
       <c r="AF27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:32">
+      <c r="AG27" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:33">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -3849,15 +3926,15 @@
       </c>
       <c r="H28" s="1">
         <f t="shared" si="7"/>
-        <v>5520</v>
+        <v>2012750</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>401500</v>
       </c>
       <c r="J28" s="1">
         <f t="shared" si="10"/>
-        <v>3643200</v>
+        <v>46230000</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="1"/>
@@ -3912,18 +3989,18 @@
         <v>23</v>
       </c>
       <c r="Z28" s="2">
-        <f t="shared" si="14"/>
-        <v>480</v>
+        <f>Z27+500</f>
+        <v>2500</v>
       </c>
       <c r="AA28" s="2">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="AB28" s="2">
         <v>22</v>
       </c>
       <c r="AC28" s="2">
-        <f t="shared" ref="AC28:AC45" si="15">AC27+30</f>
-        <v>330</v>
+        <f t="shared" si="9"/>
+        <v>804</v>
       </c>
       <c r="AD28" s="1">
         <v>0</v>
@@ -3932,8 +4009,11 @@
       <c r="AF28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:32">
+      <c r="AG28" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:33">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -3951,15 +4031,15 @@
       </c>
       <c r="H29" s="1">
         <f t="shared" si="7"/>
-        <v>6240</v>
+        <v>2696700</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>545100</v>
       </c>
       <c r="J29" s="1">
         <f t="shared" si="10"/>
-        <v>4492800</v>
+        <v>63864000</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" si="1"/>
@@ -3984,7 +4064,7 @@
         <v>24</v>
       </c>
       <c r="Q29" s="2">
-        <f t="shared" ref="Q29:Q45" si="16">Q28+5</f>
+        <f t="shared" ref="Q29:Q45" si="11">Q28+5</f>
         <v>60</v>
       </c>
       <c r="R29" s="1">
@@ -4014,18 +4094,18 @@
         <v>24</v>
       </c>
       <c r="Z29" s="2">
-        <f t="shared" si="14"/>
-        <v>520</v>
+        <f>Z28+500</f>
+        <v>3000</v>
       </c>
       <c r="AA29" s="2">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="AB29" s="2">
         <v>23</v>
       </c>
       <c r="AC29" s="2">
-        <f t="shared" si="15"/>
-        <v>360</v>
+        <f t="shared" si="9"/>
+        <v>887</v>
       </c>
       <c r="AD29" s="1">
         <v>0</v>
@@ -4034,8 +4114,11 @@
       <c r="AF29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:32">
+      <c r="AG29" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:33">
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -4053,15 +4136,15 @@
       </c>
       <c r="H30" s="1">
         <f t="shared" si="7"/>
-        <v>7000</v>
+        <v>3496850</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>697200</v>
       </c>
       <c r="J30" s="1">
         <f t="shared" si="10"/>
-        <v>5460000</v>
+        <v>85400000</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="1"/>
@@ -4086,7 +4169,7 @@
         <v>25</v>
       </c>
       <c r="Q30" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>65</v>
       </c>
       <c r="R30" s="1">
@@ -4116,18 +4199,18 @@
         <v>25</v>
       </c>
       <c r="Z30" s="2">
-        <f t="shared" si="14"/>
-        <v>560</v>
+        <f>Z29+500</f>
+        <v>3500</v>
       </c>
       <c r="AA30" s="2">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="AB30" s="2">
         <v>24</v>
       </c>
       <c r="AC30" s="2">
-        <f t="shared" si="15"/>
-        <v>390</v>
+        <f t="shared" si="9"/>
+        <v>976</v>
       </c>
       <c r="AD30" s="1">
         <v>0</v>
@@ -4136,8 +4219,11 @@
       <c r="AF30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:32">
+      <c r="AG30" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:33">
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -4155,15 +4241,15 @@
       </c>
       <c r="H31" s="1">
         <f t="shared" si="7"/>
-        <v>9360</v>
+        <v>4322800</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>890000</v>
       </c>
       <c r="J31" s="1">
         <f t="shared" si="10"/>
-        <v>6552000</v>
+        <v>111592000</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" si="1"/>
@@ -4188,7 +4274,7 @@
         <v>26</v>
       </c>
       <c r="Q31" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>70</v>
       </c>
       <c r="R31" s="1">
@@ -4218,18 +4304,18 @@
         <v>26</v>
       </c>
       <c r="Z31" s="2">
-        <f t="shared" si="14"/>
-        <v>600</v>
+        <f>Z30+500</f>
+        <v>4000</v>
       </c>
       <c r="AA31" s="2">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="AB31" s="2">
         <v>25</v>
       </c>
       <c r="AC31" s="2">
-        <f t="shared" si="15"/>
-        <v>420</v>
+        <f t="shared" si="9"/>
+        <v>1073</v>
       </c>
       <c r="AD31" s="1">
         <v>0</v>
@@ -4238,8 +4324,11 @@
       <c r="AF31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:32">
+      <c r="AG31" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:33">
       <c r="C32" s="1">
         <v>27</v>
       </c>
@@ -4257,15 +4346,15 @@
       </c>
       <c r="H32" s="1">
         <f t="shared" si="7"/>
-        <v>10368</v>
+        <v>5052150</v>
       </c>
       <c r="I32" s="1">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>1134900</v>
       </c>
       <c r="J32" s="1">
         <f t="shared" si="10"/>
-        <v>7776000</v>
+        <v>142641000</v>
       </c>
       <c r="K32" s="1">
         <f t="shared" si="1"/>
@@ -4290,7 +4379,7 @@
         <v>27</v>
       </c>
       <c r="Q32" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>75</v>
       </c>
       <c r="R32" s="1">
@@ -4320,18 +4409,18 @@
         <v>27</v>
       </c>
       <c r="Z32" s="2">
-        <f t="shared" si="14"/>
-        <v>640</v>
+        <f>Z31+500</f>
+        <v>4500</v>
       </c>
       <c r="AA32" s="2">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="AB32" s="2">
         <v>26</v>
       </c>
       <c r="AC32" s="2">
-        <f t="shared" si="15"/>
-        <v>450</v>
+        <f t="shared" si="9"/>
+        <v>1174</v>
       </c>
       <c r="AD32" s="1">
         <v>0</v>
@@ -4340,8 +4429,11 @@
       <c r="AF32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:32">
+      <c r="AG32" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:33">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -4359,15 +4451,15 @@
       </c>
       <c r="H33" s="1">
         <f t="shared" si="7"/>
-        <v>11424</v>
+        <v>6045500</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>1363500</v>
       </c>
       <c r="J33" s="1">
         <f t="shared" si="10"/>
-        <v>9139200</v>
+        <v>178780000</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" si="1"/>
@@ -4392,7 +4484,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>80</v>
       </c>
       <c r="R33" s="1">
@@ -4422,18 +4514,18 @@
         <v>28</v>
       </c>
       <c r="Z33" s="2">
-        <f t="shared" si="14"/>
-        <v>680</v>
+        <f>Z32+500</f>
+        <v>5000</v>
       </c>
       <c r="AA33" s="2">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="AB33" s="2">
         <v>27</v>
       </c>
       <c r="AC33" s="2">
-        <f t="shared" si="15"/>
-        <v>480</v>
+        <f t="shared" si="9"/>
+        <v>1277</v>
       </c>
       <c r="AD33" s="1">
         <v>0</v>
@@ -4442,8 +4534,11 @@
       <c r="AF33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:32">
+      <c r="AG33" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:33">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -4461,15 +4556,15 @@
       </c>
       <c r="H34" s="1">
         <f t="shared" si="7"/>
-        <v>12528</v>
+        <v>8305800</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>1730400</v>
       </c>
       <c r="J34" s="1">
         <f t="shared" si="10"/>
-        <v>10648800</v>
+        <v>240816000</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" si="1"/>
@@ -4494,7 +4589,7 @@
         <v>29</v>
       </c>
       <c r="Q34" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>85</v>
       </c>
       <c r="R34" s="1">
@@ -4524,18 +4619,18 @@
         <v>29</v>
       </c>
       <c r="Z34" s="2">
-        <f t="shared" si="14"/>
-        <v>720</v>
+        <f>Z33+1000</f>
+        <v>6000</v>
       </c>
       <c r="AA34" s="2">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="AB34" s="2">
         <v>28</v>
       </c>
       <c r="AC34" s="2">
-        <f t="shared" si="15"/>
-        <v>510</v>
+        <f t="shared" si="9"/>
+        <v>1384</v>
       </c>
       <c r="AD34" s="1">
         <v>0</v>
@@ -4544,8 +4639,11 @@
       <c r="AF34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:32">
+      <c r="AG34" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:33">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -4563,15 +4661,15 @@
       </c>
       <c r="H35" s="1">
         <f t="shared" si="7"/>
-        <v>13680</v>
+        <v>10362100</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>2172100</v>
       </c>
       <c r="J35" s="1">
         <f t="shared" si="10"/>
-        <v>12312000</v>
+        <v>313530000</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" si="1"/>
@@ -4596,7 +4694,7 @@
         <v>30</v>
       </c>
       <c r="Q35" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>90</v>
       </c>
       <c r="R35" s="1">
@@ -4626,18 +4724,18 @@
         <v>30</v>
       </c>
       <c r="Z35" s="2">
-        <f t="shared" si="14"/>
-        <v>760</v>
+        <f>Z34+1000</f>
+        <v>7000</v>
       </c>
       <c r="AA35" s="2">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="AB35" s="2">
         <v>29</v>
       </c>
       <c r="AC35" s="2">
-        <f t="shared" si="15"/>
-        <v>540</v>
+        <f t="shared" si="9"/>
+        <v>1493</v>
       </c>
       <c r="AD35" s="1">
         <v>0</v>
@@ -4646,8 +4744,11 @@
       <c r="AF35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:32">
+      <c r="AG35" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:33">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -4665,15 +4766,15 @@
       </c>
       <c r="H36" s="1">
         <f t="shared" si="7"/>
-        <v>17360</v>
+        <v>13919200</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>2616000</v>
       </c>
       <c r="J36" s="1">
         <f t="shared" si="10"/>
-        <v>14136000</v>
+        <v>398288000</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" si="1"/>
@@ -4698,7 +4799,7 @@
         <v>31</v>
       </c>
       <c r="Q36" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>95</v>
       </c>
       <c r="R36" s="1">
@@ -4728,18 +4829,18 @@
         <v>31</v>
       </c>
       <c r="Z36" s="2">
-        <f t="shared" si="14"/>
-        <v>800</v>
+        <f>Z35+1000</f>
+        <v>8000</v>
       </c>
       <c r="AA36" s="2">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="AB36" s="2">
         <v>30</v>
       </c>
       <c r="AC36" s="2">
-        <f t="shared" si="15"/>
-        <v>570</v>
+        <f t="shared" si="9"/>
+        <v>1606</v>
       </c>
       <c r="AD36" s="1">
         <v>0</v>
@@ -4748,8 +4849,11 @@
       <c r="AF36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:32">
+      <c r="AG36" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:33">
       <c r="C37" s="1">
         <v>32</v>
       </c>
@@ -4767,15 +4871,15 @@
       </c>
       <c r="H37" s="1">
         <f t="shared" si="7"/>
-        <v>19712</v>
+        <v>16388100</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>3152700</v>
       </c>
       <c r="J37" s="1">
         <f t="shared" si="10"/>
-        <v>16896000</v>
+        <v>499104000</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" si="1"/>
@@ -4800,7 +4904,7 @@
         <v>32</v>
       </c>
       <c r="Q37" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>100</v>
       </c>
       <c r="R37" s="1">
@@ -4830,18 +4934,18 @@
         <v>32</v>
       </c>
       <c r="Z37" s="2">
-        <f t="shared" ref="Z37:Z45" si="17">Z36+80</f>
-        <v>880</v>
+        <f>Z36+1000</f>
+        <v>9000</v>
       </c>
       <c r="AA37" s="2">
-        <v>7</v>
+        <v>131</v>
       </c>
       <c r="AB37" s="2">
         <v>31</v>
       </c>
       <c r="AC37" s="2">
-        <f t="shared" si="15"/>
-        <v>600</v>
+        <f t="shared" si="9"/>
+        <v>1733</v>
       </c>
       <c r="AD37" s="1">
         <v>0</v>
@@ -4850,8 +4954,11 @@
       <c r="AF37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:32">
+      <c r="AG37" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:33">
       <c r="C38" s="1">
         <v>33</v>
       </c>
@@ -4869,15 +4976,15 @@
       </c>
       <c r="H38" s="1">
         <f t="shared" si="7"/>
-        <v>22176</v>
+        <v>20413000</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>4064000</v>
       </c>
       <c r="J38" s="1">
         <f t="shared" si="10"/>
-        <v>20908800</v>
+        <v>615120000</v>
       </c>
       <c r="K38" s="1">
         <f t="shared" si="1"/>
@@ -4902,7 +5009,7 @@
         <v>33</v>
       </c>
       <c r="Q38" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>105</v>
       </c>
       <c r="R38" s="1">
@@ -4932,18 +5039,18 @@
         <v>33</v>
       </c>
       <c r="Z38" s="2">
-        <f t="shared" si="17"/>
-        <v>960</v>
+        <f>Z37+1000</f>
+        <v>10000</v>
       </c>
       <c r="AA38" s="2">
-        <v>7</v>
+        <v>137</v>
       </c>
       <c r="AB38" s="2">
         <v>32</v>
       </c>
       <c r="AC38" s="2">
-        <f t="shared" ref="AC38:AC45" si="18">AC37+60</f>
-        <v>660</v>
+        <f t="shared" si="9"/>
+        <v>1864</v>
       </c>
       <c r="AD38" s="1">
         <v>0</v>
@@ -4952,8 +5059,11 @@
       <c r="AF38" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:32">
+      <c r="AG38" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:33">
       <c r="C39" s="1">
         <v>34</v>
       </c>
@@ -4971,15 +5081,15 @@
       </c>
       <c r="H39" s="1">
         <f t="shared" si="7"/>
-        <v>24752</v>
+        <v>25186800</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>5187600</v>
       </c>
       <c r="J39" s="1">
         <f t="shared" si="10"/>
-        <v>25459200</v>
+        <v>816408000</v>
       </c>
       <c r="K39" s="1">
         <f t="shared" si="1"/>
@@ -5004,7 +5114,7 @@
         <v>34</v>
       </c>
       <c r="Q39" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>110</v>
       </c>
       <c r="R39" s="1">
@@ -5034,18 +5144,18 @@
         <v>34</v>
       </c>
       <c r="Z39" s="2">
-        <f t="shared" si="17"/>
-        <v>1040</v>
+        <f t="shared" ref="Z39:Z45" si="12">Z38+2000</f>
+        <v>12000</v>
       </c>
       <c r="AA39" s="2">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="AB39" s="2">
         <v>33</v>
       </c>
       <c r="AC39" s="2">
-        <f t="shared" si="18"/>
-        <v>720</v>
+        <f t="shared" si="9"/>
+        <v>2001</v>
       </c>
       <c r="AD39" s="1">
         <v>0</v>
@@ -5054,8 +5164,11 @@
       <c r="AF39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:32">
+      <c r="AG39" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:33">
       <c r="C40" s="1">
         <v>35</v>
       </c>
@@ -5073,15 +5186,15 @@
       </c>
       <c r="H40" s="1">
         <f t="shared" si="7"/>
-        <v>27440</v>
+        <v>32750200</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>6521200</v>
       </c>
       <c r="J40" s="1">
         <f t="shared" si="10"/>
-        <v>30576000</v>
+        <v>1048600000</v>
       </c>
       <c r="K40" s="1">
         <f t="shared" si="1"/>
@@ -5106,7 +5219,7 @@
         <v>35</v>
       </c>
       <c r="Q40" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>115</v>
       </c>
       <c r="R40" s="1">
@@ -5136,18 +5249,18 @@
         <v>35</v>
       </c>
       <c r="Z40" s="2">
-        <f t="shared" si="17"/>
-        <v>1120</v>
-      </c>
-      <c r="AA40" s="2">
-        <v>7</v>
+        <f t="shared" si="12"/>
+        <v>14000</v>
+      </c>
+      <c r="AA40" s="1">
+        <v>149</v>
       </c>
       <c r="AB40" s="2">
         <v>34</v>
       </c>
       <c r="AC40" s="2">
-        <f t="shared" si="18"/>
-        <v>780</v>
+        <f t="shared" si="9"/>
+        <v>2140</v>
       </c>
       <c r="AD40" s="1">
         <v>0</v>
@@ -5156,8 +5269,11 @@
       <c r="AF40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:32">
+      <c r="AG40" s="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A41" s="2"/>
       <c r="C41" s="1">
         <v>36</v>
@@ -5176,15 +5292,15 @@
       </c>
       <c r="H41" s="1">
         <f t="shared" si="7"/>
-        <v>34560</v>
+        <v>39380800</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>7784000</v>
       </c>
       <c r="J41" s="1">
         <f t="shared" si="10"/>
-        <v>36288000</v>
+        <v>1318464000</v>
       </c>
       <c r="K41" s="1">
         <f t="shared" si="1"/>
@@ -5209,7 +5325,7 @@
         <v>36</v>
       </c>
       <c r="Q41" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>120</v>
       </c>
       <c r="R41" s="1">
@@ -5239,18 +5355,18 @@
         <v>36</v>
       </c>
       <c r="Z41" s="2">
-        <f t="shared" si="17"/>
-        <v>1200</v>
-      </c>
-      <c r="AA41" s="2">
-        <v>8</v>
+        <f t="shared" si="12"/>
+        <v>16000</v>
+      </c>
+      <c r="AA41" s="1">
+        <v>151</v>
       </c>
       <c r="AB41" s="2">
         <v>35</v>
       </c>
       <c r="AC41" s="2">
-        <f t="shared" si="18"/>
-        <v>840</v>
+        <f t="shared" si="9"/>
+        <v>2289</v>
       </c>
       <c r="AD41" s="1">
         <v>0</v>
@@ -5258,8 +5374,11 @@
       <c r="AF41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:32">
+      <c r="AG41" s="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A42" s="2"/>
       <c r="C42" s="1">
         <v>37</v>
@@ -5278,15 +5397,15 @@
       </c>
       <c r="H42" s="1">
         <f t="shared" si="7"/>
-        <v>37888</v>
+        <v>47194200</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>9655200</v>
       </c>
       <c r="J42" s="1">
         <f t="shared" si="10"/>
-        <v>42624000</v>
+        <v>1625040000</v>
       </c>
       <c r="K42" s="1">
         <f t="shared" si="1"/>
@@ -5311,7 +5430,7 @@
         <v>37</v>
       </c>
       <c r="Q42" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>125</v>
       </c>
       <c r="R42" s="1">
@@ -5341,18 +5460,18 @@
         <v>37</v>
       </c>
       <c r="Z42" s="2">
-        <f t="shared" si="17"/>
-        <v>1280</v>
-      </c>
-      <c r="AA42" s="2">
-        <v>8</v>
+        <f t="shared" si="12"/>
+        <v>18000</v>
+      </c>
+      <c r="AA42" s="1">
+        <v>157</v>
       </c>
       <c r="AB42" s="2">
         <v>36</v>
       </c>
       <c r="AC42" s="2">
-        <f t="shared" si="18"/>
-        <v>900</v>
+        <f t="shared" si="9"/>
+        <v>2440</v>
       </c>
       <c r="AD42" s="1">
         <v>0</v>
@@ -5360,8 +5479,11 @@
       <c r="AF42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:32">
+      <c r="AG42" s="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A43" s="2"/>
       <c r="C43" s="1">
         <v>38</v>
@@ -5380,15 +5502,15 @@
       </c>
       <c r="H43" s="1">
         <f t="shared" si="7"/>
-        <v>41344</v>
+        <v>56398000</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>11174000</v>
       </c>
       <c r="J43" s="1">
         <f t="shared" si="10"/>
-        <v>49612800</v>
+        <v>1973720000</v>
       </c>
       <c r="K43" s="1">
         <f t="shared" si="1"/>
@@ -5413,7 +5535,7 @@
         <v>38</v>
       </c>
       <c r="Q43" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>130</v>
       </c>
       <c r="R43" s="1">
@@ -5443,18 +5565,18 @@
         <v>38</v>
       </c>
       <c r="Z43" s="2">
-        <f t="shared" si="17"/>
-        <v>1360</v>
-      </c>
-      <c r="AA43" s="2">
-        <v>8</v>
+        <f t="shared" si="12"/>
+        <v>20000</v>
+      </c>
+      <c r="AA43" s="1">
+        <v>163</v>
       </c>
       <c r="AB43" s="2">
         <v>37</v>
       </c>
       <c r="AC43" s="2">
-        <f t="shared" si="18"/>
-        <v>960</v>
+        <f t="shared" si="9"/>
+        <v>2597</v>
       </c>
       <c r="AD43" s="1">
         <v>0</v>
@@ -5462,8 +5584,11 @@
       <c r="AF43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:32">
+      <c r="AG43" s="1">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A44" s="2"/>
       <c r="C44" s="1">
         <v>39</v>
@@ -5482,15 +5607,15 @@
       </c>
       <c r="H44" s="1">
         <f t="shared" si="7"/>
-        <v>44928</v>
+        <v>74732500</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>14915000</v>
       </c>
       <c r="J44" s="1">
         <f t="shared" si="10"/>
-        <v>57283200</v>
+        <v>2691000000</v>
       </c>
       <c r="K44" s="1">
         <f t="shared" si="1"/>
@@ -5515,7 +5640,7 @@
         <v>39</v>
       </c>
       <c r="Q44" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>135</v>
       </c>
       <c r="R44" s="1">
@@ -5545,18 +5670,18 @@
         <v>39</v>
       </c>
       <c r="Z44" s="2">
-        <f t="shared" si="17"/>
-        <v>1440</v>
-      </c>
-      <c r="AA44" s="2">
-        <v>8</v>
+        <f>Z43+5000</f>
+        <v>25000</v>
+      </c>
+      <c r="AA44" s="1">
+        <v>167</v>
       </c>
       <c r="AB44" s="2">
         <v>38</v>
       </c>
       <c r="AC44" s="2">
-        <f t="shared" si="18"/>
-        <v>1020</v>
+        <f t="shared" si="9"/>
+        <v>2760</v>
       </c>
       <c r="AD44" s="1">
         <v>0</v>
@@ -5564,8 +5689,11 @@
       <c r="AF44" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:32">
+      <c r="AG44" s="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A45" s="2"/>
       <c r="C45" s="1">
         <v>40</v>
@@ -5584,15 +5712,15 @@
       </c>
       <c r="H45" s="1">
         <f t="shared" si="7"/>
-        <v>48640</v>
+        <v>93939000</v>
       </c>
       <c r="I45" s="1">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>19071000</v>
       </c>
       <c r="J45" s="1">
         <f t="shared" si="10"/>
-        <v>65664000</v>
+        <v>3512400000</v>
       </c>
       <c r="K45" s="1">
         <f t="shared" si="1"/>
@@ -5617,7 +5745,7 @@
         <v>40</v>
       </c>
       <c r="Q45" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>140</v>
       </c>
       <c r="R45" s="1">
@@ -5647,18 +5775,18 @@
         <v>40</v>
       </c>
       <c r="Z45" s="2">
-        <f t="shared" si="17"/>
-        <v>1520</v>
-      </c>
-      <c r="AA45" s="2">
-        <v>8</v>
+        <f>Z44+5000</f>
+        <v>30000</v>
+      </c>
+      <c r="AA45" s="1">
+        <v>173</v>
       </c>
       <c r="AB45" s="2">
         <v>39</v>
       </c>
       <c r="AC45" s="2">
-        <f t="shared" si="18"/>
-        <v>1080</v>
+        <f t="shared" si="9"/>
+        <v>2927</v>
       </c>
       <c r="AD45" s="1">
         <v>0</v>
@@ -5666,8 +5794,11 @@
       <c r="AF45" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:32">
+      <c r="AG45" s="1">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A46" s="2"/>
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
@@ -5681,10 +5812,298 @@
       <c r="AA46" s="2"/>
       <c r="AB46" s="2"/>
       <c r="AC46" s="2"/>
+      <c r="AG46" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:33">
+      <c r="AG47" s="2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:33">
+      <c r="AG48" s="2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="33:33">
+      <c r="AG49" s="2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="33:33">
+      <c r="AG50" s="2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="33:33">
+      <c r="AG51" s="2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="33:33">
+      <c r="AG52" s="2">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="33:33">
+      <c r="AG53" s="2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="33:33">
+      <c r="AG54" s="2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="33:33">
+      <c r="AG55" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="33:33">
+      <c r="AG56" s="2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="33:33">
+      <c r="AG57" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="33:33">
+      <c r="AG58" s="2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="33:33">
+      <c r="AG59" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="33:33">
+      <c r="AG60" s="2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="33:33">
+      <c r="AG61" s="2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="33:33">
+      <c r="AG62" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="33:33">
+      <c r="AG63" s="2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="33:33">
+      <c r="AG64" s="2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="33:33">
+      <c r="AG65" s="2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="33:33">
+      <c r="AG66" s="2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="33:33">
+      <c r="AG67" s="2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="33:33">
+      <c r="AG68" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="33:33">
+      <c r="AG69" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="33:33">
+      <c r="AG70" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="33:33">
+      <c r="AG71" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="33:33">
+      <c r="AG72" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="33:33">
+      <c r="AG73" s="2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="33:33">
+      <c r="AG74" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="33:33">
+      <c r="AG75" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="33:33">
+      <c r="AG76" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="33:33">
+      <c r="AG77" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="33:33">
+      <c r="AG78" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="33:33">
+      <c r="AG79" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="33:33">
+      <c r="AG80" s="2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="33:33">
+      <c r="AG81" s="2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="33:33">
+      <c r="AG82" s="2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="33:33">
+      <c r="AG83" s="2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="33:33">
+      <c r="AG84" s="2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="33:33">
+      <c r="AG85" s="2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="33:33">
+      <c r="AG86" s="2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="33:33">
+      <c r="AG87" s="2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="33:33">
+      <c r="AG88" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="33:33">
+      <c r="AG89" s="2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="33:33">
+      <c r="AG90" s="2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="33:33">
+      <c r="AG91" s="2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="33:33">
+      <c r="AG92" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="33:33">
+      <c r="AG93" s="2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="33:33">
+      <c r="AG94" s="2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="33:33">
+      <c r="AG95" s="2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="33:33">
+      <c r="AG96" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="33:33">
+      <c r="AG97" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="33:33">
+      <c r="AG98" s="2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="33:33">
+      <c r="AG99" s="2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="33:33">
+      <c r="AG100" s="2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="33:33">
+      <c r="AG101" s="2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="33:33">
+      <c r="AG102" s="2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="33:33">
+      <c r="AG103" s="2">
+        <v>509</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N3 O3 P3 Q3 R3 S3 T3 U3 C4:G4 H4 I4:N4 O4 P4 Q4 R4 S4 T4 U4 C5:N5 O5 P5 Q5 R5 S5 T5 U5 AD3:AF5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:U5 AD3:AF5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J7" s="1">
         <f>Y7*Z7*AC7</f>
-        <v>3600</v>
+        <v>4800</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="1"/>
@@ -1795,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="AC7" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AD7" s="1">
         <v>0</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J8" s="1">
         <f>Y8*Z8*AC8</f>
-        <v>7560</v>
+        <v>16800</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="1"/>
@@ -1899,8 +1899,7 @@
         <v>2</v>
       </c>
       <c r="AC8" s="2">
-        <f t="shared" ref="AC8:AC45" si="9">AC7+AG7</f>
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AD8" s="1">
         <v>0</v>
@@ -1938,8 +1937,8 @@
         <v>144</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" ref="J7:J45" si="10">Y9*Z9*AC9</f>
-        <v>14720</v>
+        <f t="shared" ref="J7:J45" si="9">Y9*Z9*AC9</f>
+        <v>38400</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="1"/>
@@ -2004,8 +2003,7 @@
         <v>3</v>
       </c>
       <c r="AC9" s="2">
-        <f t="shared" si="9"/>
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AD9" s="1">
         <v>0</v>
@@ -2043,8 +2041,8 @@
         <v>360</v>
       </c>
       <c r="J10" s="1">
-        <f t="shared" si="10"/>
-        <v>27000</v>
+        <f t="shared" si="9"/>
+        <v>90000</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" si="1"/>
@@ -2109,8 +2107,7 @@
         <v>4</v>
       </c>
       <c r="AC10" s="2">
-        <f t="shared" si="9"/>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AD10" s="1">
         <v>0</v>
@@ -2148,8 +2145,8 @@
         <v>700</v>
       </c>
       <c r="J11" s="1">
-        <f t="shared" si="10"/>
-        <v>49200</v>
+        <f t="shared" si="9"/>
+        <v>168000</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" si="1"/>
@@ -2214,8 +2211,7 @@
         <v>5</v>
       </c>
       <c r="AC11" s="2">
-        <f t="shared" si="9"/>
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="AD11" s="1">
         <v>0</v>
@@ -2253,8 +2249,8 @@
         <v>1584</v>
       </c>
       <c r="J12" s="1">
-        <f t="shared" si="10"/>
-        <v>90720</v>
+        <f t="shared" si="9"/>
+        <v>257040</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" si="1"/>
@@ -2319,8 +2315,8 @@
         <v>6</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" si="9"/>
-        <v>54</v>
+        <f t="shared" ref="AC8:AC45" si="10">AC11+AG11</f>
+        <v>153</v>
       </c>
       <c r="AD12" s="1">
         <v>0</v>
@@ -2358,8 +2354,8 @@
         <v>2548</v>
       </c>
       <c r="J13" s="1">
-        <f t="shared" si="10"/>
-        <v>159040</v>
+        <f t="shared" si="9"/>
+        <v>380800</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="1"/>
@@ -2424,8 +2420,8 @@
         <v>7</v>
       </c>
       <c r="AC13" s="2">
-        <f t="shared" si="9"/>
-        <v>71</v>
+        <f t="shared" si="10"/>
+        <v>170</v>
       </c>
       <c r="AD13" s="1">
         <v>0</v>
@@ -2463,8 +2459,8 @@
         <v>4352</v>
       </c>
       <c r="J14" s="1">
-        <f t="shared" si="10"/>
-        <v>259200</v>
+        <f t="shared" si="9"/>
+        <v>544320</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="1"/>
@@ -2529,8 +2525,8 @@
         <v>8</v>
       </c>
       <c r="AC14" s="2">
-        <f t="shared" si="9"/>
-        <v>90</v>
+        <f t="shared" si="10"/>
+        <v>189</v>
       </c>
       <c r="AD14" s="1">
         <v>0</v>
@@ -2568,8 +2564,8 @@
         <v>6156</v>
       </c>
       <c r="J15" s="1">
-        <f t="shared" si="10"/>
-        <v>406800</v>
+        <f t="shared" si="9"/>
+        <v>763200</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="1"/>
@@ -2634,8 +2630,8 @@
         <v>9</v>
       </c>
       <c r="AC15" s="2">
-        <f t="shared" si="9"/>
-        <v>113</v>
+        <f t="shared" si="10"/>
+        <v>212</v>
       </c>
       <c r="AD15" s="1">
         <v>0</v>
@@ -2673,8 +2669,8 @@
         <v>9200</v>
       </c>
       <c r="J16" s="1">
-        <f t="shared" si="10"/>
-        <v>624800</v>
+        <f t="shared" si="9"/>
+        <v>1060400</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" si="1"/>
@@ -2739,8 +2735,8 @@
         <v>10</v>
       </c>
       <c r="AC16" s="2">
-        <f t="shared" si="9"/>
-        <v>142</v>
+        <f t="shared" si="10"/>
+        <v>241</v>
       </c>
       <c r="AD16" s="1">
         <v>0</v>
@@ -2778,8 +2774,8 @@
         <v>15950</v>
       </c>
       <c r="J17" s="1">
-        <f t="shared" si="10"/>
-        <v>1038000</v>
+        <f t="shared" si="9"/>
+        <v>1632000</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" si="1"/>
@@ -2834,7 +2830,7 @@
         <v>12</v>
       </c>
       <c r="Z17" s="2">
-        <f>Z16+100</f>
+        <f t="shared" ref="Z17:Z22" si="11">Z16+100</f>
         <v>500</v>
       </c>
       <c r="AA17" s="2">
@@ -2844,8 +2840,8 @@
         <v>11</v>
       </c>
       <c r="AC17" s="2">
-        <f t="shared" si="9"/>
-        <v>173</v>
+        <f t="shared" si="10"/>
+        <v>272</v>
       </c>
       <c r="AD17" s="1">
         <v>0</v>
@@ -2883,8 +2879,8 @@
         <v>22320</v>
       </c>
       <c r="J18" s="1">
-        <f t="shared" si="10"/>
-        <v>1638000</v>
+        <f t="shared" si="9"/>
+        <v>2410200</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" si="1"/>
@@ -2939,7 +2935,7 @@
         <v>13</v>
       </c>
       <c r="Z18" s="2">
-        <f>Z17+100</f>
+        <f t="shared" si="11"/>
         <v>600</v>
       </c>
       <c r="AA18" s="2">
@@ -2949,8 +2945,8 @@
         <v>12</v>
       </c>
       <c r="AC18" s="2">
-        <f t="shared" si="9"/>
-        <v>210</v>
+        <f t="shared" si="10"/>
+        <v>309</v>
       </c>
       <c r="AD18" s="1">
         <v>0</v>
@@ -2988,8 +2984,8 @@
         <v>33670</v>
       </c>
       <c r="J19" s="1">
-        <f t="shared" si="10"/>
-        <v>2459800</v>
+        <f t="shared" si="9"/>
+        <v>3430000</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" si="1"/>
@@ -3044,7 +3040,7 @@
         <v>14</v>
       </c>
       <c r="Z19" s="2">
-        <f>Z18+100</f>
+        <f t="shared" si="11"/>
         <v>700</v>
       </c>
       <c r="AA19" s="2">
@@ -3054,8 +3050,8 @@
         <v>13</v>
       </c>
       <c r="AC19" s="2">
-        <f t="shared" si="9"/>
-        <v>251</v>
+        <f t="shared" si="10"/>
+        <v>350</v>
       </c>
       <c r="AD19" s="1">
         <v>0</v>
@@ -3093,8 +3089,8 @@
         <v>45920</v>
       </c>
       <c r="J20" s="1">
-        <f t="shared" si="10"/>
-        <v>3528000</v>
+        <f t="shared" si="9"/>
+        <v>4716000</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" si="1"/>
@@ -3149,7 +3145,7 @@
         <v>15</v>
       </c>
       <c r="Z20" s="2">
-        <f>Z19+100</f>
+        <f t="shared" si="11"/>
         <v>800</v>
       </c>
       <c r="AA20" s="2">
@@ -3159,8 +3155,8 @@
         <v>14</v>
       </c>
       <c r="AC20" s="2">
-        <f t="shared" si="9"/>
-        <v>294</v>
+        <f t="shared" si="10"/>
+        <v>393</v>
       </c>
       <c r="AD20" s="1">
         <v>0</v>
@@ -3198,8 +3194,8 @@
         <v>58050</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="10"/>
-        <v>4910400</v>
+        <f t="shared" si="9"/>
+        <v>6336000</v>
       </c>
       <c r="K21" s="1">
         <f t="shared" si="1"/>
@@ -3254,7 +3250,7 @@
         <v>16</v>
       </c>
       <c r="Z21" s="2">
-        <f>Z20+100</f>
+        <f t="shared" si="11"/>
         <v>900</v>
       </c>
       <c r="AA21" s="2">
@@ -3264,8 +3260,8 @@
         <v>15</v>
       </c>
       <c r="AC21" s="2">
-        <f t="shared" si="9"/>
-        <v>341</v>
+        <f t="shared" si="10"/>
+        <v>440</v>
       </c>
       <c r="AD21" s="1">
         <v>0</v>
@@ -3303,8 +3299,8 @@
         <v>75200</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="10"/>
-        <v>6698000</v>
+        <f t="shared" si="9"/>
+        <v>8381000</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" si="1"/>
@@ -3359,7 +3355,7 @@
         <v>17</v>
       </c>
       <c r="Z22" s="2">
-        <f>Z21+100</f>
+        <f t="shared" si="11"/>
         <v>1000</v>
       </c>
       <c r="AA22" s="2">
@@ -3369,8 +3365,8 @@
         <v>16</v>
       </c>
       <c r="AC22" s="2">
-        <f t="shared" si="9"/>
-        <v>394</v>
+        <f t="shared" si="10"/>
+        <v>493</v>
       </c>
       <c r="AD22" s="1">
         <v>0</v>
@@ -3408,8 +3404,8 @@
         <v>108120</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="10"/>
-        <v>9784800</v>
+        <f t="shared" si="9"/>
+        <v>11923200</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" si="1"/>
@@ -3474,8 +3470,8 @@
         <v>17</v>
       </c>
       <c r="AC23" s="2">
-        <f t="shared" si="9"/>
-        <v>453</v>
+        <f t="shared" si="10"/>
+        <v>552</v>
       </c>
       <c r="AD23" s="1">
         <v>0</v>
@@ -3513,8 +3509,8 @@
         <v>148680</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="10"/>
-        <v>13672400</v>
+        <f t="shared" si="9"/>
+        <v>16305800</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" si="1"/>
@@ -3579,8 +3575,8 @@
         <v>18</v>
       </c>
       <c r="AC24" s="2">
-        <f t="shared" si="9"/>
-        <v>514</v>
+        <f t="shared" si="10"/>
+        <v>613</v>
       </c>
       <c r="AD24" s="1">
         <v>0</v>
@@ -3618,8 +3614,8 @@
         <v>185440</v>
       </c>
       <c r="J25" s="1">
-        <f t="shared" si="10"/>
-        <v>18592000</v>
+        <f t="shared" si="9"/>
+        <v>21760000</v>
       </c>
       <c r="K25" s="1">
         <f t="shared" si="1"/>
@@ -3684,8 +3680,8 @@
         <v>19</v>
       </c>
       <c r="AC25" s="2">
-        <f t="shared" si="9"/>
-        <v>581</v>
+        <f t="shared" si="10"/>
+        <v>680</v>
       </c>
       <c r="AD25" s="1">
         <v>0</v>
@@ -3723,8 +3719,8 @@
         <v>241200</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="10"/>
-        <v>24645600</v>
+        <f t="shared" si="9"/>
+        <v>28387800</v>
       </c>
       <c r="K26" s="1">
         <f t="shared" si="1"/>
@@ -3789,8 +3785,8 @@
         <v>20</v>
       </c>
       <c r="AC26" s="2">
-        <f t="shared" si="9"/>
-        <v>652</v>
+        <f t="shared" si="10"/>
+        <v>751</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
@@ -3828,8 +3824,8 @@
         <v>298200</v>
       </c>
       <c r="J27" s="1">
-        <f t="shared" si="10"/>
-        <v>31900000</v>
+        <f t="shared" si="9"/>
+        <v>36256000</v>
       </c>
       <c r="K27" s="1">
         <f t="shared" si="1"/>
@@ -3894,8 +3890,8 @@
         <v>21</v>
       </c>
       <c r="AC27" s="2">
-        <f t="shared" si="9"/>
-        <v>725</v>
+        <f t="shared" si="10"/>
+        <v>824</v>
       </c>
       <c r="AD27" s="1">
         <v>0</v>
@@ -3933,8 +3929,8 @@
         <v>401500</v>
       </c>
       <c r="J28" s="1">
-        <f t="shared" si="10"/>
-        <v>46230000</v>
+        <f t="shared" si="9"/>
+        <v>51922500</v>
       </c>
       <c r="K28" s="1">
         <f t="shared" si="1"/>
@@ -3989,7 +3985,7 @@
         <v>23</v>
       </c>
       <c r="Z28" s="2">
-        <f>Z27+500</f>
+        <f t="shared" ref="Z28:Z33" si="12">Z27+500</f>
         <v>2500</v>
       </c>
       <c r="AA28" s="2">
@@ -3999,8 +3995,8 @@
         <v>22</v>
       </c>
       <c r="AC28" s="2">
-        <f t="shared" si="9"/>
-        <v>804</v>
+        <f t="shared" si="10"/>
+        <v>903</v>
       </c>
       <c r="AD28" s="1">
         <v>0</v>
@@ -4038,8 +4034,8 @@
         <v>545100</v>
       </c>
       <c r="J29" s="1">
-        <f t="shared" si="10"/>
-        <v>63864000</v>
+        <f t="shared" si="9"/>
+        <v>70992000</v>
       </c>
       <c r="K29" s="1">
         <f t="shared" si="1"/>
@@ -4064,7 +4060,7 @@
         <v>24</v>
       </c>
       <c r="Q29" s="2">
-        <f t="shared" ref="Q29:Q45" si="11">Q28+5</f>
+        <f t="shared" ref="Q29:Q45" si="13">Q28+5</f>
         <v>60</v>
       </c>
       <c r="R29" s="1">
@@ -4094,7 +4090,7 @@
         <v>24</v>
       </c>
       <c r="Z29" s="2">
-        <f>Z28+500</f>
+        <f t="shared" si="12"/>
         <v>3000</v>
       </c>
       <c r="AA29" s="2">
@@ -4104,8 +4100,8 @@
         <v>23</v>
       </c>
       <c r="AC29" s="2">
-        <f t="shared" si="9"/>
-        <v>887</v>
+        <f t="shared" si="10"/>
+        <v>986</v>
       </c>
       <c r="AD29" s="1">
         <v>0</v>
@@ -4143,8 +4139,8 @@
         <v>697200</v>
       </c>
       <c r="J30" s="1">
-        <f t="shared" si="10"/>
-        <v>85400000</v>
+        <f t="shared" si="9"/>
+        <v>94062500</v>
       </c>
       <c r="K30" s="1">
         <f t="shared" si="1"/>
@@ -4169,7 +4165,7 @@
         <v>25</v>
       </c>
       <c r="Q30" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>65</v>
       </c>
       <c r="R30" s="1">
@@ -4199,7 +4195,7 @@
         <v>25</v>
       </c>
       <c r="Z30" s="2">
-        <f>Z29+500</f>
+        <f t="shared" si="12"/>
         <v>3500</v>
       </c>
       <c r="AA30" s="2">
@@ -4209,8 +4205,8 @@
         <v>24</v>
       </c>
       <c r="AC30" s="2">
-        <f t="shared" si="9"/>
-        <v>976</v>
+        <f t="shared" si="10"/>
+        <v>1075</v>
       </c>
       <c r="AD30" s="1">
         <v>0</v>
@@ -4248,8 +4244,8 @@
         <v>890000</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="10"/>
-        <v>111592000</v>
+        <f t="shared" si="9"/>
+        <v>121888000</v>
       </c>
       <c r="K31" s="1">
         <f t="shared" si="1"/>
@@ -4274,7 +4270,7 @@
         <v>26</v>
       </c>
       <c r="Q31" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>70</v>
       </c>
       <c r="R31" s="1">
@@ -4304,7 +4300,7 @@
         <v>26</v>
       </c>
       <c r="Z31" s="2">
-        <f>Z30+500</f>
+        <f t="shared" si="12"/>
         <v>4000</v>
       </c>
       <c r="AA31" s="2">
@@ -4314,8 +4310,8 @@
         <v>25</v>
       </c>
       <c r="AC31" s="2">
-        <f t="shared" si="9"/>
-        <v>1073</v>
+        <f t="shared" si="10"/>
+        <v>1172</v>
       </c>
       <c r="AD31" s="1">
         <v>0</v>
@@ -4353,8 +4349,8 @@
         <v>1134900</v>
       </c>
       <c r="J32" s="1">
-        <f t="shared" si="10"/>
-        <v>142641000</v>
+        <f t="shared" si="9"/>
+        <v>154669500</v>
       </c>
       <c r="K32" s="1">
         <f t="shared" si="1"/>
@@ -4379,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="Q32" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>75</v>
       </c>
       <c r="R32" s="1">
@@ -4409,7 +4405,7 @@
         <v>27</v>
       </c>
       <c r="Z32" s="2">
-        <f>Z31+500</f>
+        <f t="shared" si="12"/>
         <v>4500</v>
       </c>
       <c r="AA32" s="2">
@@ -4419,8 +4415,8 @@
         <v>26</v>
       </c>
       <c r="AC32" s="2">
-        <f t="shared" si="9"/>
-        <v>1174</v>
+        <f t="shared" si="10"/>
+        <v>1273</v>
       </c>
       <c r="AD32" s="1">
         <v>0</v>
@@ -4458,8 +4454,8 @@
         <v>1363500</v>
       </c>
       <c r="J33" s="1">
-        <f t="shared" si="10"/>
-        <v>178780000</v>
+        <f t="shared" si="9"/>
+        <v>192640000</v>
       </c>
       <c r="K33" s="1">
         <f t="shared" si="1"/>
@@ -4484,7 +4480,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="R33" s="1">
@@ -4514,7 +4510,7 @@
         <v>28</v>
       </c>
       <c r="Z33" s="2">
-        <f>Z32+500</f>
+        <f t="shared" si="12"/>
         <v>5000</v>
       </c>
       <c r="AA33" s="2">
@@ -4524,8 +4520,8 @@
         <v>27</v>
       </c>
       <c r="AC33" s="2">
-        <f t="shared" si="9"/>
-        <v>1277</v>
+        <f t="shared" si="10"/>
+        <v>1376</v>
       </c>
       <c r="AD33" s="1">
         <v>0</v>
@@ -4563,8 +4559,8 @@
         <v>1730400</v>
       </c>
       <c r="J34" s="1">
-        <f t="shared" si="10"/>
-        <v>240816000</v>
+        <f t="shared" si="9"/>
+        <v>258042000</v>
       </c>
       <c r="K34" s="1">
         <f t="shared" si="1"/>
@@ -4589,7 +4585,7 @@
         <v>29</v>
       </c>
       <c r="Q34" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>85</v>
       </c>
       <c r="R34" s="1">
@@ -4629,8 +4625,8 @@
         <v>28</v>
       </c>
       <c r="AC34" s="2">
-        <f t="shared" si="9"/>
-        <v>1384</v>
+        <f t="shared" si="10"/>
+        <v>1483</v>
       </c>
       <c r="AD34" s="1">
         <v>0</v>
@@ -4668,8 +4664,8 @@
         <v>2172100</v>
       </c>
       <c r="J35" s="1">
-        <f t="shared" si="10"/>
-        <v>313530000</v>
+        <f t="shared" si="9"/>
+        <v>334320000</v>
       </c>
       <c r="K35" s="1">
         <f t="shared" si="1"/>
@@ -4694,7 +4690,7 @@
         <v>30</v>
       </c>
       <c r="Q35" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>90</v>
       </c>
       <c r="R35" s="1">
@@ -4734,8 +4730,8 @@
         <v>29</v>
       </c>
       <c r="AC35" s="2">
-        <f t="shared" si="9"/>
-        <v>1493</v>
+        <f t="shared" si="10"/>
+        <v>1592</v>
       </c>
       <c r="AD35" s="1">
         <v>0</v>
@@ -4773,8 +4769,8 @@
         <v>2616000</v>
       </c>
       <c r="J36" s="1">
-        <f t="shared" si="10"/>
-        <v>398288000</v>
+        <f t="shared" si="9"/>
+        <v>422840000</v>
       </c>
       <c r="K36" s="1">
         <f t="shared" si="1"/>
@@ -4799,7 +4795,7 @@
         <v>31</v>
       </c>
       <c r="Q36" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>95</v>
       </c>
       <c r="R36" s="1">
@@ -4839,8 +4835,8 @@
         <v>30</v>
       </c>
       <c r="AC36" s="2">
-        <f t="shared" si="9"/>
-        <v>1606</v>
+        <f t="shared" si="10"/>
+        <v>1705</v>
       </c>
       <c r="AD36" s="1">
         <v>0</v>
@@ -4878,8 +4874,8 @@
         <v>3152700</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="10"/>
-        <v>499104000</v>
+        <f t="shared" si="9"/>
+        <v>527616000</v>
       </c>
       <c r="K37" s="1">
         <f t="shared" si="1"/>
@@ -4904,7 +4900,7 @@
         <v>32</v>
       </c>
       <c r="Q37" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
       <c r="R37" s="1">
@@ -4944,8 +4940,8 @@
         <v>31</v>
       </c>
       <c r="AC37" s="2">
-        <f t="shared" si="9"/>
-        <v>1733</v>
+        <f t="shared" si="10"/>
+        <v>1832</v>
       </c>
       <c r="AD37" s="1">
         <v>0</v>
@@ -4983,8 +4979,8 @@
         <v>4064000</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="10"/>
-        <v>615120000</v>
+        <f t="shared" si="9"/>
+        <v>647790000</v>
       </c>
       <c r="K38" s="1">
         <f t="shared" si="1"/>
@@ -5009,7 +5005,7 @@
         <v>33</v>
       </c>
       <c r="Q38" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>105</v>
       </c>
       <c r="R38" s="1">
@@ -5049,8 +5045,8 @@
         <v>32</v>
       </c>
       <c r="AC38" s="2">
-        <f t="shared" si="9"/>
-        <v>1864</v>
+        <f t="shared" si="10"/>
+        <v>1963</v>
       </c>
       <c r="AD38" s="1">
         <v>0</v>
@@ -5088,8 +5084,8 @@
         <v>5187600</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="10"/>
-        <v>816408000</v>
+        <f t="shared" si="9"/>
+        <v>856800000</v>
       </c>
       <c r="K39" s="1">
         <f t="shared" si="1"/>
@@ -5114,7 +5110,7 @@
         <v>34</v>
       </c>
       <c r="Q39" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>110</v>
       </c>
       <c r="R39" s="1">
@@ -5144,7 +5140,7 @@
         <v>34</v>
       </c>
       <c r="Z39" s="2">
-        <f t="shared" ref="Z39:Z45" si="12">Z38+2000</f>
+        <f t="shared" ref="Z39:Z45" si="14">Z38+2000</f>
         <v>12000</v>
       </c>
       <c r="AA39" s="2">
@@ -5154,8 +5150,8 @@
         <v>33</v>
       </c>
       <c r="AC39" s="2">
-        <f t="shared" si="9"/>
-        <v>2001</v>
+        <f t="shared" si="10"/>
+        <v>2100</v>
       </c>
       <c r="AD39" s="1">
         <v>0</v>
@@ -5193,8 +5189,8 @@
         <v>6521200</v>
       </c>
       <c r="J40" s="1">
-        <f t="shared" si="10"/>
-        <v>1048600000</v>
+        <f t="shared" si="9"/>
+        <v>1097110000</v>
       </c>
       <c r="K40" s="1">
         <f t="shared" si="1"/>
@@ -5219,7 +5215,7 @@
         <v>35</v>
       </c>
       <c r="Q40" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>115</v>
       </c>
       <c r="R40" s="1">
@@ -5249,7 +5245,7 @@
         <v>35</v>
       </c>
       <c r="Z40" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>14000</v>
       </c>
       <c r="AA40" s="1">
@@ -5259,8 +5255,8 @@
         <v>34</v>
       </c>
       <c r="AC40" s="2">
-        <f t="shared" si="9"/>
-        <v>2140</v>
+        <f t="shared" si="10"/>
+        <v>2239</v>
       </c>
       <c r="AD40" s="1">
         <v>0</v>
@@ -5299,8 +5295,8 @@
         <v>7784000</v>
       </c>
       <c r="J41" s="1">
-        <f t="shared" si="10"/>
-        <v>1318464000</v>
+        <f t="shared" si="9"/>
+        <v>1375488000</v>
       </c>
       <c r="K41" s="1">
         <f t="shared" si="1"/>
@@ -5325,7 +5321,7 @@
         <v>36</v>
       </c>
       <c r="Q41" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>120</v>
       </c>
       <c r="R41" s="1">
@@ -5355,7 +5351,7 @@
         <v>36</v>
       </c>
       <c r="Z41" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>16000</v>
       </c>
       <c r="AA41" s="1">
@@ -5365,8 +5361,8 @@
         <v>35</v>
       </c>
       <c r="AC41" s="2">
-        <f t="shared" si="9"/>
-        <v>2289</v>
+        <f t="shared" si="10"/>
+        <v>2388</v>
       </c>
       <c r="AD41" s="1">
         <v>0</v>
@@ -5404,8 +5400,8 @@
         <v>9655200</v>
       </c>
       <c r="J42" s="1">
-        <f t="shared" si="10"/>
-        <v>1625040000</v>
+        <f t="shared" si="9"/>
+        <v>1690974000</v>
       </c>
       <c r="K42" s="1">
         <f t="shared" si="1"/>
@@ -5430,7 +5426,7 @@
         <v>37</v>
       </c>
       <c r="Q42" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>125</v>
       </c>
       <c r="R42" s="1">
@@ -5460,7 +5456,7 @@
         <v>37</v>
       </c>
       <c r="Z42" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>18000</v>
       </c>
       <c r="AA42" s="1">
@@ -5470,8 +5466,8 @@
         <v>36</v>
       </c>
       <c r="AC42" s="2">
-        <f t="shared" si="9"/>
-        <v>2440</v>
+        <f t="shared" si="10"/>
+        <v>2539</v>
       </c>
       <c r="AD42" s="1">
         <v>0</v>
@@ -5509,8 +5505,8 @@
         <v>11174000</v>
       </c>
       <c r="J43" s="1">
-        <f t="shared" si="10"/>
-        <v>1973720000</v>
+        <f t="shared" si="9"/>
+        <v>2048960000</v>
       </c>
       <c r="K43" s="1">
         <f t="shared" si="1"/>
@@ -5535,7 +5531,7 @@
         <v>38</v>
       </c>
       <c r="Q43" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>130</v>
       </c>
       <c r="R43" s="1">
@@ -5565,7 +5561,7 @@
         <v>38</v>
       </c>
       <c r="Z43" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>20000</v>
       </c>
       <c r="AA43" s="1">
@@ -5575,8 +5571,8 @@
         <v>37</v>
       </c>
       <c r="AC43" s="2">
-        <f t="shared" si="9"/>
-        <v>2597</v>
+        <f t="shared" si="10"/>
+        <v>2696</v>
       </c>
       <c r="AD43" s="1">
         <v>0</v>
@@ -5614,8 +5610,8 @@
         <v>14915000</v>
       </c>
       <c r="J44" s="1">
-        <f t="shared" si="10"/>
-        <v>2691000000</v>
+        <f t="shared" si="9"/>
+        <v>2787525000</v>
       </c>
       <c r="K44" s="1">
         <f t="shared" si="1"/>
@@ -5640,7 +5636,7 @@
         <v>39</v>
       </c>
       <c r="Q44" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>135</v>
       </c>
       <c r="R44" s="1">
@@ -5680,8 +5676,8 @@
         <v>38</v>
       </c>
       <c r="AC44" s="2">
-        <f t="shared" si="9"/>
-        <v>2760</v>
+        <f t="shared" si="10"/>
+        <v>2859</v>
       </c>
       <c r="AD44" s="1">
         <v>0</v>
@@ -5719,8 +5715,8 @@
         <v>19071000</v>
       </c>
       <c r="J45" s="1">
-        <f t="shared" si="10"/>
-        <v>3512400000</v>
+        <f t="shared" si="9"/>
+        <v>3631200000</v>
       </c>
       <c r="K45" s="1">
         <f t="shared" si="1"/>
@@ -5745,7 +5741,7 @@
         <v>40</v>
       </c>
       <c r="Q45" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>140</v>
       </c>
       <c r="R45" s="1">
@@ -5785,8 +5781,8 @@
         <v>39</v>
       </c>
       <c r="AC45" s="2">
-        <f t="shared" si="9"/>
-        <v>2927</v>
+        <f t="shared" si="10"/>
+        <v>3026</v>
       </c>
       <c r="AD45" s="1">
         <v>0</v>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="107">
   <si>
     <t>#</t>
   </si>
@@ -134,124 +134,220 @@
     <t>long</t>
   </si>
   <si>
-    <t>鸡</t>
-  </si>
-  <si>
-    <t>鹿</t>
-  </si>
-  <si>
-    <t>草人</t>
-  </si>
-  <si>
-    <t>野猫</t>
-  </si>
-  <si>
-    <t>食人花</t>
-  </si>
-  <si>
-    <t>雪人</t>
-  </si>
-  <si>
-    <t>蝙蝠</t>
-  </si>
-  <si>
-    <t>骷髅</t>
-  </si>
-  <si>
-    <t>僵尸</t>
-  </si>
-  <si>
-    <t>毒蛇</t>
-  </si>
-  <si>
-    <t>野狼</t>
-  </si>
-  <si>
-    <t>沙虫</t>
-  </si>
-  <si>
-    <t>小鹰</t>
-  </si>
-  <si>
-    <t>角虫</t>
-  </si>
-  <si>
-    <t>蜈蚣</t>
-  </si>
-  <si>
-    <t>钳虫</t>
-  </si>
-  <si>
-    <t>蠕虫</t>
-  </si>
-  <si>
-    <t>黑野猪</t>
-  </si>
-  <si>
-    <t>白野猪</t>
-  </si>
-  <si>
-    <t>蝎蛇</t>
-  </si>
-  <si>
-    <t>火焰恶魔</t>
-  </si>
-  <si>
-    <t>恶魔勇士</t>
-  </si>
-  <si>
-    <t>邪魔雕像</t>
-  </si>
-  <si>
-    <t>邪魔卫士</t>
-  </si>
-  <si>
-    <t>红野猪</t>
-  </si>
-  <si>
-    <t>树妖</t>
-  </si>
-  <si>
-    <t>邪魔侍卫</t>
-  </si>
-  <si>
-    <t>剧毒僵尸</t>
-  </si>
-  <si>
-    <t>骷髅锤兵</t>
-  </si>
-  <si>
-    <t>牛魔将军</t>
-  </si>
-  <si>
-    <t>水龙</t>
-  </si>
-  <si>
-    <t>土龙</t>
-  </si>
-  <si>
-    <t>毒龙</t>
-  </si>
-  <si>
-    <t>火龙</t>
-  </si>
-  <si>
-    <t>冰龙</t>
-  </si>
-  <si>
-    <t>幻影鸡</t>
-  </si>
-  <si>
-    <t>幻影鹿</t>
-  </si>
-  <si>
-    <t>幻影草人</t>
-  </si>
-  <si>
-    <t>幻影猫</t>
-  </si>
-  <si>
-    <t>幻影花</t>
+    <t>赤眼恶狼</t>
+  </si>
+  <si>
+    <t>山贼骷髅</t>
+  </si>
+  <si>
+    <t>游荡兽人</t>
+  </si>
+  <si>
+    <t>魔眼蜘蛛</t>
+  </si>
+  <si>
+    <t>岩甲蝎</t>
+  </si>
+  <si>
+    <t>鬃毛狮</t>
+  </si>
+  <si>
+    <t>毒雾蛆虫</t>
+  </si>
+  <si>
+    <t>响尾蜈蚣</t>
+  </si>
+  <si>
+    <t>双头蜈蚣</t>
+  </si>
+  <si>
+    <t>恶灵蛛王</t>
+  </si>
+  <si>
+    <t>双头蛇</t>
+  </si>
+  <si>
+    <t>沼泽巨鳄</t>
+  </si>
+  <si>
+    <t>嗜血乌鸦</t>
+  </si>
+  <si>
+    <t>伏地行尸</t>
+  </si>
+  <si>
+    <t>食尸鬼</t>
+  </si>
+  <si>
+    <t>血眼蝙蝠</t>
+  </si>
+  <si>
+    <t>尸魔</t>
+  </si>
+  <si>
+    <t>棺守尸卫</t>
+  </si>
+  <si>
+    <t>魅惑花妖</t>
+  </si>
+  <si>
+    <t>荆棘树精</t>
+  </si>
+  <si>
+    <t>深渊鱼人</t>
+  </si>
+  <si>
+    <t>啸月狼人</t>
+  </si>
+  <si>
+    <t>巨型蠕虫</t>
+  </si>
+  <si>
+    <t>噩梦角鹿</t>
+  </si>
+  <si>
+    <t>腐骨恶犬</t>
+  </si>
+  <si>
+    <t>枯骨守卫</t>
+  </si>
+  <si>
+    <t>亡魂射手</t>
+  </si>
+  <si>
+    <t>幽灵鬼火</t>
+  </si>
+  <si>
+    <t>骷髅法师</t>
+  </si>
+  <si>
+    <t>骸骨守卫</t>
+  </si>
+  <si>
+    <t>野猪战士</t>
+  </si>
+  <si>
+    <t>野猪勇士</t>
+  </si>
+  <si>
+    <t>野猪力士</t>
+  </si>
+  <si>
+    <t>野猪萨满</t>
+  </si>
+  <si>
+    <t>野猪战将</t>
+  </si>
+  <si>
+    <t>野猪亲卫</t>
+  </si>
+  <si>
+    <t>血焰花</t>
+  </si>
+  <si>
+    <t>炽火甲虫</t>
+  </si>
+  <si>
+    <t>火蛇</t>
+  </si>
+  <si>
+    <t>赤炎兽</t>
+  </si>
+  <si>
+    <t>焰魔姬</t>
+  </si>
+  <si>
+    <t>炎魔</t>
+  </si>
+  <si>
+    <t>冰甲蝎</t>
+  </si>
+  <si>
+    <t>寒冰守卫</t>
+  </si>
+  <si>
+    <t>霜甲龙龟</t>
+  </si>
+  <si>
+    <t>冰霜骑士</t>
+  </si>
+  <si>
+    <t>冰霜巨人</t>
+  </si>
+  <si>
+    <t>寒冰古兽</t>
+  </si>
+  <si>
+    <t>赤瞳鬼面蛛</t>
+  </si>
+  <si>
+    <t>魅惑蛇姬</t>
+  </si>
+  <si>
+    <t>毒牙巨蜥</t>
+  </si>
+  <si>
+    <t>暗夜行者</t>
+  </si>
+  <si>
+    <t>暗影祭司</t>
+  </si>
+  <si>
+    <t>暗影女骑</t>
+  </si>
+  <si>
+    <t>半人马战士</t>
+  </si>
+  <si>
+    <t>巨熊守卫</t>
+  </si>
+  <si>
+    <t>图腾萨满</t>
+  </si>
+  <si>
+    <t>屠戮者</t>
+  </si>
+  <si>
+    <t>狂暴牛头</t>
+  </si>
+  <si>
+    <t>蛮族亲卫</t>
+  </si>
+  <si>
+    <t>深渊魔瞳</t>
+  </si>
+  <si>
+    <t>收割者</t>
+  </si>
+  <si>
+    <t>血魔</t>
+  </si>
+  <si>
+    <t>失序恶魔</t>
+  </si>
+  <si>
+    <t>黑锋骑士</t>
+  </si>
+  <si>
+    <t>异界巫师</t>
+  </si>
+  <si>
+    <t>长角恶魔</t>
+  </si>
+  <si>
+    <t>地狱三头犬</t>
+  </si>
+  <si>
+    <t>恶魔女巫</t>
+  </si>
+  <si>
+    <t>魇兽</t>
+  </si>
+  <si>
+    <t>大恶魔</t>
+  </si>
+  <si>
+    <t>深渊领主</t>
   </si>
 </sst>
 </file>
@@ -884,14 +980,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1219,7 +1325,7 @@
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="3" customWidth="1"/>
     <col min="7" max="7" width="9.58333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.0833333333333" style="2" customWidth="1"/>
     <col min="9" max="9" width="15.0833333333333" style="2" customWidth="1"/>
@@ -1248,6 +1354,7 @@
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
+      <c r="F1" s="3"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -1298,6 +1405,7 @@
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
+      <c r="F2" s="3"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -1348,67 +1456,67 @@
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="V3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="4" t="s">
         <v>21</v>
       </c>
       <c r="X3" s="1" t="s">
@@ -1429,93 +1537,93 @@
       <c r="AC3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AE3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AF3" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="U4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="W4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
-      <c r="AD4" s="3" t="s">
+      <c r="AD4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AE4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AF4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="AG4" s="1">
@@ -1525,80 +1633,80 @@
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="R5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="S5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="T5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="U5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="V5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="W5" s="3" t="s">
+      <c r="W5" s="4" t="s">
         <v>34</v>
       </c>
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
-      <c r="AD5" s="3" t="s">
+      <c r="AD5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AE5" s="3" t="s">
+      <c r="AE5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AF5" s="3" t="s">
+      <c r="AF5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="AG5" s="2">
@@ -1615,7 +1723,7 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="1">
@@ -1625,35 +1733,35 @@
         <v>10</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" ref="I6:I45" si="0">AB6*AG4*Z6/10</f>
+        <f t="shared" ref="I6:I69" si="0">AB6*AG4*Z6/10</f>
         <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>100</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" ref="K6:K45" si="1">Y6*5</f>
+        <f t="shared" ref="K6:K69" si="1">Y6*5</f>
         <v>5</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L45" si="2">Y6*3</f>
+        <f t="shared" ref="L6:L69" si="2">Y6*3</f>
         <v>3</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M45" si="3">Y6*2</f>
+        <f t="shared" ref="M6:M69" si="3">Y6*2</f>
         <v>2</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" ref="N6:N45" si="4">Y6*4</f>
+        <f t="shared" ref="N6:N69" si="4">Y6*4</f>
         <v>4</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="6">
         <v>1</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="Q6" s="6">
         <v>1</v>
       </c>
       <c r="R6" s="1">
@@ -1662,18 +1770,18 @@
       <c r="S6" s="1">
         <v>0</v>
       </c>
-      <c r="T6" s="4">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4">
+      <c r="T6" s="6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6">
         <v>0</v>
       </c>
       <c r="V6" s="1">
-        <f t="shared" ref="V6:V46" si="5">X6*10</f>
+        <f t="shared" ref="V6:V69" si="5">X6*10</f>
         <v>100</v>
       </c>
       <c r="W6" s="1">
-        <f t="shared" ref="W6:W46" si="6">X6*10</f>
+        <f t="shared" ref="W6:W69" si="6">X6*10</f>
         <v>100</v>
       </c>
       <c r="X6" s="1">
@@ -1715,14 +1823,14 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
       <c r="H7" s="1">
-        <f t="shared" ref="H7:H45" si="7">AG9*Z7*AA7/10</f>
+        <f t="shared" ref="H7:H70" si="7">AG9*Z7*AA7/10</f>
         <v>252</v>
       </c>
       <c r="I7" s="1">
@@ -1752,10 +1860,10 @@
       <c r="O7" s="1">
         <v>1</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="6">
         <v>2</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="Q7" s="6">
         <v>10</v>
       </c>
       <c r="R7" s="1">
@@ -1764,10 +1872,10 @@
       <c r="S7" s="1">
         <v>0</v>
       </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4">
+      <c r="T7" s="6">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6">
         <v>0</v>
       </c>
       <c r="V7" s="1">
@@ -1818,7 +1926,7 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="5" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="1">
@@ -1855,7 +1963,7 @@
       <c r="O8" s="1">
         <v>2</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="6">
         <v>3</v>
       </c>
       <c r="Q8" s="2">
@@ -1868,10 +1976,10 @@
       <c r="S8" s="1">
         <v>0</v>
       </c>
-      <c r="T8" s="4">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4">
+      <c r="T8" s="6">
+        <v>0</v>
+      </c>
+      <c r="U8" s="6">
         <v>0</v>
       </c>
       <c r="V8" s="1">
@@ -1922,7 +2030,7 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="1">
@@ -1937,7 +2045,7 @@
         <v>144</v>
       </c>
       <c r="J9" s="1">
-        <f t="shared" ref="J7:J45" si="9">Y9*Z9*AC9</f>
+        <f t="shared" ref="J7:J72" si="9">Y9*Z9*AC9</f>
         <v>38400</v>
       </c>
       <c r="K9" s="1">
@@ -1959,7 +2067,7 @@
       <c r="O9" s="1">
         <v>3</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="6">
         <v>4</v>
       </c>
       <c r="Q9" s="2">
@@ -1972,10 +2080,10 @@
       <c r="S9" s="1">
         <v>0</v>
       </c>
-      <c r="T9" s="4">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4">
+      <c r="T9" s="6">
+        <v>0</v>
+      </c>
+      <c r="U9" s="6">
         <v>0</v>
       </c>
       <c r="V9" s="1">
@@ -2026,7 +2134,7 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="5" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="1">
@@ -2063,7 +2171,7 @@
       <c r="O10" s="1">
         <v>4</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="6">
         <v>5</v>
       </c>
       <c r="Q10" s="2">
@@ -2076,10 +2184,10 @@
       <c r="S10" s="1">
         <v>0</v>
       </c>
-      <c r="T10" s="4">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4">
+      <c r="T10" s="6">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6">
         <v>0</v>
       </c>
       <c r="V10" s="1">
@@ -2130,7 +2238,7 @@
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="3" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="1">
@@ -2167,7 +2275,7 @@
       <c r="O11" s="1">
         <v>5</v>
       </c>
-      <c r="P11" s="4">
+      <c r="P11" s="6">
         <v>6</v>
       </c>
       <c r="Q11" s="2">
@@ -2180,10 +2288,10 @@
       <c r="S11" s="1">
         <v>0</v>
       </c>
-      <c r="T11" s="4">
-        <v>0</v>
-      </c>
-      <c r="U11" s="4">
+      <c r="T11" s="6">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6">
         <v>0</v>
       </c>
       <c r="V11" s="1">
@@ -2234,7 +2342,7 @@
       <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="5" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="1">
@@ -2271,7 +2379,7 @@
       <c r="O12" s="1">
         <v>6</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="6">
         <v>7</v>
       </c>
       <c r="Q12" s="2">
@@ -2284,10 +2392,10 @@
       <c r="S12" s="1">
         <v>0</v>
       </c>
-      <c r="T12" s="4">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4">
+      <c r="T12" s="6">
+        <v>0</v>
+      </c>
+      <c r="U12" s="6">
         <v>0</v>
       </c>
       <c r="V12" s="1">
@@ -2315,7 +2423,7 @@
         <v>6</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" ref="AC8:AC45" si="10">AC11+AG11</f>
+        <f t="shared" ref="AC8:AC75" si="10">AC11+AG11</f>
         <v>153</v>
       </c>
       <c r="AD12" s="1">
@@ -2339,7 +2447,7 @@
       <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="1">
@@ -2376,7 +2484,7 @@
       <c r="O13" s="1">
         <v>7</v>
       </c>
-      <c r="P13" s="4">
+      <c r="P13" s="6">
         <v>8</v>
       </c>
       <c r="Q13" s="2">
@@ -2389,10 +2497,10 @@
       <c r="S13" s="1">
         <v>0</v>
       </c>
-      <c r="T13" s="4">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4">
+      <c r="T13" s="6">
+        <v>0</v>
+      </c>
+      <c r="U13" s="6">
         <v>0</v>
       </c>
       <c r="V13" s="1">
@@ -2444,7 +2552,7 @@
       <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G14" s="1">
@@ -2481,7 +2589,7 @@
       <c r="O14" s="1">
         <v>8</v>
       </c>
-      <c r="P14" s="4">
+      <c r="P14" s="6">
         <v>9</v>
       </c>
       <c r="Q14" s="2">
@@ -2494,10 +2602,10 @@
       <c r="S14" s="1">
         <v>0</v>
       </c>
-      <c r="T14" s="4">
-        <v>0</v>
-      </c>
-      <c r="U14" s="4">
+      <c r="T14" s="6">
+        <v>0</v>
+      </c>
+      <c r="U14" s="6">
         <v>0</v>
       </c>
       <c r="V14" s="1">
@@ -2549,7 +2657,7 @@
       <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="7" t="s">
         <v>44</v>
       </c>
       <c r="G15" s="1">
@@ -2586,7 +2694,7 @@
       <c r="O15" s="1">
         <v>9</v>
       </c>
-      <c r="P15" s="4">
+      <c r="P15" s="6">
         <v>10</v>
       </c>
       <c r="Q15" s="2">
@@ -2599,10 +2707,10 @@
       <c r="S15" s="1">
         <v>0</v>
       </c>
-      <c r="T15" s="4">
-        <v>0</v>
-      </c>
-      <c r="U15" s="4">
+      <c r="T15" s="6">
+        <v>0</v>
+      </c>
+      <c r="U15" s="6">
         <v>0</v>
       </c>
       <c r="V15" s="1">
@@ -2654,7 +2762,7 @@
       <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="G16" s="1">
@@ -2691,7 +2799,7 @@
       <c r="O16" s="1">
         <v>10</v>
       </c>
-      <c r="P16" s="4">
+      <c r="P16" s="6">
         <v>11</v>
       </c>
       <c r="Q16" s="2">
@@ -2704,10 +2812,10 @@
       <c r="S16" s="1">
         <v>0</v>
       </c>
-      <c r="T16" s="4">
-        <v>0</v>
-      </c>
-      <c r="U16" s="4">
+      <c r="T16" s="6">
+        <v>0</v>
+      </c>
+      <c r="U16" s="6">
         <v>0</v>
       </c>
       <c r="V16" s="1">
@@ -2759,7 +2867,7 @@
       <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="3" t="s">
         <v>46</v>
       </c>
       <c r="G17" s="1">
@@ -2796,7 +2904,7 @@
       <c r="O17" s="1">
         <v>11</v>
       </c>
-      <c r="P17" s="4">
+      <c r="P17" s="6">
         <v>12</v>
       </c>
       <c r="Q17" s="2">
@@ -2809,10 +2917,10 @@
       <c r="S17" s="1">
         <v>0</v>
       </c>
-      <c r="T17" s="4">
-        <v>0</v>
-      </c>
-      <c r="U17" s="4">
+      <c r="T17" s="6">
+        <v>0</v>
+      </c>
+      <c r="U17" s="6">
         <v>0</v>
       </c>
       <c r="V17" s="1">
@@ -2864,7 +2972,7 @@
       <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="1">
@@ -2901,7 +3009,7 @@
       <c r="O18" s="1">
         <v>12</v>
       </c>
-      <c r="P18" s="4">
+      <c r="P18" s="6">
         <v>13</v>
       </c>
       <c r="Q18" s="2">
@@ -2914,10 +3022,10 @@
       <c r="S18" s="1">
         <v>0</v>
       </c>
-      <c r="T18" s="4">
-        <v>0</v>
-      </c>
-      <c r="U18" s="4">
+      <c r="T18" s="6">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6">
         <v>0</v>
       </c>
       <c r="V18" s="1">
@@ -2969,7 +3077,7 @@
       <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="5" t="s">
         <v>48</v>
       </c>
       <c r="G19" s="1">
@@ -3006,7 +3114,7 @@
       <c r="O19" s="1">
         <v>13</v>
       </c>
-      <c r="P19" s="4">
+      <c r="P19" s="6">
         <v>14</v>
       </c>
       <c r="Q19" s="2">
@@ -3019,10 +3127,10 @@
       <c r="S19" s="1">
         <v>0</v>
       </c>
-      <c r="T19" s="4">
-        <v>0</v>
-      </c>
-      <c r="U19" s="4">
+      <c r="T19" s="6">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6">
         <v>0</v>
       </c>
       <c r="V19" s="1">
@@ -3074,7 +3182,7 @@
       <c r="E20" s="1">
         <v>1</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="5" t="s">
         <v>49</v>
       </c>
       <c r="G20" s="1">
@@ -3111,7 +3219,7 @@
       <c r="O20" s="1">
         <v>14</v>
       </c>
-      <c r="P20" s="4">
+      <c r="P20" s="6">
         <v>15</v>
       </c>
       <c r="Q20" s="2">
@@ -3124,10 +3232,10 @@
       <c r="S20" s="1">
         <v>0</v>
       </c>
-      <c r="T20" s="4">
-        <v>0</v>
-      </c>
-      <c r="U20" s="4">
+      <c r="T20" s="6">
+        <v>0</v>
+      </c>
+      <c r="U20" s="6">
         <v>0</v>
       </c>
       <c r="V20" s="1">
@@ -3179,7 +3287,7 @@
       <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G21" s="1">
@@ -3216,7 +3324,7 @@
       <c r="O21" s="1">
         <v>15</v>
       </c>
-      <c r="P21" s="4">
+      <c r="P21" s="6">
         <v>16</v>
       </c>
       <c r="Q21" s="2">
@@ -3229,10 +3337,10 @@
       <c r="S21" s="1">
         <v>0</v>
       </c>
-      <c r="T21" s="4">
-        <v>0</v>
-      </c>
-      <c r="U21" s="4">
+      <c r="T21" s="6">
+        <v>0</v>
+      </c>
+      <c r="U21" s="6">
         <v>0</v>
       </c>
       <c r="V21" s="1">
@@ -3284,7 +3392,7 @@
       <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="5" t="s">
         <v>51</v>
       </c>
       <c r="G22" s="1">
@@ -3321,7 +3429,7 @@
       <c r="O22" s="1">
         <v>16</v>
       </c>
-      <c r="P22" s="4">
+      <c r="P22" s="6">
         <v>17</v>
       </c>
       <c r="Q22" s="2">
@@ -3334,10 +3442,10 @@
       <c r="S22" s="1">
         <v>0</v>
       </c>
-      <c r="T22" s="4">
-        <v>0</v>
-      </c>
-      <c r="U22" s="4">
+      <c r="T22" s="6">
+        <v>0</v>
+      </c>
+      <c r="U22" s="6">
         <v>0</v>
       </c>
       <c r="V22" s="1">
@@ -3389,7 +3497,7 @@
       <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="3" t="s">
         <v>52</v>
       </c>
       <c r="G23" s="1">
@@ -3426,7 +3534,7 @@
       <c r="O23" s="1">
         <v>17</v>
       </c>
-      <c r="P23" s="4">
+      <c r="P23" s="6">
         <v>18</v>
       </c>
       <c r="Q23" s="2">
@@ -3439,10 +3547,10 @@
       <c r="S23" s="1">
         <v>0</v>
       </c>
-      <c r="T23" s="4">
-        <v>0</v>
-      </c>
-      <c r="U23" s="4">
+      <c r="T23" s="6">
+        <v>0</v>
+      </c>
+      <c r="U23" s="6">
         <v>0</v>
       </c>
       <c r="V23" s="1">
@@ -3494,7 +3602,7 @@
       <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G24" s="1">
@@ -3531,7 +3639,7 @@
       <c r="O24" s="1">
         <v>18</v>
       </c>
-      <c r="P24" s="4">
+      <c r="P24" s="6">
         <v>19</v>
       </c>
       <c r="Q24" s="2">
@@ -3544,10 +3652,10 @@
       <c r="S24" s="1">
         <v>0</v>
       </c>
-      <c r="T24" s="4">
-        <v>0</v>
-      </c>
-      <c r="U24" s="4">
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
         <v>0</v>
       </c>
       <c r="V24" s="1">
@@ -3599,7 +3707,7 @@
       <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="5" t="s">
         <v>54</v>
       </c>
       <c r="G25" s="1">
@@ -3636,7 +3744,7 @@
       <c r="O25" s="1">
         <v>19</v>
       </c>
-      <c r="P25" s="4">
+      <c r="P25" s="6">
         <v>20</v>
       </c>
       <c r="Q25" s="2">
@@ -3649,10 +3757,10 @@
       <c r="S25" s="1">
         <v>0</v>
       </c>
-      <c r="T25" s="4">
-        <v>0</v>
-      </c>
-      <c r="U25" s="4">
+      <c r="T25" s="6">
+        <v>0</v>
+      </c>
+      <c r="U25" s="6">
         <v>0</v>
       </c>
       <c r="V25" s="1">
@@ -3704,7 +3812,7 @@
       <c r="E26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="5" t="s">
         <v>55</v>
       </c>
       <c r="G26" s="1">
@@ -3741,7 +3849,7 @@
       <c r="O26" s="1">
         <v>20</v>
       </c>
-      <c r="P26" s="4">
+      <c r="P26" s="6">
         <v>21</v>
       </c>
       <c r="Q26" s="2">
@@ -3754,10 +3862,10 @@
       <c r="S26" s="1">
         <v>0</v>
       </c>
-      <c r="T26" s="4">
-        <v>0</v>
-      </c>
-      <c r="U26" s="4">
+      <c r="T26" s="6">
+        <v>0</v>
+      </c>
+      <c r="U26" s="6">
         <v>0</v>
       </c>
       <c r="V26" s="1">
@@ -3809,7 +3917,7 @@
       <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G27" s="1">
@@ -3846,7 +3954,7 @@
       <c r="O27" s="1">
         <v>21</v>
       </c>
-      <c r="P27" s="4">
+      <c r="P27" s="6">
         <v>22</v>
       </c>
       <c r="Q27" s="2">
@@ -3859,10 +3967,10 @@
       <c r="S27" s="1">
         <v>0</v>
       </c>
-      <c r="T27" s="4">
-        <v>0</v>
-      </c>
-      <c r="U27" s="4">
+      <c r="T27" s="6">
+        <v>0</v>
+      </c>
+      <c r="U27" s="6">
         <v>0</v>
       </c>
       <c r="V27" s="1">
@@ -3914,7 +4022,7 @@
       <c r="E28" s="1">
         <v>1</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G28" s="1">
@@ -3951,7 +4059,7 @@
       <c r="O28" s="1">
         <v>22</v>
       </c>
-      <c r="P28" s="4">
+      <c r="P28" s="6">
         <v>23</v>
       </c>
       <c r="Q28" s="2">
@@ -3964,10 +4072,10 @@
       <c r="S28" s="1">
         <v>0</v>
       </c>
-      <c r="T28" s="4">
-        <v>0</v>
-      </c>
-      <c r="U28" s="4">
+      <c r="T28" s="6">
+        <v>0</v>
+      </c>
+      <c r="U28" s="6">
         <v>0</v>
       </c>
       <c r="V28" s="1">
@@ -4019,7 +4127,7 @@
       <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G29" s="1">
@@ -4056,11 +4164,11 @@
       <c r="O29" s="1">
         <v>23</v>
       </c>
-      <c r="P29" s="4">
+      <c r="P29" s="6">
         <v>24</v>
       </c>
       <c r="Q29" s="2">
-        <f t="shared" ref="Q29:Q45" si="13">Q28+5</f>
+        <f t="shared" ref="Q29:Q77" si="13">Q28+5</f>
         <v>60</v>
       </c>
       <c r="R29" s="1">
@@ -4069,10 +4177,10 @@
       <c r="S29" s="1">
         <v>0</v>
       </c>
-      <c r="T29" s="4">
-        <v>0</v>
-      </c>
-      <c r="U29" s="4">
+      <c r="T29" s="6">
+        <v>0</v>
+      </c>
+      <c r="U29" s="6">
         <v>0</v>
       </c>
       <c r="V29" s="1">
@@ -4124,7 +4232,7 @@
       <c r="E30" s="1">
         <v>1</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="5" t="s">
         <v>59</v>
       </c>
       <c r="G30" s="1">
@@ -4161,7 +4269,7 @@
       <c r="O30" s="1">
         <v>24</v>
       </c>
-      <c r="P30" s="4">
+      <c r="P30" s="6">
         <v>25</v>
       </c>
       <c r="Q30" s="2">
@@ -4174,10 +4282,10 @@
       <c r="S30" s="1">
         <v>0</v>
       </c>
-      <c r="T30" s="4">
-        <v>0</v>
-      </c>
-      <c r="U30" s="4">
+      <c r="T30" s="6">
+        <v>0</v>
+      </c>
+      <c r="U30" s="6">
         <v>0</v>
       </c>
       <c r="V30" s="1">
@@ -4229,7 +4337,7 @@
       <c r="E31" s="1">
         <v>1</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G31" s="1">
@@ -4266,7 +4374,7 @@
       <c r="O31" s="1">
         <v>25</v>
       </c>
-      <c r="P31" s="4">
+      <c r="P31" s="6">
         <v>26</v>
       </c>
       <c r="Q31" s="2">
@@ -4279,10 +4387,10 @@
       <c r="S31" s="1">
         <v>0</v>
       </c>
-      <c r="T31" s="4">
-        <v>0</v>
-      </c>
-      <c r="U31" s="4">
+      <c r="T31" s="6">
+        <v>0</v>
+      </c>
+      <c r="U31" s="6">
         <v>0</v>
       </c>
       <c r="V31" s="1">
@@ -4334,7 +4442,7 @@
       <c r="E32" s="1">
         <v>1</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="8" t="s">
         <v>61</v>
       </c>
       <c r="G32" s="1">
@@ -4371,7 +4479,7 @@
       <c r="O32" s="1">
         <v>26</v>
       </c>
-      <c r="P32" s="4">
+      <c r="P32" s="6">
         <v>27</v>
       </c>
       <c r="Q32" s="2">
@@ -4384,10 +4492,10 @@
       <c r="S32" s="1">
         <v>0</v>
       </c>
-      <c r="T32" s="4">
-        <v>0</v>
-      </c>
-      <c r="U32" s="4">
+      <c r="T32" s="6">
+        <v>0</v>
+      </c>
+      <c r="U32" s="6">
         <v>0</v>
       </c>
       <c r="V32" s="1">
@@ -4439,7 +4547,7 @@
       <c r="E33" s="1">
         <v>1</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="5" t="s">
         <v>62</v>
       </c>
       <c r="G33" s="1">
@@ -4476,7 +4584,7 @@
       <c r="O33" s="1">
         <v>27</v>
       </c>
-      <c r="P33" s="4">
+      <c r="P33" s="6">
         <v>28</v>
       </c>
       <c r="Q33" s="2">
@@ -4489,10 +4597,10 @@
       <c r="S33" s="1">
         <v>0</v>
       </c>
-      <c r="T33" s="4">
-        <v>0</v>
-      </c>
-      <c r="U33" s="4">
+      <c r="T33" s="6">
+        <v>0</v>
+      </c>
+      <c r="U33" s="6">
         <v>0</v>
       </c>
       <c r="V33" s="1">
@@ -4544,7 +4652,7 @@
       <c r="E34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="8" t="s">
         <v>63</v>
       </c>
       <c r="G34" s="1">
@@ -4581,7 +4689,7 @@
       <c r="O34" s="1">
         <v>28</v>
       </c>
-      <c r="P34" s="4">
+      <c r="P34" s="6">
         <v>29</v>
       </c>
       <c r="Q34" s="2">
@@ -4594,10 +4702,10 @@
       <c r="S34" s="1">
         <v>0</v>
       </c>
-      <c r="T34" s="4">
-        <v>0</v>
-      </c>
-      <c r="U34" s="4">
+      <c r="T34" s="6">
+        <v>0</v>
+      </c>
+      <c r="U34" s="6">
         <v>0</v>
       </c>
       <c r="V34" s="1">
@@ -4649,7 +4757,7 @@
       <c r="E35" s="1">
         <v>1</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G35" s="1">
@@ -4686,7 +4794,7 @@
       <c r="O35" s="1">
         <v>29</v>
       </c>
-      <c r="P35" s="4">
+      <c r="P35" s="6">
         <v>30</v>
       </c>
       <c r="Q35" s="2">
@@ -4699,10 +4807,10 @@
       <c r="S35" s="1">
         <v>0</v>
       </c>
-      <c r="T35" s="4">
-        <v>0</v>
-      </c>
-      <c r="U35" s="4">
+      <c r="T35" s="6">
+        <v>0</v>
+      </c>
+      <c r="U35" s="6">
         <v>0</v>
       </c>
       <c r="V35" s="1">
@@ -4754,7 +4862,7 @@
       <c r="E36" s="1">
         <v>1</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G36" s="1">
@@ -4791,7 +4899,7 @@
       <c r="O36" s="1">
         <v>30</v>
       </c>
-      <c r="P36" s="4">
+      <c r="P36" s="6">
         <v>31</v>
       </c>
       <c r="Q36" s="2">
@@ -4804,10 +4912,10 @@
       <c r="S36" s="1">
         <v>0</v>
       </c>
-      <c r="T36" s="4">
-        <v>0</v>
-      </c>
-      <c r="U36" s="4">
+      <c r="T36" s="6">
+        <v>0</v>
+      </c>
+      <c r="U36" s="6">
         <v>0</v>
       </c>
       <c r="V36" s="1">
@@ -4859,7 +4967,7 @@
       <c r="E37" s="1">
         <v>1</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="5" t="s">
         <v>66</v>
       </c>
       <c r="G37" s="1">
@@ -4896,7 +5004,7 @@
       <c r="O37" s="1">
         <v>31</v>
       </c>
-      <c r="P37" s="4">
+      <c r="P37" s="6">
         <v>32</v>
       </c>
       <c r="Q37" s="2">
@@ -4909,10 +5017,10 @@
       <c r="S37" s="1">
         <v>0</v>
       </c>
-      <c r="T37" s="4">
-        <v>0</v>
-      </c>
-      <c r="U37" s="4">
+      <c r="T37" s="6">
+        <v>0</v>
+      </c>
+      <c r="U37" s="6">
         <v>0</v>
       </c>
       <c r="V37" s="1">
@@ -4964,7 +5072,7 @@
       <c r="E38" s="1">
         <v>1</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G38" s="1">
@@ -5001,7 +5109,7 @@
       <c r="O38" s="1">
         <v>32</v>
       </c>
-      <c r="P38" s="4">
+      <c r="P38" s="6">
         <v>33</v>
       </c>
       <c r="Q38" s="2">
@@ -5014,10 +5122,10 @@
       <c r="S38" s="1">
         <v>0</v>
       </c>
-      <c r="T38" s="4">
-        <v>0</v>
-      </c>
-      <c r="U38" s="4">
+      <c r="T38" s="6">
+        <v>0</v>
+      </c>
+      <c r="U38" s="6">
         <v>0</v>
       </c>
       <c r="V38" s="1">
@@ -5069,7 +5177,7 @@
       <c r="E39" s="1">
         <v>1</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="5" t="s">
         <v>68</v>
       </c>
       <c r="G39" s="1">
@@ -5106,7 +5214,7 @@
       <c r="O39" s="1">
         <v>33</v>
       </c>
-      <c r="P39" s="4">
+      <c r="P39" s="6">
         <v>34</v>
       </c>
       <c r="Q39" s="2">
@@ -5119,10 +5227,10 @@
       <c r="S39" s="1">
         <v>0</v>
       </c>
-      <c r="T39" s="4">
-        <v>0</v>
-      </c>
-      <c r="U39" s="4">
+      <c r="T39" s="6">
+        <v>0</v>
+      </c>
+      <c r="U39" s="6">
         <v>0</v>
       </c>
       <c r="V39" s="1">
@@ -5174,7 +5282,7 @@
       <c r="E40" s="1">
         <v>1</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="5" t="s">
         <v>69</v>
       </c>
       <c r="G40" s="1">
@@ -5211,7 +5319,7 @@
       <c r="O40" s="1">
         <v>34</v>
       </c>
-      <c r="P40" s="4">
+      <c r="P40" s="6">
         <v>35</v>
       </c>
       <c r="Q40" s="2">
@@ -5224,10 +5332,10 @@
       <c r="S40" s="1">
         <v>0</v>
       </c>
-      <c r="T40" s="4">
-        <v>0</v>
-      </c>
-      <c r="U40" s="4">
+      <c r="T40" s="6">
+        <v>0</v>
+      </c>
+      <c r="U40" s="6">
         <v>0</v>
       </c>
       <c r="V40" s="1">
@@ -5278,13 +5386,13 @@
         <v>36</v>
       </c>
       <c r="E41" s="1">
-        <v>2</v>
-      </c>
-      <c r="F41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>70</v>
       </c>
       <c r="G41" s="1">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H41" s="1">
         <f t="shared" si="7"/>
@@ -5317,7 +5425,7 @@
       <c r="O41" s="1">
         <v>35</v>
       </c>
-      <c r="P41" s="4">
+      <c r="P41" s="6">
         <v>36</v>
       </c>
       <c r="Q41" s="2">
@@ -5330,10 +5438,10 @@
       <c r="S41" s="1">
         <v>0</v>
       </c>
-      <c r="T41" s="4">
-        <v>0</v>
-      </c>
-      <c r="U41" s="4">
+      <c r="T41" s="6">
+        <v>0</v>
+      </c>
+      <c r="U41" s="6">
         <v>0</v>
       </c>
       <c r="V41" s="1">
@@ -5383,13 +5491,13 @@
         <v>37</v>
       </c>
       <c r="E42" s="1">
-        <v>2</v>
-      </c>
-      <c r="F42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G42" s="1">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="H42" s="1">
         <f t="shared" si="7"/>
@@ -5422,7 +5530,7 @@
       <c r="O42" s="1">
         <v>36</v>
       </c>
-      <c r="P42" s="4">
+      <c r="P42" s="6">
         <v>37</v>
       </c>
       <c r="Q42" s="2">
@@ -5435,10 +5543,10 @@
       <c r="S42" s="1">
         <v>0</v>
       </c>
-      <c r="T42" s="4">
-        <v>0</v>
-      </c>
-      <c r="U42" s="4">
+      <c r="T42" s="6">
+        <v>0</v>
+      </c>
+      <c r="U42" s="6">
         <v>0</v>
       </c>
       <c r="V42" s="1">
@@ -5488,13 +5596,13 @@
         <v>38</v>
       </c>
       <c r="E43" s="1">
-        <v>2</v>
-      </c>
-      <c r="F43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>72</v>
       </c>
       <c r="G43" s="1">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="H43" s="1">
         <f t="shared" si="7"/>
@@ -5527,7 +5635,7 @@
       <c r="O43" s="1">
         <v>37</v>
       </c>
-      <c r="P43" s="4">
+      <c r="P43" s="6">
         <v>38</v>
       </c>
       <c r="Q43" s="2">
@@ -5540,10 +5648,10 @@
       <c r="S43" s="1">
         <v>0</v>
       </c>
-      <c r="T43" s="4">
-        <v>0</v>
-      </c>
-      <c r="U43" s="4">
+      <c r="T43" s="6">
+        <v>0</v>
+      </c>
+      <c r="U43" s="6">
         <v>0</v>
       </c>
       <c r="V43" s="1">
@@ -5593,13 +5701,13 @@
         <v>39</v>
       </c>
       <c r="E44" s="1">
-        <v>2</v>
-      </c>
-      <c r="F44" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>73</v>
       </c>
       <c r="G44" s="1">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="H44" s="1">
         <f t="shared" si="7"/>
@@ -5632,7 +5740,7 @@
       <c r="O44" s="1">
         <v>38</v>
       </c>
-      <c r="P44" s="4">
+      <c r="P44" s="6">
         <v>39</v>
       </c>
       <c r="Q44" s="2">
@@ -5645,10 +5753,10 @@
       <c r="S44" s="1">
         <v>0</v>
       </c>
-      <c r="T44" s="4">
-        <v>0</v>
-      </c>
-      <c r="U44" s="4">
+      <c r="T44" s="6">
+        <v>0</v>
+      </c>
+      <c r="U44" s="6">
         <v>0</v>
       </c>
       <c r="V44" s="1">
@@ -5666,7 +5774,7 @@
         <v>39</v>
       </c>
       <c r="Z44" s="2">
-        <f>Z43+5000</f>
+        <f t="shared" ref="Z44:Z77" si="15">Z43+5000</f>
         <v>25000</v>
       </c>
       <c r="AA44" s="1">
@@ -5698,13 +5806,13 @@
         <v>40</v>
       </c>
       <c r="E45" s="1">
-        <v>2</v>
-      </c>
-      <c r="F45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="5" t="s">
         <v>74</v>
       </c>
       <c r="G45" s="1">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H45" s="1">
         <f t="shared" si="7"/>
@@ -5737,7 +5845,7 @@
       <c r="O45" s="1">
         <v>39</v>
       </c>
-      <c r="P45" s="4">
+      <c r="P45" s="6">
         <v>40</v>
       </c>
       <c r="Q45" s="2">
@@ -5750,10 +5858,10 @@
       <c r="S45" s="1">
         <v>0</v>
       </c>
-      <c r="T45" s="4">
-        <v>0</v>
-      </c>
-      <c r="U45" s="4">
+      <c r="T45" s="6">
+        <v>0</v>
+      </c>
+      <c r="U45" s="6">
         <v>0</v>
       </c>
       <c r="V45" s="1">
@@ -5771,7 +5879,7 @@
         <v>40</v>
       </c>
       <c r="Z45" s="2">
-        <f>Z44+5000</f>
+        <f t="shared" si="15"/>
         <v>30000</v>
       </c>
       <c r="AA45" s="1">
@@ -5796,188 +5904,3375 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:33">
       <c r="A46" s="2"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="2"/>
-      <c r="AA46" s="2"/>
-      <c r="AB46" s="2"/>
-      <c r="AC46" s="2"/>
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1">
+        <v>41</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G46" s="1">
+        <v>41</v>
+      </c>
+      <c r="H46" s="1">
+        <f t="shared" si="7"/>
+        <v>115650500</v>
+      </c>
+      <c r="I46" s="1">
+        <f t="shared" si="0"/>
+        <v>22795500</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" si="9"/>
+        <v>4478600000</v>
+      </c>
+      <c r="K46" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L46" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M46" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N46" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O46" s="1">
+        <v>39</v>
+      </c>
+      <c r="P46" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q46" s="2">
+        <f t="shared" si="13"/>
+        <v>145</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="6">
+        <v>0</v>
+      </c>
+      <c r="U46" s="6">
+        <v>0</v>
+      </c>
+      <c r="V46" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W46" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X46" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y46" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z46" s="2">
+        <f t="shared" si="15"/>
+        <v>35000</v>
+      </c>
+      <c r="AA46" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB46" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC46" s="2">
+        <f t="shared" si="10"/>
+        <v>3199</v>
+      </c>
+      <c r="AD46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="1">
+        <v>0</v>
+      </c>
       <c r="AG46" s="2">
         <v>179</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:33">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1">
+        <v>42</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G47" s="1">
+        <v>42</v>
+      </c>
+      <c r="H47" s="1">
+        <f t="shared" si="7"/>
+        <v>133556000</v>
+      </c>
+      <c r="I47" s="1">
+        <f t="shared" si="0"/>
+        <v>26988000</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="9"/>
+        <v>5404800000</v>
+      </c>
+      <c r="K47" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L47" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M47" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N47" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O47" s="1">
+        <v>39</v>
+      </c>
+      <c r="P47" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q47" s="2">
+        <f t="shared" si="13"/>
+        <v>150</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="6">
+        <v>0</v>
+      </c>
+      <c r="U47" s="6">
+        <v>0</v>
+      </c>
+      <c r="V47" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W47" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X47" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y47" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z47" s="2">
+        <f t="shared" si="15"/>
+        <v>40000</v>
+      </c>
+      <c r="AA47" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB47" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC47" s="2">
+        <f t="shared" si="10"/>
+        <v>3378</v>
+      </c>
+      <c r="AD47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="1"/>
+      <c r="AF47" s="1">
+        <v>0</v>
+      </c>
       <c r="AG47" s="2">
         <v>181</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:33">
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1">
+        <v>43</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" s="1">
+        <v>43</v>
+      </c>
+      <c r="H48" s="1">
+        <f t="shared" si="7"/>
+        <v>153364500</v>
+      </c>
+      <c r="I48" s="1">
+        <f t="shared" si="0"/>
+        <v>31414500</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="9"/>
+        <v>6406200000</v>
+      </c>
+      <c r="K48" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L48" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M48" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N48" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O48" s="1">
+        <v>39</v>
+      </c>
+      <c r="P48" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q48" s="2">
+        <f t="shared" si="13"/>
+        <v>155</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+      <c r="S48" s="1">
+        <v>0</v>
+      </c>
+      <c r="T48" s="6">
+        <v>0</v>
+      </c>
+      <c r="U48" s="6">
+        <v>0</v>
+      </c>
+      <c r="V48" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W48" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X48" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y48" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z48" s="2">
+        <f t="shared" si="15"/>
+        <v>45000</v>
+      </c>
+      <c r="AA48" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB48" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC48" s="2">
+        <f t="shared" si="10"/>
+        <v>3559</v>
+      </c>
+      <c r="AD48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1">
+        <v>0</v>
+      </c>
       <c r="AG48" s="2">
         <v>191</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="33:33">
+    <row r="49" customHeight="1" spans="3:33">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1">
+        <v>44</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G49" s="1">
+        <v>44</v>
+      </c>
+      <c r="H49" s="1">
+        <f t="shared" si="7"/>
+        <v>172135000</v>
+      </c>
+      <c r="I49" s="1">
+        <f t="shared" si="0"/>
+        <v>35295000</v>
+      </c>
+      <c r="J49" s="1">
+        <f t="shared" si="9"/>
+        <v>7500000000</v>
+      </c>
+      <c r="K49" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L49" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M49" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N49" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O49" s="1">
+        <v>39</v>
+      </c>
+      <c r="P49" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q49" s="2">
+        <f t="shared" si="13"/>
+        <v>160</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+      <c r="S49" s="1">
+        <v>0</v>
+      </c>
+      <c r="T49" s="6">
+        <v>0</v>
+      </c>
+      <c r="U49" s="6">
+        <v>0</v>
+      </c>
+      <c r="V49" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W49" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X49" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y49" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z49" s="2">
+        <f t="shared" si="15"/>
+        <v>50000</v>
+      </c>
+      <c r="AA49" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB49" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC49" s="2">
+        <f t="shared" si="10"/>
+        <v>3750</v>
+      </c>
+      <c r="AD49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="1"/>
+      <c r="AF49" s="1">
+        <v>0</v>
+      </c>
       <c r="AG49" s="2">
         <v>193</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="33:33">
+    <row r="50" customHeight="1" spans="3:33">
+      <c r="C50" s="1">
+        <v>45</v>
+      </c>
+      <c r="D50" s="1">
+        <v>45</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G50" s="1">
+        <v>45</v>
+      </c>
+      <c r="H50" s="1">
+        <f t="shared" si="7"/>
+        <v>200766500</v>
+      </c>
+      <c r="I50" s="1">
+        <f t="shared" si="0"/>
+        <v>40969500</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="9"/>
+        <v>8674600000</v>
+      </c>
+      <c r="K50" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L50" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M50" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N50" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O50" s="1">
+        <v>39</v>
+      </c>
+      <c r="P50" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q50" s="2">
+        <f t="shared" si="13"/>
+        <v>165</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0</v>
+      </c>
+      <c r="U50" s="6">
+        <v>0</v>
+      </c>
+      <c r="V50" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W50" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X50" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y50" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z50" s="2">
+        <f t="shared" si="15"/>
+        <v>55000</v>
+      </c>
+      <c r="AA50" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB50" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC50" s="2">
+        <f t="shared" si="10"/>
+        <v>3943</v>
+      </c>
+      <c r="AD50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1">
+        <v>0</v>
+      </c>
       <c r="AG50" s="2">
         <v>197</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="33:33">
+    <row r="51" customHeight="1" spans="3:33">
+      <c r="C51" s="1">
+        <v>46</v>
+      </c>
+      <c r="D51" s="1">
+        <v>46</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G51" s="1">
+        <v>46</v>
+      </c>
+      <c r="H51" s="1">
+        <f t="shared" si="7"/>
+        <v>231474000</v>
+      </c>
+      <c r="I51" s="1">
+        <f t="shared" si="0"/>
+        <v>45162000</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" si="9"/>
+        <v>9936000000</v>
+      </c>
+      <c r="K51" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L51" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M51" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N51" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O51" s="1">
+        <v>39</v>
+      </c>
+      <c r="P51" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q51" s="2">
+        <f t="shared" si="13"/>
+        <v>170</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+      <c r="S51" s="1">
+        <v>0</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>0</v>
+      </c>
+      <c r="V51" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W51" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X51" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y51" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z51" s="2">
+        <f t="shared" si="15"/>
+        <v>60000</v>
+      </c>
+      <c r="AA51" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB51" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC51" s="2">
+        <f t="shared" si="10"/>
+        <v>4140</v>
+      </c>
+      <c r="AD51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1">
+        <v>0</v>
+      </c>
       <c r="AG51" s="2">
         <v>199</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="33:33">
+    <row r="52" customHeight="1" spans="3:33">
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1">
+        <v>47</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52" s="1">
+        <v>47</v>
+      </c>
+      <c r="H52" s="1">
+        <f t="shared" si="7"/>
+        <v>255261500</v>
+      </c>
+      <c r="I52" s="1">
+        <f t="shared" si="0"/>
+        <v>49939500</v>
+      </c>
+      <c r="J52" s="1">
+        <f t="shared" si="9"/>
+        <v>11281400000</v>
+      </c>
+      <c r="K52" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L52" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M52" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N52" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O52" s="1">
+        <v>39</v>
+      </c>
+      <c r="P52" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q52" s="2">
+        <f t="shared" si="13"/>
+        <v>175</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="T52" s="6">
+        <v>0</v>
+      </c>
+      <c r="U52" s="6">
+        <v>0</v>
+      </c>
+      <c r="V52" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W52" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X52" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y52" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z52" s="2">
+        <f t="shared" si="15"/>
+        <v>65000</v>
+      </c>
+      <c r="AA52" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB52" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC52" s="2">
+        <f t="shared" si="10"/>
+        <v>4339</v>
+      </c>
+      <c r="AD52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="1"/>
+      <c r="AF52" s="1">
+        <v>0</v>
+      </c>
       <c r="AG52" s="2">
         <v>211</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="33:33">
+    <row r="53" customHeight="1" spans="3:33">
+      <c r="C53" s="1">
+        <v>48</v>
+      </c>
+      <c r="D53" s="1">
+        <v>48</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" s="1">
+        <v>48</v>
+      </c>
+      <c r="H53" s="1">
+        <f t="shared" si="7"/>
+        <v>277319000</v>
+      </c>
+      <c r="I53" s="1">
+        <f t="shared" si="0"/>
+        <v>54327000</v>
+      </c>
+      <c r="J53" s="1">
+        <f t="shared" si="9"/>
+        <v>12740000000</v>
+      </c>
+      <c r="K53" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L53" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M53" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N53" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O53" s="1">
+        <v>39</v>
+      </c>
+      <c r="P53" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q53" s="2">
+        <f t="shared" si="13"/>
+        <v>180</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+      <c r="S53" s="1">
+        <v>0</v>
+      </c>
+      <c r="T53" s="6">
+        <v>0</v>
+      </c>
+      <c r="U53" s="6">
+        <v>0</v>
+      </c>
+      <c r="V53" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W53" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X53" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y53" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z53" s="2">
+        <f t="shared" si="15"/>
+        <v>70000</v>
+      </c>
+      <c r="AA53" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB53" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC53" s="2">
+        <f t="shared" si="10"/>
+        <v>4550</v>
+      </c>
+      <c r="AD53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="1"/>
+      <c r="AF53" s="1">
+        <v>0</v>
+      </c>
       <c r="AG53" s="2">
         <v>223</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="33:33">
+    <row r="54" customHeight="1" spans="3:33">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="1">
+        <v>49</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G54" s="1">
+        <v>49</v>
+      </c>
+      <c r="H54" s="1">
+        <f t="shared" si="7"/>
+        <v>302317500</v>
+      </c>
+      <c r="I54" s="1">
+        <f t="shared" si="0"/>
+        <v>61717500</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="9"/>
+        <v>14319000000</v>
+      </c>
+      <c r="K54" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L54" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M54" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N54" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O54" s="1">
+        <v>39</v>
+      </c>
+      <c r="P54" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q54" s="2">
+        <f t="shared" si="13"/>
+        <v>185</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+      <c r="S54" s="1">
+        <v>0</v>
+      </c>
+      <c r="T54" s="6">
+        <v>0</v>
+      </c>
+      <c r="U54" s="6">
+        <v>0</v>
+      </c>
+      <c r="V54" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W54" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X54" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y54" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z54" s="2">
+        <f t="shared" si="15"/>
+        <v>75000</v>
+      </c>
+      <c r="AA54" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB54" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC54" s="2">
+        <f t="shared" si="10"/>
+        <v>4773</v>
+      </c>
+      <c r="AD54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="1"/>
+      <c r="AF54" s="1">
+        <v>0</v>
+      </c>
       <c r="AG54" s="2">
         <v>227</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="33:33">
+    <row r="55" customHeight="1" spans="3:33">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="1">
+        <v>50</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G55" s="1">
+        <v>50</v>
+      </c>
+      <c r="H55" s="1">
+        <f t="shared" si="7"/>
+        <v>330776000</v>
+      </c>
+      <c r="I55" s="1">
+        <f t="shared" si="0"/>
+        <v>69576000</v>
+      </c>
+      <c r="J55" s="1">
+        <f t="shared" si="9"/>
+        <v>16000000000</v>
+      </c>
+      <c r="K55" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L55" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M55" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N55" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O55" s="1">
+        <v>39</v>
+      </c>
+      <c r="P55" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q55" s="2">
+        <f t="shared" si="13"/>
+        <v>190</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="1">
+        <v>0</v>
+      </c>
+      <c r="T55" s="6">
+        <v>0</v>
+      </c>
+      <c r="U55" s="6">
+        <v>0</v>
+      </c>
+      <c r="V55" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W55" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X55" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y55" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z55" s="2">
+        <f t="shared" si="15"/>
+        <v>80000</v>
+      </c>
+      <c r="AA55" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB55" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC55" s="2">
+        <f t="shared" si="10"/>
+        <v>5000</v>
+      </c>
+      <c r="AD55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="1"/>
+      <c r="AF55" s="1">
+        <v>0</v>
+      </c>
       <c r="AG55" s="2">
         <v>229</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="33:33">
+    <row r="56" customHeight="1" spans="3:33">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="1">
+        <v>51</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G56" s="1">
+        <v>51</v>
+      </c>
+      <c r="H56" s="1">
+        <f t="shared" si="7"/>
+        <v>354390500</v>
+      </c>
+      <c r="I56" s="1">
+        <f t="shared" si="0"/>
+        <v>75250500</v>
+      </c>
+      <c r="J56" s="1">
+        <f t="shared" si="9"/>
+        <v>17778600000</v>
+      </c>
+      <c r="K56" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L56" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M56" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N56" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O56" s="1">
+        <v>39</v>
+      </c>
+      <c r="P56" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q56" s="2">
+        <f t="shared" si="13"/>
+        <v>195</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
+        <v>0</v>
+      </c>
+      <c r="T56" s="6">
+        <v>0</v>
+      </c>
+      <c r="U56" s="6">
+        <v>0</v>
+      </c>
+      <c r="V56" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W56" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X56" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y56" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z56" s="2">
+        <f t="shared" si="15"/>
+        <v>85000</v>
+      </c>
+      <c r="AA56" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB56" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC56" s="2">
+        <f t="shared" si="10"/>
+        <v>5229</v>
+      </c>
+      <c r="AD56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="1"/>
+      <c r="AF56" s="1">
+        <v>0</v>
+      </c>
       <c r="AG56" s="2">
         <v>233</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="33:33">
+    <row r="57" customHeight="1" spans="3:33">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="1">
+        <v>52</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G57" s="1">
+        <v>52</v>
+      </c>
+      <c r="H57" s="1">
+        <f t="shared" si="7"/>
+        <v>390807000</v>
+      </c>
+      <c r="I57" s="1">
+        <f t="shared" si="0"/>
+        <v>80379000</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="9"/>
+        <v>19663200000</v>
+      </c>
+      <c r="K57" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L57" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M57" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N57" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O57" s="1">
+        <v>39</v>
+      </c>
+      <c r="P57" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q57" s="2">
+        <f t="shared" si="13"/>
+        <v>200</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="1">
+        <v>0</v>
+      </c>
+      <c r="T57" s="6">
+        <v>0</v>
+      </c>
+      <c r="U57" s="6">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W57" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X57" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y57" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z57" s="2">
+        <f t="shared" si="15"/>
+        <v>90000</v>
+      </c>
+      <c r="AA57" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB57" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC57" s="2">
+        <f t="shared" si="10"/>
+        <v>5462</v>
+      </c>
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="1"/>
+      <c r="AF57" s="1">
+        <v>0</v>
+      </c>
       <c r="AG57" s="2">
         <v>239</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="33:33">
+    <row r="58" customHeight="1" spans="3:33">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="1">
+        <v>53</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G58" s="1">
+        <v>53</v>
+      </c>
+      <c r="H58" s="1">
+        <f t="shared" si="7"/>
+        <v>422379500</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="0"/>
+        <v>86326500</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="9"/>
+        <v>21663800000</v>
+      </c>
+      <c r="K58" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L58" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M58" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N58" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O58" s="1">
+        <v>39</v>
+      </c>
+      <c r="P58" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q58" s="2">
+        <f t="shared" si="13"/>
+        <v>205</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0</v>
+      </c>
+      <c r="S58" s="1">
+        <v>0</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0</v>
+      </c>
+      <c r="V58" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W58" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X58" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y58" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z58" s="2">
+        <f t="shared" si="15"/>
+        <v>95000</v>
+      </c>
+      <c r="AA58" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB58" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC58" s="2">
+        <f t="shared" si="10"/>
+        <v>5701</v>
+      </c>
+      <c r="AD58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="1"/>
+      <c r="AF58" s="1">
+        <v>0</v>
+      </c>
       <c r="AG58" s="2">
         <v>241</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="33:33">
+    <row r="59" customHeight="1" spans="3:33">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="1">
+        <v>54</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G59" s="1">
+        <v>54</v>
+      </c>
+      <c r="H59" s="1">
+        <f t="shared" si="7"/>
+        <v>454990000</v>
+      </c>
+      <c r="I59" s="1">
+        <f t="shared" si="0"/>
+        <v>93210000</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="9"/>
+        <v>23768000000</v>
+      </c>
+      <c r="K59" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L59" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M59" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N59" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O59" s="1">
+        <v>39</v>
+      </c>
+      <c r="P59" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q59" s="2">
+        <f t="shared" si="13"/>
+        <v>210</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+      <c r="S59" s="1">
+        <v>0</v>
+      </c>
+      <c r="T59" s="6">
+        <v>0</v>
+      </c>
+      <c r="U59" s="6">
+        <v>0</v>
+      </c>
+      <c r="V59" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W59" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X59" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y59" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z59" s="2">
+        <f t="shared" si="15"/>
+        <v>100000</v>
+      </c>
+      <c r="AA59" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB59" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC59" s="2">
+        <f t="shared" si="10"/>
+        <v>5942</v>
+      </c>
+      <c r="AD59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="1"/>
+      <c r="AF59" s="1">
+        <v>0</v>
+      </c>
       <c r="AG59" s="2">
         <v>251</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="33:33">
+    <row r="60" customHeight="1" spans="3:33">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="1">
+        <v>55</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G60" s="1">
+        <v>55</v>
+      </c>
+      <c r="H60" s="1">
+        <f t="shared" si="7"/>
+        <v>488638500</v>
+      </c>
+      <c r="I60" s="1">
+        <f t="shared" si="0"/>
+        <v>98689500</v>
+      </c>
+      <c r="J60" s="1">
+        <f t="shared" si="9"/>
+        <v>26010600000</v>
+      </c>
+      <c r="K60" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L60" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M60" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N60" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O60" s="1">
+        <v>39</v>
+      </c>
+      <c r="P60" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q60" s="2">
+        <f t="shared" si="13"/>
+        <v>215</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
+      </c>
+      <c r="T60" s="6">
+        <v>0</v>
+      </c>
+      <c r="U60" s="6">
+        <v>0</v>
+      </c>
+      <c r="V60" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W60" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X60" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y60" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z60" s="2">
+        <f t="shared" si="15"/>
+        <v>105000</v>
+      </c>
+      <c r="AA60" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB60" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC60" s="2">
+        <f t="shared" si="10"/>
+        <v>6193</v>
+      </c>
+      <c r="AD60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="1"/>
+      <c r="AF60" s="1">
+        <v>0</v>
+      </c>
       <c r="AG60" s="2">
         <v>257</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="33:33">
+    <row r="61" customHeight="1" spans="3:33">
+      <c r="C61" s="1">
+        <v>56</v>
+      </c>
+      <c r="D61" s="1">
+        <v>56</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G61" s="1">
+        <v>56</v>
+      </c>
+      <c r="H61" s="1">
+        <f t="shared" si="7"/>
+        <v>515713000</v>
+      </c>
+      <c r="I61" s="1">
+        <f t="shared" si="0"/>
+        <v>107679000</v>
+      </c>
+      <c r="J61" s="1">
+        <f t="shared" si="9"/>
+        <v>28380000000</v>
+      </c>
+      <c r="K61" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L61" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M61" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N61" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O61" s="1">
+        <v>39</v>
+      </c>
+      <c r="P61" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q61" s="2">
+        <f t="shared" si="13"/>
+        <v>220</v>
+      </c>
+      <c r="R61" s="1">
+        <v>0</v>
+      </c>
+      <c r="S61" s="1">
+        <v>0</v>
+      </c>
+      <c r="T61" s="6">
+        <v>0</v>
+      </c>
+      <c r="U61" s="6">
+        <v>0</v>
+      </c>
+      <c r="V61" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W61" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X61" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y61" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z61" s="2">
+        <f t="shared" si="15"/>
+        <v>110000</v>
+      </c>
+      <c r="AA61" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB61" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC61" s="2">
+        <f t="shared" si="10"/>
+        <v>6450</v>
+      </c>
+      <c r="AD61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="1"/>
+      <c r="AF61" s="1">
+        <v>0</v>
+      </c>
       <c r="AG61" s="2">
         <v>263</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="33:33">
+    <row r="62" customHeight="1" spans="3:33">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="1">
+        <v>57</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G62" s="1">
+        <v>57</v>
+      </c>
+      <c r="H62" s="1">
+        <f t="shared" si="7"/>
+        <v>551091500</v>
+      </c>
+      <c r="I62" s="1">
+        <f t="shared" si="0"/>
+        <v>115264500</v>
+      </c>
+      <c r="J62" s="1">
+        <f t="shared" si="9"/>
+        <v>30879800000</v>
+      </c>
+      <c r="K62" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L62" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N62" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O62" s="1">
+        <v>39</v>
+      </c>
+      <c r="P62" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q62" s="2">
+        <f t="shared" si="13"/>
+        <v>225</v>
+      </c>
+      <c r="R62" s="1">
+        <v>0</v>
+      </c>
+      <c r="S62" s="1">
+        <v>0</v>
+      </c>
+      <c r="T62" s="6">
+        <v>0</v>
+      </c>
+      <c r="U62" s="6">
+        <v>0</v>
+      </c>
+      <c r="V62" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W62" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X62" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y62" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z62" s="2">
+        <f t="shared" si="15"/>
+        <v>115000</v>
+      </c>
+      <c r="AA62" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB62" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC62" s="2">
+        <f t="shared" si="10"/>
+        <v>6713</v>
+      </c>
+      <c r="AD62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="1"/>
+      <c r="AF62" s="1">
+        <v>0</v>
+      </c>
       <c r="AG62" s="2">
         <v>269</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="33:33">
+    <row r="63" customHeight="1" spans="3:33">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="1">
+        <v>58</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G63" s="1">
+        <v>58</v>
+      </c>
+      <c r="H63" s="1">
+        <f t="shared" si="7"/>
+        <v>583356000</v>
+      </c>
+      <c r="I63" s="1">
+        <f t="shared" si="0"/>
+        <v>123084000</v>
+      </c>
+      <c r="J63" s="1">
+        <f t="shared" si="9"/>
+        <v>33513600000</v>
+      </c>
+      <c r="K63" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L63" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N63" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O63" s="1">
+        <v>39</v>
+      </c>
+      <c r="P63" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q63" s="2">
+        <f t="shared" si="13"/>
+        <v>230</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="1">
+        <v>0</v>
+      </c>
+      <c r="T63" s="6">
+        <v>0</v>
+      </c>
+      <c r="U63" s="6">
+        <v>0</v>
+      </c>
+      <c r="V63" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W63" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X63" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z63" s="2">
+        <f t="shared" si="15"/>
+        <v>120000</v>
+      </c>
+      <c r="AA63" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB63" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC63" s="2">
+        <f t="shared" si="10"/>
+        <v>6982</v>
+      </c>
+      <c r="AD63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="1"/>
+      <c r="AF63" s="1">
+        <v>0</v>
+      </c>
       <c r="AG63" s="2">
         <v>271</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="33:33">
+    <row r="64" customHeight="1" spans="3:33">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="1">
+        <v>59</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G64" s="1">
+        <v>59</v>
+      </c>
+      <c r="H64" s="1">
+        <f t="shared" si="7"/>
+        <v>611987500</v>
+      </c>
+      <c r="I64" s="1">
+        <f t="shared" si="0"/>
+        <v>131137500</v>
+      </c>
+      <c r="J64" s="1">
+        <f t="shared" si="9"/>
+        <v>36265000000</v>
+      </c>
+      <c r="K64" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L64" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M64" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N64" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O64" s="1">
+        <v>39</v>
+      </c>
+      <c r="P64" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q64" s="2">
+        <f t="shared" si="13"/>
+        <v>235</v>
+      </c>
+      <c r="R64" s="1">
+        <v>0</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0</v>
+      </c>
+      <c r="T64" s="6">
+        <v>0</v>
+      </c>
+      <c r="U64" s="6">
+        <v>0</v>
+      </c>
+      <c r="V64" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W64" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X64" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y64" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z64" s="2">
+        <f t="shared" si="15"/>
+        <v>125000</v>
+      </c>
+      <c r="AA64" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB64" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC64" s="2">
+        <f t="shared" si="10"/>
+        <v>7253</v>
+      </c>
+      <c r="AD64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="1"/>
+      <c r="AF64" s="1">
+        <v>0</v>
+      </c>
       <c r="AG64" s="2">
         <v>277</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="33:33">
+    <row r="65" customHeight="1" spans="3:33">
+      <c r="C65" s="1">
+        <v>60</v>
+      </c>
+      <c r="D65" s="1">
+        <v>60</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G65" s="1">
+        <v>60</v>
+      </c>
+      <c r="H65" s="1">
+        <f t="shared" si="7"/>
+        <v>658957000</v>
+      </c>
+      <c r="I65" s="1">
+        <f t="shared" si="0"/>
+        <v>137397000</v>
+      </c>
+      <c r="J65" s="1">
+        <f t="shared" si="9"/>
+        <v>39156000000</v>
+      </c>
+      <c r="K65" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L65" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M65" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N65" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O65" s="1">
+        <v>39</v>
+      </c>
+      <c r="P65" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q65" s="2">
+        <f t="shared" si="13"/>
+        <v>240</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+      <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="T65" s="6">
+        <v>0</v>
+      </c>
+      <c r="U65" s="6">
+        <v>0</v>
+      </c>
+      <c r="V65" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W65" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X65" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y65" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z65" s="2">
+        <f t="shared" si="15"/>
+        <v>130000</v>
+      </c>
+      <c r="AA65" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB65" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC65" s="2">
+        <f t="shared" si="10"/>
+        <v>7530</v>
+      </c>
+      <c r="AD65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="1"/>
+      <c r="AF65" s="1">
+        <v>0</v>
+      </c>
       <c r="AG65" s="2">
         <v>281</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="33:33">
+    <row r="66" customHeight="1" spans="3:33">
+      <c r="C66" s="1">
+        <v>61</v>
+      </c>
+      <c r="D66" s="1">
+        <v>61</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G66" s="1">
+        <v>61</v>
+      </c>
+      <c r="H66" s="1">
+        <f t="shared" si="7"/>
+        <v>716998500</v>
+      </c>
+      <c r="I66" s="1">
+        <f t="shared" si="0"/>
+        <v>145840500</v>
+      </c>
+      <c r="J66" s="1">
+        <f t="shared" si="9"/>
+        <v>42179400000</v>
+      </c>
+      <c r="K66" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L66" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N66" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O66" s="1">
+        <v>39</v>
+      </c>
+      <c r="P66" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q66" s="2">
+        <f t="shared" si="13"/>
+        <v>245</v>
+      </c>
+      <c r="R66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
+      </c>
+      <c r="T66" s="6">
+        <v>0</v>
+      </c>
+      <c r="U66" s="6">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W66" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X66" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y66" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z66" s="2">
+        <f t="shared" si="15"/>
+        <v>135000</v>
+      </c>
+      <c r="AA66" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB66" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC66" s="2">
+        <f t="shared" si="10"/>
+        <v>7811</v>
+      </c>
+      <c r="AD66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="1"/>
+      <c r="AF66" s="1">
+        <v>0</v>
+      </c>
       <c r="AG66" s="2">
         <v>283</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="33:33">
+    <row r="67" customHeight="1" spans="3:33">
+      <c r="C67" s="1">
+        <v>62</v>
+      </c>
+      <c r="D67" s="1">
+        <v>62</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G67" s="1">
+        <v>62</v>
+      </c>
+      <c r="H67" s="1">
+        <f t="shared" si="7"/>
+        <v>753242000</v>
+      </c>
+      <c r="I67" s="1">
+        <f t="shared" si="0"/>
+        <v>153426000</v>
+      </c>
+      <c r="J67" s="1">
+        <f t="shared" si="9"/>
+        <v>45326400000</v>
+      </c>
+      <c r="K67" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L67" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M67" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N67" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O67" s="1">
+        <v>39</v>
+      </c>
+      <c r="P67" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q67" s="2">
+        <f t="shared" si="13"/>
+        <v>250</v>
+      </c>
+      <c r="R67" s="1">
+        <v>0</v>
+      </c>
+      <c r="S67" s="1">
+        <v>0</v>
+      </c>
+      <c r="T67" s="6">
+        <v>0</v>
+      </c>
+      <c r="U67" s="6">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W67" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X67" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y67" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z67" s="2">
+        <f t="shared" si="15"/>
+        <v>140000</v>
+      </c>
+      <c r="AA67" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB67" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC67" s="2">
+        <f t="shared" si="10"/>
+        <v>8094</v>
+      </c>
+      <c r="AD67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="1"/>
+      <c r="AF67" s="1">
+        <v>0</v>
+      </c>
       <c r="AG67" s="2">
         <v>293</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="33:33">
+    <row r="68" customHeight="1" spans="3:33">
+      <c r="C68" s="1">
+        <v>63</v>
+      </c>
+      <c r="D68" s="1">
+        <v>63</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G68" s="1">
+        <v>63</v>
+      </c>
+      <c r="H68" s="1">
+        <f t="shared" si="7"/>
+        <v>785160500</v>
+      </c>
+      <c r="I68" s="1">
+        <f t="shared" si="0"/>
+        <v>160036500</v>
+      </c>
+      <c r="J68" s="1">
+        <f t="shared" si="9"/>
+        <v>48644600000</v>
+      </c>
+      <c r="K68" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L68" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M68" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N68" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O68" s="1">
+        <v>39</v>
+      </c>
+      <c r="P68" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q68" s="2">
+        <f t="shared" si="13"/>
+        <v>255</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="6">
+        <v>0</v>
+      </c>
+      <c r="U68" s="6">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W68" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X68" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z68" s="2">
+        <f t="shared" si="15"/>
+        <v>145000</v>
+      </c>
+      <c r="AA68" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB68" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC68" s="2">
+        <f t="shared" si="10"/>
+        <v>8387</v>
+      </c>
+      <c r="AD68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="1"/>
+      <c r="AF68" s="1">
+        <v>0</v>
+      </c>
       <c r="AG68" s="2">
         <v>307</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="33:33">
+    <row r="69" customHeight="1" spans="3:33">
+      <c r="C69" s="1">
+        <v>64</v>
+      </c>
+      <c r="D69" s="1">
+        <v>64</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G69" s="1">
+        <v>64</v>
+      </c>
+      <c r="H69" s="1">
+        <f t="shared" si="7"/>
+        <v>822615000</v>
+      </c>
+      <c r="I69" s="1">
+        <f t="shared" si="0"/>
+        <v>171405000</v>
+      </c>
+      <c r="J69" s="1">
+        <f t="shared" si="9"/>
+        <v>52164000000</v>
+      </c>
+      <c r="K69" s="1">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="L69" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="M69" s="1">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="N69" s="1">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="O69" s="1">
+        <v>39</v>
+      </c>
+      <c r="P69" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q69" s="2">
+        <f t="shared" si="13"/>
+        <v>260</v>
+      </c>
+      <c r="R69" s="1">
+        <v>0</v>
+      </c>
+      <c r="S69" s="1">
+        <v>0</v>
+      </c>
+      <c r="T69" s="6">
+        <v>0</v>
+      </c>
+      <c r="U69" s="6">
+        <v>0</v>
+      </c>
+      <c r="V69" s="1">
+        <f t="shared" si="5"/>
+        <v>490</v>
+      </c>
+      <c r="W69" s="1">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="X69" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y69" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z69" s="2">
+        <f t="shared" si="15"/>
+        <v>150000</v>
+      </c>
+      <c r="AA69" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB69" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC69" s="2">
+        <f t="shared" si="10"/>
+        <v>8694</v>
+      </c>
+      <c r="AD69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="1"/>
+      <c r="AF69" s="1">
+        <v>0</v>
+      </c>
       <c r="AG69" s="2">
         <v>311</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="33:33">
+    <row r="70" customHeight="1" spans="3:33">
+      <c r="C70" s="1">
+        <v>65</v>
+      </c>
+      <c r="D70" s="1">
+        <v>65</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G70" s="1">
+        <v>65</v>
+      </c>
+      <c r="H70" s="1">
+        <f t="shared" si="7"/>
+        <v>887576500</v>
+      </c>
+      <c r="I70" s="1">
+        <f t="shared" ref="I70:I77" si="16">AB70*AG68*Z70/10</f>
+        <v>185581500</v>
+      </c>
+      <c r="J70" s="1">
+        <f t="shared" si="9"/>
+        <v>55831000000</v>
+      </c>
+      <c r="K70" s="1">
+        <f t="shared" ref="K70:K77" si="17">Y70*5</f>
+        <v>200</v>
+      </c>
+      <c r="L70" s="1">
+        <f t="shared" ref="L70:L77" si="18">Y70*3</f>
+        <v>120</v>
+      </c>
+      <c r="M70" s="1">
+        <f t="shared" ref="M70:M77" si="19">Y70*2</f>
+        <v>80</v>
+      </c>
+      <c r="N70" s="1">
+        <f t="shared" ref="N70:N77" si="20">Y70*4</f>
+        <v>160</v>
+      </c>
+      <c r="O70" s="1">
+        <v>39</v>
+      </c>
+      <c r="P70" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q70" s="2">
+        <f t="shared" si="13"/>
+        <v>265</v>
+      </c>
+      <c r="R70" s="1">
+        <v>0</v>
+      </c>
+      <c r="S70" s="1">
+        <v>0</v>
+      </c>
+      <c r="T70" s="6">
+        <v>0</v>
+      </c>
+      <c r="U70" s="6">
+        <v>0</v>
+      </c>
+      <c r="V70" s="1">
+        <f t="shared" ref="V70:V77" si="21">X70*10</f>
+        <v>490</v>
+      </c>
+      <c r="W70" s="1">
+        <f t="shared" ref="W70:W77" si="22">X70*10</f>
+        <v>490</v>
+      </c>
+      <c r="X70" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y70" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z70" s="2">
+        <f t="shared" si="15"/>
+        <v>155000</v>
+      </c>
+      <c r="AA70" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB70" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC70" s="2">
+        <f t="shared" si="10"/>
+        <v>9005</v>
+      </c>
+      <c r="AD70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="1"/>
+      <c r="AF70" s="1">
+        <v>0</v>
+      </c>
       <c r="AG70" s="2">
         <v>313</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="33:33">
+    <row r="71" customHeight="1" spans="3:33">
+      <c r="C71" s="1">
+        <v>66</v>
+      </c>
+      <c r="D71" s="1">
+        <v>66</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G71" s="1">
+        <v>66</v>
+      </c>
+      <c r="H71" s="1">
+        <f t="shared" ref="H71:H77" si="23">AG73*Z71*AA71/10</f>
+        <v>932816000</v>
+      </c>
+      <c r="I71" s="1">
+        <f t="shared" si="16"/>
+        <v>194064000</v>
+      </c>
+      <c r="J71" s="1">
+        <f t="shared" si="9"/>
+        <v>59635200000</v>
+      </c>
+      <c r="K71" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L71" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M71" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N71" s="1">
+        <f t="shared" si="20"/>
+        <v>160</v>
+      </c>
+      <c r="O71" s="1">
+        <v>39</v>
+      </c>
+      <c r="P71" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q71" s="2">
+        <f t="shared" si="13"/>
+        <v>270</v>
+      </c>
+      <c r="R71" s="1">
+        <v>0</v>
+      </c>
+      <c r="S71" s="1">
+        <v>0</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0</v>
+      </c>
+      <c r="U71" s="6">
+        <v>0</v>
+      </c>
+      <c r="V71" s="1">
+        <f t="shared" si="21"/>
+        <v>490</v>
+      </c>
+      <c r="W71" s="1">
+        <f t="shared" si="22"/>
+        <v>490</v>
+      </c>
+      <c r="X71" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y71" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z71" s="2">
+        <f t="shared" si="15"/>
+        <v>160000</v>
+      </c>
+      <c r="AA71" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB71" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC71" s="2">
+        <f t="shared" si="10"/>
+        <v>9318</v>
+      </c>
+      <c r="AD71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="1"/>
+      <c r="AF71" s="1">
+        <v>0</v>
+      </c>
       <c r="AG71" s="2">
         <v>317</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="33:33">
+    <row r="72" customHeight="1" spans="3:33">
+      <c r="C72" s="1">
+        <v>67</v>
+      </c>
+      <c r="D72" s="1">
+        <v>67</v>
+      </c>
+      <c r="E72" s="1">
+        <v>1</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G72" s="1">
+        <v>67</v>
+      </c>
+      <c r="H72" s="1">
+        <f t="shared" si="23"/>
+        <v>990511500</v>
+      </c>
+      <c r="I72" s="1">
+        <f t="shared" si="16"/>
+        <v>201415500</v>
+      </c>
+      <c r="J72" s="1">
+        <f t="shared" si="9"/>
+        <v>63591000000</v>
+      </c>
+      <c r="K72" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L72" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M72" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N72" s="1">
+        <f t="shared" si="20"/>
+        <v>160</v>
+      </c>
+      <c r="O72" s="1">
+        <v>39</v>
+      </c>
+      <c r="P72" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q72" s="2">
+        <f t="shared" si="13"/>
+        <v>275</v>
+      </c>
+      <c r="R72" s="1">
+        <v>0</v>
+      </c>
+      <c r="S72" s="1">
+        <v>0</v>
+      </c>
+      <c r="T72" s="6">
+        <v>0</v>
+      </c>
+      <c r="U72" s="6">
+        <v>0</v>
+      </c>
+      <c r="V72" s="1">
+        <f t="shared" si="21"/>
+        <v>490</v>
+      </c>
+      <c r="W72" s="1">
+        <f t="shared" si="22"/>
+        <v>490</v>
+      </c>
+      <c r="X72" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y72" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z72" s="2">
+        <f t="shared" si="15"/>
+        <v>165000</v>
+      </c>
+      <c r="AA72" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB72" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC72" s="2">
+        <f t="shared" si="10"/>
+        <v>9635</v>
+      </c>
+      <c r="AD72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="1"/>
+      <c r="AF72" s="1">
+        <v>0</v>
+      </c>
       <c r="AG72" s="2">
         <v>331</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="33:33">
+    <row r="73" customHeight="1" spans="3:33">
+      <c r="C73" s="1">
+        <v>68</v>
+      </c>
+      <c r="D73" s="1">
+        <v>68</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G73" s="1">
+        <v>68</v>
+      </c>
+      <c r="H73" s="1">
+        <f t="shared" si="23"/>
+        <v>1026409000</v>
+      </c>
+      <c r="I73" s="1">
+        <f t="shared" si="16"/>
+        <v>210171000</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" ref="J73:J77" si="24">Y73*Z73*AC73</f>
+        <v>67768800000</v>
+      </c>
+      <c r="K73" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L73" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M73" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N73" s="1">
+        <f t="shared" si="20"/>
+        <v>160</v>
+      </c>
+      <c r="O73" s="1">
+        <v>39</v>
+      </c>
+      <c r="P73" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q73" s="2">
+        <f t="shared" si="13"/>
+        <v>280</v>
+      </c>
+      <c r="R73" s="1">
+        <v>0</v>
+      </c>
+      <c r="S73" s="1">
+        <v>0</v>
+      </c>
+      <c r="T73" s="6">
+        <v>0</v>
+      </c>
+      <c r="U73" s="6">
+        <v>0</v>
+      </c>
+      <c r="V73" s="1">
+        <f t="shared" si="21"/>
+        <v>490</v>
+      </c>
+      <c r="W73" s="1">
+        <f t="shared" si="22"/>
+        <v>490</v>
+      </c>
+      <c r="X73" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y73" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z73" s="2">
+        <f t="shared" si="15"/>
+        <v>170000</v>
+      </c>
+      <c r="AA73" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB73" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC73" s="2">
+        <f t="shared" si="10"/>
+        <v>9966</v>
+      </c>
+      <c r="AD73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="1"/>
+      <c r="AF73" s="1">
+        <v>0</v>
+      </c>
       <c r="AG73" s="2">
         <v>337</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="33:33">
+    <row r="74" customHeight="1" spans="3:33">
+      <c r="C74" s="1">
+        <v>69</v>
+      </c>
+      <c r="D74" s="1">
+        <v>69</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G74" s="1">
+        <v>69</v>
+      </c>
+      <c r="H74" s="1">
+        <f t="shared" si="23"/>
+        <v>1068707500</v>
+      </c>
+      <c r="I74" s="1">
+        <f t="shared" si="16"/>
+        <v>225907500</v>
+      </c>
+      <c r="J74" s="1">
+        <f t="shared" si="24"/>
+        <v>72121000000</v>
+      </c>
+      <c r="K74" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L74" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M74" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N74" s="1">
+        <f t="shared" si="20"/>
+        <v>160</v>
+      </c>
+      <c r="O74" s="1">
+        <v>39</v>
+      </c>
+      <c r="P74" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q74" s="2">
+        <f t="shared" si="13"/>
+        <v>285</v>
+      </c>
+      <c r="R74" s="1">
+        <v>0</v>
+      </c>
+      <c r="S74" s="1">
+        <v>0</v>
+      </c>
+      <c r="T74" s="6">
+        <v>0</v>
+      </c>
+      <c r="U74" s="6">
+        <v>0</v>
+      </c>
+      <c r="V74" s="1">
+        <f t="shared" si="21"/>
+        <v>490</v>
+      </c>
+      <c r="W74" s="1">
+        <f t="shared" si="22"/>
+        <v>490</v>
+      </c>
+      <c r="X74" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y74" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z74" s="2">
+        <f t="shared" si="15"/>
+        <v>175000</v>
+      </c>
+      <c r="AA74" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB74" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC74" s="2">
+        <f t="shared" si="10"/>
+        <v>10303</v>
+      </c>
+      <c r="AD74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="1"/>
+      <c r="AF74" s="1">
+        <v>0</v>
+      </c>
       <c r="AG74" s="2">
         <v>347</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="33:33">
+    <row r="75" customHeight="1" spans="3:33">
+      <c r="C75" s="1">
+        <v>70</v>
+      </c>
+      <c r="D75" s="1">
+        <v>70</v>
+      </c>
+      <c r="E75" s="1">
+        <v>1</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G75" s="1">
+        <v>70</v>
+      </c>
+      <c r="H75" s="1">
+        <f t="shared" si="23"/>
+        <v>1117926000</v>
+      </c>
+      <c r="I75" s="1">
+        <f t="shared" si="16"/>
+        <v>236574000</v>
+      </c>
+      <c r="J75" s="1">
+        <f t="shared" si="24"/>
+        <v>76680000000</v>
+      </c>
+      <c r="K75" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L75" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M75" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N75" s="1">
+        <f t="shared" si="20"/>
+        <v>160</v>
+      </c>
+      <c r="O75" s="1">
+        <v>39</v>
+      </c>
+      <c r="P75" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q75" s="2">
+        <f t="shared" si="13"/>
+        <v>290</v>
+      </c>
+      <c r="R75" s="1">
+        <v>0</v>
+      </c>
+      <c r="S75" s="1">
+        <v>0</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>0</v>
+      </c>
+      <c r="V75" s="1">
+        <f t="shared" si="21"/>
+        <v>490</v>
+      </c>
+      <c r="W75" s="1">
+        <f t="shared" si="22"/>
+        <v>490</v>
+      </c>
+      <c r="X75" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y75" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z75" s="2">
+        <f t="shared" si="15"/>
+        <v>180000</v>
+      </c>
+      <c r="AA75" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB75" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC75" s="2">
+        <f t="shared" si="10"/>
+        <v>10650</v>
+      </c>
+      <c r="AD75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="1"/>
+      <c r="AF75" s="1">
+        <v>0</v>
+      </c>
       <c r="AG75" s="2">
         <v>349</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="33:33">
+    <row r="76" customHeight="1" spans="3:33">
+      <c r="C76" s="1">
+        <v>71</v>
+      </c>
+      <c r="D76" s="1">
+        <v>71</v>
+      </c>
+      <c r="E76" s="1">
+        <v>1</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G76" s="1">
+        <v>71</v>
+      </c>
+      <c r="H76" s="1">
+        <f t="shared" si="23"/>
+        <v>1174583500</v>
+      </c>
+      <c r="I76" s="1">
+        <f t="shared" si="16"/>
+        <v>250360500</v>
+      </c>
+      <c r="J76" s="1">
+        <f t="shared" si="24"/>
+        <v>81392600000</v>
+      </c>
+      <c r="K76" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L76" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M76" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N76" s="1">
+        <f t="shared" si="20"/>
+        <v>160</v>
+      </c>
+      <c r="O76" s="1">
+        <v>39</v>
+      </c>
+      <c r="P76" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q76" s="2">
+        <f t="shared" si="13"/>
+        <v>295</v>
+      </c>
+      <c r="R76" s="1">
+        <v>0</v>
+      </c>
+      <c r="S76" s="1">
+        <v>0</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0</v>
+      </c>
+      <c r="U76" s="6">
+        <v>0</v>
+      </c>
+      <c r="V76" s="1">
+        <f t="shared" si="21"/>
+        <v>490</v>
+      </c>
+      <c r="W76" s="1">
+        <f t="shared" si="22"/>
+        <v>490</v>
+      </c>
+      <c r="X76" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y76" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z76" s="2">
+        <f t="shared" si="15"/>
+        <v>185000</v>
+      </c>
+      <c r="AA76" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB76" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC76" s="2">
+        <f>AC75+AG75</f>
+        <v>10999</v>
+      </c>
+      <c r="AD76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="1"/>
+      <c r="AF76" s="1">
+        <v>0</v>
+      </c>
       <c r="AG76" s="2">
         <v>353</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="33:33">
+    <row r="77" customHeight="1" spans="3:33">
+      <c r="C77" s="1">
+        <v>72</v>
+      </c>
+      <c r="D77" s="1">
+        <v>72</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G77" s="1">
+        <v>72</v>
+      </c>
+      <c r="H77" s="1">
+        <f t="shared" si="23"/>
+        <v>1226051000</v>
+      </c>
+      <c r="I77" s="1">
+        <f t="shared" si="16"/>
+        <v>258609000</v>
+      </c>
+      <c r="J77" s="1">
+        <f t="shared" si="24"/>
+        <v>86275200000</v>
+      </c>
+      <c r="K77" s="1">
+        <f t="shared" si="17"/>
+        <v>200</v>
+      </c>
+      <c r="L77" s="1">
+        <f t="shared" si="18"/>
+        <v>120</v>
+      </c>
+      <c r="M77" s="1">
+        <f t="shared" si="19"/>
+        <v>80</v>
+      </c>
+      <c r="N77" s="1">
+        <f t="shared" si="20"/>
+        <v>160</v>
+      </c>
+      <c r="O77" s="1">
+        <v>39</v>
+      </c>
+      <c r="P77" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q77" s="2">
+        <f t="shared" si="13"/>
+        <v>300</v>
+      </c>
+      <c r="R77" s="1">
+        <v>0</v>
+      </c>
+      <c r="S77" s="1">
+        <v>0</v>
+      </c>
+      <c r="T77" s="6">
+        <v>0</v>
+      </c>
+      <c r="U77" s="6">
+        <v>0</v>
+      </c>
+      <c r="V77" s="1">
+        <f t="shared" si="21"/>
+        <v>490</v>
+      </c>
+      <c r="W77" s="1">
+        <f t="shared" si="22"/>
+        <v>490</v>
+      </c>
+      <c r="X77" s="1">
+        <v>49</v>
+      </c>
+      <c r="Y77" s="1">
+        <v>40</v>
+      </c>
+      <c r="Z77" s="2">
+        <f t="shared" si="15"/>
+        <v>190000</v>
+      </c>
+      <c r="AA77" s="1">
+        <v>173</v>
+      </c>
+      <c r="AB77" s="2">
+        <v>39</v>
+      </c>
+      <c r="AC77" s="2">
+        <f>AC76+AG76</f>
+        <v>11352</v>
+      </c>
+      <c r="AD77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="1"/>
+      <c r="AF77" s="1">
+        <v>0</v>
+      </c>
       <c r="AG77" s="2">
         <v>359</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="33:33">
+    <row r="78" customHeight="1" spans="3:33">
       <c r="AG78" s="2">
         <v>367</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="33:33">
+    <row r="79" customHeight="1" spans="3:33">
       <c r="AG79" s="2">
         <v>373</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="33:33">
+    <row r="80" customHeight="1" spans="3:33">
       <c r="AG80" s="2">
         <v>379</v>
       </c>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="14" spans="1:33">
+    <row r="6" spans="1:33">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H8" s="1">
         <f t="shared" si="7"/>
-        <v>770</v>
+        <v>616</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" si="0"/>
@@ -2001,7 +2001,7 @@
         <v>140</v>
       </c>
       <c r="AA8" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB8" s="2">
         <v>2</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="H9" s="1">
         <f t="shared" si="7"/>
-        <v>1456</v>
+        <v>1040</v>
       </c>
       <c r="I9" s="1">
         <f t="shared" si="0"/>
@@ -2105,7 +2105,7 @@
         <v>160</v>
       </c>
       <c r="AA9" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB9" s="2">
         <v>3</v>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="H10" s="1">
         <f t="shared" si="7"/>
-        <v>3366</v>
+        <v>1836</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" si="0"/>
@@ -2209,7 +2209,7 @@
         <v>180</v>
       </c>
       <c r="AA10" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AB10" s="2">
         <v>4</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="H11" s="1">
         <f t="shared" si="7"/>
-        <v>4940</v>
+        <v>2660</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" si="0"/>
@@ -2313,7 +2313,7 @@
         <v>200</v>
       </c>
       <c r="AA11" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AB11" s="2">
         <v>5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="H12" s="1">
         <f t="shared" si="7"/>
-        <v>9384</v>
+        <v>4416</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="0"/>
@@ -2417,7 +2417,7 @@
         <v>240</v>
       </c>
       <c r="AA12" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AB12" s="2">
         <v>6</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H13" s="1">
         <f t="shared" si="7"/>
-        <v>15428</v>
+        <v>7308</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="0"/>
@@ -2522,7 +2522,7 @@
         <v>280</v>
       </c>
       <c r="AA13" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AB13" s="2">
         <v>7</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="H14" s="1">
         <f t="shared" si="7"/>
-        <v>22816</v>
+        <v>9920</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="0"/>
@@ -2627,7 +2627,7 @@
         <v>320</v>
       </c>
       <c r="AA14" s="2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AB14" s="2">
         <v>8</v>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="H15" s="1">
         <f t="shared" si="7"/>
-        <v>38628</v>
+        <v>14652</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" si="0"/>
@@ -2732,7 +2732,7 @@
         <v>360</v>
       </c>
       <c r="AA15" s="2">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="AB15" s="2">
         <v>9</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="H16" s="1">
         <f t="shared" si="7"/>
-        <v>50840</v>
+        <v>21320</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" si="0"/>
@@ -2837,7 +2837,7 @@
         <v>400</v>
       </c>
       <c r="AA16" s="2">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="AB16" s="2">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="H17" s="1">
         <f t="shared" si="7"/>
-        <v>79550</v>
+        <v>36550</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" si="0"/>
@@ -2942,7 +2942,7 @@
         <v>500</v>
       </c>
       <c r="AA17" s="2">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="AB17" s="2">
         <v>11</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="H18" s="1">
         <f t="shared" si="7"/>
-        <v>115620</v>
+        <v>53580</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="0"/>
@@ -3047,7 +3047,7 @@
         <v>600</v>
       </c>
       <c r="AA18" s="2">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="AB18" s="2">
         <v>12</v>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="H19" s="1">
         <f t="shared" si="7"/>
-        <v>159530</v>
+        <v>85330</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="0"/>
@@ -3152,7 +3152,7 @@
         <v>700</v>
       </c>
       <c r="AA19" s="2">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="AB19" s="2">
         <v>13</v>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H20" s="1">
         <f t="shared" si="7"/>
-        <v>221840</v>
+        <v>136880</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="0"/>
@@ -3257,7 +3257,7 @@
         <v>800</v>
       </c>
       <c r="AA20" s="2">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AB20" s="2">
         <v>14</v>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="H21" s="1">
         <f t="shared" si="7"/>
-        <v>290970</v>
+        <v>170190</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="0"/>
@@ -3362,7 +3362,7 @@
         <v>900</v>
       </c>
       <c r="AA21" s="2">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="AB21" s="2">
         <v>15</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="H22" s="1">
         <f t="shared" si="7"/>
-        <v>395300</v>
+        <v>247900</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="0"/>
@@ -3467,7 +3467,7 @@
         <v>1000</v>
       </c>
       <c r="AA22" s="2">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="AB22" s="2">
         <v>16</v>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="H23" s="1">
         <f t="shared" si="7"/>
-        <v>519720</v>
+        <v>349320</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" si="0"/>
@@ -3572,7 +3572,7 @@
         <v>1200</v>
       </c>
       <c r="AA23" s="2">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AB23" s="2">
         <v>17</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="H24" s="1">
         <f t="shared" si="7"/>
-        <v>684740</v>
+        <v>439460</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" si="0"/>
@@ -3677,7 +3677,7 @@
         <v>1400</v>
       </c>
       <c r="AA24" s="2">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="AB24" s="2">
         <v>18</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="H25" s="1">
         <f t="shared" si="7"/>
-        <v>897440</v>
+        <v>594080</v>
       </c>
       <c r="I25" s="1">
         <f t="shared" si="0"/>
@@ -3782,7 +3782,7 @@
         <v>1600</v>
       </c>
       <c r="AA25" s="2">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="AB25" s="2">
         <v>19</v>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="H26" s="1">
         <f t="shared" si="7"/>
-        <v>1090620</v>
+        <v>791820</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="0"/>
@@ -3887,7 +3887,7 @@
         <v>1800</v>
       </c>
       <c r="AA26" s="2">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="AB26" s="2">
         <v>20</v>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="H27" s="1">
         <f t="shared" si="7"/>
-        <v>1406200</v>
+        <v>1050200</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="0"/>
@@ -3992,7 +3992,7 @@
         <v>2000</v>
       </c>
       <c r="AA27" s="2">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="AB27" s="2">
         <v>21</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H28" s="1">
         <f t="shared" si="7"/>
-        <v>2012750</v>
+        <v>1479250</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="0"/>
@@ -4097,7 +4097,7 @@
         <v>2500</v>
       </c>
       <c r="AA28" s="2">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="AB28" s="2">
         <v>22</v>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="H29" s="1">
         <f t="shared" si="7"/>
-        <v>2696700</v>
+        <v>2030100</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="0"/>
@@ -4202,7 +4202,7 @@
         <v>3000</v>
       </c>
       <c r="AA29" s="2">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="AB29" s="2">
         <v>23</v>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="H30" s="1">
         <f t="shared" si="7"/>
-        <v>3496850</v>
+        <v>2559550</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="0"/>
@@ -4307,7 +4307,7 @@
         <v>3500</v>
       </c>
       <c r="AA30" s="2">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="AB30" s="2">
         <v>24</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="H31" s="1">
         <f t="shared" si="7"/>
-        <v>4322800</v>
+        <v>3124400</v>
       </c>
       <c r="I31" s="1">
         <f t="shared" si="0"/>
@@ -4412,7 +4412,7 @@
         <v>4000</v>
       </c>
       <c r="AA31" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="AB31" s="2">
         <v>25</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="H32" s="1">
         <f t="shared" si="7"/>
-        <v>5052150</v>
+        <v>3874950</v>
       </c>
       <c r="I32" s="1">
         <f t="shared" si="0"/>
@@ -4517,7 +4517,7 @@
         <v>4500</v>
       </c>
       <c r="AA32" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AB32" s="2">
         <v>26</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="H33" s="1">
         <f t="shared" si="7"/>
-        <v>6045500</v>
+        <v>4689500</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="0"/>
@@ -4622,7 +4622,7 @@
         <v>5000</v>
       </c>
       <c r="AA33" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AB33" s="2">
         <v>27</v>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="H34" s="1">
         <f t="shared" si="7"/>
-        <v>8305800</v>
+        <v>6781800</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="0"/>
@@ -4727,7 +4727,7 @@
         <v>6000</v>
       </c>
       <c r="AA34" s="2">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="AB34" s="2">
         <v>28</v>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="H35" s="1">
         <f t="shared" si="7"/>
-        <v>10362100</v>
+        <v>8894900</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" si="0"/>
@@ -4832,7 +4832,7 @@
         <v>7000</v>
       </c>
       <c r="AA35" s="2">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="AB35" s="2">
         <v>29</v>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H36" s="1">
         <f t="shared" si="7"/>
-        <v>13919200</v>
+        <v>11069600</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="0"/>
@@ -4937,7 +4937,7 @@
         <v>8000</v>
       </c>
       <c r="AA36" s="2">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="AB36" s="2">
         <v>30</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="H37" s="1">
         <f t="shared" si="7"/>
-        <v>16388100</v>
+        <v>12885300</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="0"/>
@@ -5042,7 +5042,7 @@
         <v>9000</v>
       </c>
       <c r="AA37" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="AB37" s="2">
         <v>31</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="H38" s="1">
         <f t="shared" si="7"/>
-        <v>20413000</v>
+        <v>15943000</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="0"/>
@@ -5147,7 +5147,7 @@
         <v>10000</v>
       </c>
       <c r="AA38" s="2">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="AB38" s="2">
         <v>32</v>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H39" s="1">
         <f t="shared" si="7"/>
-        <v>25186800</v>
+        <v>19750800</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="0"/>
@@ -5252,7 +5252,7 @@
         <v>12000</v>
       </c>
       <c r="AA39" s="2">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="AB39" s="2">
         <v>33</v>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H40" s="1">
         <f t="shared" si="7"/>
-        <v>32750200</v>
+        <v>24837400</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="0"/>
@@ -5356,8 +5356,8 @@
         <f t="shared" si="14"/>
         <v>14000</v>
       </c>
-      <c r="AA40" s="1">
-        <v>149</v>
+      <c r="AA40" s="2">
+        <v>113</v>
       </c>
       <c r="AB40" s="2">
         <v>34</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="H41" s="1">
         <f t="shared" si="7"/>
-        <v>39380800</v>
+        <v>33121600</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="0"/>
@@ -5462,8 +5462,8 @@
         <f t="shared" si="14"/>
         <v>16000</v>
       </c>
-      <c r="AA41" s="1">
-        <v>151</v>
+      <c r="AA41" s="2">
+        <v>127</v>
       </c>
       <c r="AB41" s="2">
         <v>35</v>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="H42" s="1">
         <f t="shared" si="7"/>
-        <v>47194200</v>
+        <v>39378600</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="0"/>
@@ -5567,8 +5567,8 @@
         <f t="shared" si="14"/>
         <v>18000</v>
       </c>
-      <c r="AA42" s="1">
-        <v>157</v>
+      <c r="AA42" s="2">
+        <v>131</v>
       </c>
       <c r="AB42" s="2">
         <v>36</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="H43" s="1">
         <f t="shared" si="7"/>
-        <v>56398000</v>
+        <v>47402000</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="0"/>
@@ -5672,8 +5672,8 @@
         <f t="shared" si="14"/>
         <v>20000</v>
       </c>
-      <c r="AA43" s="1">
-        <v>163</v>
+      <c r="AA43" s="2">
+        <v>137</v>
       </c>
       <c r="AB43" s="2">
         <v>37</v>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="H44" s="1">
         <f t="shared" si="7"/>
-        <v>74732500</v>
+        <v>62202500</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="0"/>
@@ -5777,8 +5777,8 @@
         <f t="shared" ref="Z44:Z77" si="15">Z43+5000</f>
         <v>25000</v>
       </c>
-      <c r="AA44" s="1">
-        <v>167</v>
+      <c r="AA44" s="2">
+        <v>139</v>
       </c>
       <c r="AB44" s="2">
         <v>38</v>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="H45" s="1">
         <f t="shared" si="7"/>
-        <v>93939000</v>
+        <v>80907000</v>
       </c>
       <c r="I45" s="1">
         <f t="shared" si="0"/>
@@ -5883,7 +5883,7 @@
         <v>30000</v>
       </c>
       <c r="AA45" s="1">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="AB45" s="2">
         <v>39</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H46" s="1">
         <f t="shared" si="7"/>
-        <v>115650500</v>
+        <v>100943500</v>
       </c>
       <c r="I46" s="1">
         <f t="shared" si="0"/>
@@ -5988,7 +5988,7 @@
         <v>35000</v>
       </c>
       <c r="AA46" s="1">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="AB46" s="2">
         <v>39</v>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="H47" s="1">
         <f t="shared" si="7"/>
-        <v>133556000</v>
+        <v>116572000</v>
       </c>
       <c r="I47" s="1">
         <f t="shared" si="0"/>
@@ -6092,7 +6092,7 @@
         <v>40000</v>
       </c>
       <c r="AA47" s="1">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="AB47" s="2">
         <v>39</v>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H48" s="1">
         <f t="shared" si="7"/>
-        <v>153364500</v>
+        <v>139180500</v>
       </c>
       <c r="I48" s="1">
         <f t="shared" si="0"/>
@@ -6197,7 +6197,7 @@
         <v>45000</v>
       </c>
       <c r="AA48" s="1">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="AB48" s="2">
         <v>39</v>

--- a/Excel/MonsterBase.xlsx
+++ b/Excel/MonsterBase.xlsx
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" ht="14" spans="1:33">
       <c r="C6" s="1">
         <v>1</v>
       </c>
